--- a/resume_data.xlsx
+++ b/resume_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="516" yWindow="600" windowWidth="15996" windowHeight="7092" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resume_data" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,18 +16,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -420,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="60" customWidth="1" min="3" max="3"/>
@@ -462,453 +457,15 @@
     <row r="2" ht="409.6" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Data Scientist specializing in Machine Learning, Applied Statistics, and Growth Analytics, with expertise in building scalable, cloud-native solutions for financial services and consumer-facing businesses. Skilled in Python, SQL, predictive modeling, feature engineering, and large-scale customer analytics to optimize acquisition, retention, churn, and long-term customer value (LTV). Experienced in developing production-ready ML pipelines, MLOps, and model-monitoring frameworks that improve prediction accuracy, operational efficiency, and risk management. Adept at translating complex data into actionable business strategies for CAC optimization, payback periods, customer segmentation, and growth-spend allocation. Collaborated cross-functionally with Product, Finance, Marketing, Data Engineering, and Engineering teams to deliver measurable business outcomes through data-driven decision-making.</t>
+          <t>ChatGPT said: Data Scientist specializing in **biological data** analysis, **clinical data** modeling, and **precision medicine**, with experience building scalable analytical applications and data-driven solutions for complex decision-making. Skilled in Python, SQL, **statistical methods**, and machine learning to integrate high-dimensional datasets, improve data quality, and generate actionable insights. Experienced in developing computational pipelines, automating analytical workflows, and translating research findings into clear reports and visualizations. Focused on supporting genomic data analysis, clinical evidence generation, risk reduction, and improved patient outcomes through reliable, scalable data science solutions.</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable customer intelligence solutions for a banking client using Python, GPT-5, Claude, LangChain, and AWS Bedrock, analyzing large-scale customer and transaction datasets to improve acquisition quality, retention, and LTV while reducing Tier-1 support workload by 40%.
-Computed CAC, payback periods, customer value, and acquisition efficiency using SQL, Power BI, and AWS SageMaker, applying supervised learning techniques and feature engineering to evaluate customer segments and identify growth opportunities 1–2 reporting cycles earlier.
-Fine-tuned BERT and Hugging Face Transformers models to analyze 100K+ monthly customer interactions, applying Applied Statistics, model evaluation, and churn prediction techniques to improve classification accuracy by 25% and identify customer retention risks.
-Strengthened financial transaction analytics through XGBoost, Isolation Forest, and PyTorch, conducting cohort modelling, customer risk assessment, and experiment design to reduce fraud-related false positives by 30% while informing commercial trade-offs across lending and payments.
-Productionised 10+ machine learning models using Kubeflow, MLflow, Apache Airflow, Docker, and Kubernetes, partnering with Engineering and Data Engineering to automate pipelines, monitor model performance, and maintain MLOps governance while communicating model limitations and recommendations to non-technical stakeholders.</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Analysed large-scale retail customer, product, marketing, and transaction datasets using Python, PySpark, and Azure Databricks, applying ARIMA, Prophet, and LSTM models to improve demand forecast accuracy by 20% and support growth, monetisation, and merchandising decisions.
-Engineered customer analytics and data integration pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating data across customer segments, sales channels, and geographic markets while reducing processing time by 30%.
-Evaluated acquisition quality, retention modelling, and churn prediction using Scikit-learn, Logistic Regression, and Random Forest, incorporating feature engineering, model evaluation, and statistical trade-offs to identify high-value customer cohorts and improve retention strategies.
-Monitored sales performance, inventory anomalies, and customer behaviour through Power BI, DAX, and Azure Monitor, modifying analytical reports, troubleshooting data discrepancies, and correcting model inputs to reduce manual investigation effort by 35%.
-Managed cross-functional analytics initiatives using Agile/Scrum, Jira, and Git, participated in experiment reviews, oriented business stakeholders to modelling assumptions, and motivated collaborative decisions on acquisition efficiency, campaign performance, and customer lifetime value in a fast-moving retail environment.
-The following target-job keywords are incorporated into the summary and experience sections. Additional relevant terms are listed here to support ATS matching.
-Core Data Science: Machine Learning, Applied Statistics, Analytics, supervised learning techniques, model evaluation, feature engineering, statistical trade-offs, business judgement, large-scale datasets.
-Growth and Customer Analytics: B2C, D2C, LTV, growth, acquisition, retention, churn, monetisation, customer value, CAC, payback period, acquisition efficiency, cohort modelling, retention modelling, churn prediction, marketing mix, customer segmentation.
-Business and Collaboration: Growth &amp; Marketing, Product, Finance, Data Engineering, Engineering, cross-functional collaboration, clear communication, non-technical stakeholders, commercial impact, high ownership, evolving priorities, fast-moving environment, fluent English.
-Industry Alignment: Fintech, banking, payments, investing, lending, financial consumer products, consumer fintech, health tech, subscription, retail, wellness, marketplace businesses.
-Production and Experimentation: Productionising models, pipelines, reporting, MLOps, model monitoring, experiment design, causal inference, incrementality measurement, multiple countries, currencies, channels, and customer segments.
-Important resume note: The additional keywords above should be retained only where you can substantiate your familiarity or experience during an interview. The target role emphasizes growth-oriented data science, and specific experience with causal inference, incrementality measurement, and marketing mix modelling was not established in the original responsibilities. Similarly, the supplied dates do not independently establish the job description's five-year experience requirement.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume Arq</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="225" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in full-stack data development, machine learning, and scalable, cloud-native applications that transform complex data into actionable business insights. Experienced in building production-ready data models, optimizing SQL queries, and delivering analytics solutions across payments, financial technology, and customer intelligence. Skilled in data modeling, experimental design, automated testing, and analytics engineering best practices to improve data quality, operational efficiency, and decision-making. Adept at collaborating with product, engineering, data, design, and business teams to ship high-quality features, reduce risk, and enhance customer experiences. Focused on leveraging modern data stack technologies, scalable data pipelines, and business-driven analytics to deliver measurable outcomes.</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable, full-stack conversational AI applications for payments and financial technology workflows using Python, SQL, Amazon Redshift, and AWS Bedrock, integrating retrieval-augmented generation to automate Tier-1 customer support and reduce agent workload by 40%.
-Engineered financial analytics models and executive dashboards using Snowflake, Looker, and dbt, computed credit utilization and risk indicators, and exposed actionable insights to stakeholders, identifying at-risk accounts 1–2 reporting cycles earlier.
-Fine-tuned BERT and Hugging Face Transformers models to analyze 100K+ monthly customer feedback records, improving classification accuracy by 25% and supporting experimental design, hypothesis testing, and iterative product improvements.
-Strengthened fraud detection across AML/KYC transaction workflows using Python, XGBoost, and Amazon SageMaker; troubleshot data quality issues, corrected model outputs, and monitored anomaly detection performance, reducing false positives by 30%.
-Managed production model releases and the analytics engineering development cycle through Git, Docker, Kubernetes, and CI/CD/CT pipelines; participated in cross-functional product, engineering, data, and design planning, motivated continuous improvement, and oriented stakeholders toward scalable delivery and measurable product outcomes.</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Built demand forecasting and customer churn solutions for retail analytics using Python, PySpark, and Google BigQuery, applying ARIMA, LSTM, and Prophet models to point-of-sale, inventory, and loyalty datasets, improving forecast accuracy by 20% and informing replenishment decisions.
-Orchestrated scalable data ingestion and transformation workflows using Fivetran, Azure Data Factory, and ADLS Gen2, consolidating transaction, store operations, and customer service data into analytics-ready datasets and reducing processing time by 30%.
-Delivered interactive business intelligence dashboards using Sigma, Omni, and Power BI, distributed reports on sales performance, inventory shrinkage, and customer behavior, and reduced manual investigation effort by 35% through actionable alerts and visual analytics.
-Modified and validated analytical data models using Snowflake, dbt, and SQL, established documentation, version control, automated testing, and codebase development standards, and applied Hightouch workflows to support reliable data activation and downstream business operations.
-Collaborated with product, engineering, data, design, and business teams in an Agile/Scrum environment, evaluated B2B enterprise sales cycle metrics and customer conversion trends, managed iterative technical solutions, and tested reporting improvements to support faster decisions and continuous product optimization.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume ramp</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="360" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sr Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in supervised and unsupervised learning, computer vision model development, and production-ready AI models that transform complex data into actionable business outcomes. Experienced in building scalable, cloud-native machine learning applications using Python, PyTorch, TensorFlow, and Kubernetes to improve operational efficiency, strengthen risk detection, and enhance customer experiences. Skilled in translating large datasets and complex relationships into data-driven insights, intuitive visualizations, and compelling reports that support strategic decision-making. Focused on secure software development, open-source machine learning solutions, model deployment, and research-driven experimentation to solve industry-specific challenges. Collaborative and accountable professional committed to customer-focused innovation, technical excellence, and measurable business impact.</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable conversational AI applications for banking customers using Python, GPT-5, Claude, LangChain, and AWS Bedrock, integrating retrieval-augmented generation to automate Tier-1 support and reduce agent workload by 40% while aligning solutions with customer use cases.
-Engineered supervised learning models using PyTorch, Logistic Regression, and Gradient Boosting to assess credit utilization and identify at-risk accounts 1–2 reporting cycles earlier, translating complex financial relationships into data-driven insights and intuitive Power BI visualizations for decision-makers.
-Fine-tuned BERT and Hugging Face Transformers on more than 100,000 monthly customer feedback records, improving sentiment classification accuracy by 25% and participating in research-driven experimentation to evaluate model performance, analytical insights, and customer behavior patterns.
-Strengthened fraud detection through supervised and unsupervised learning, leveraging TensorFlow, XGBoost, Isolation Forest, and synthetic data generation to reduce false positives by 30% across AML/KYC workflows; troubleshot model errors, corrected classification issues, and communicated findings through compelling reports.
-Managed and monitored deployment pipelines using Docker, Kubernetes, NVIDIA CUDA Toolkit, and Kubeflow, supporting 10+ production AI models; modified deployment configurations, participated in open-source projects, motivated cross-functional collaboration, oriented team members to model workflows, and enforced security policies and secure software development goals.</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Analyzed retail transaction, inventory, and loyalty datasets using Python, PySpark, and Scikit-learn, applying supervised and unsupervised learning alongside ARIMA, LSTM, and Prophet to improve demand forecasting accuracy by 20% and deliver analytical insights for merchandising decisions.
-Orchestrated data preparation and feature engineering across Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transaction, store operations, and customer service data into analytics-ready datasets while reducing processing time by 30% and maintaining data quality standards.
-Conducted computer vision model development experiments using OpenCV, TensorFlow, and PyTorch to evaluate image-based anomaly detection approaches for retail inventory monitoring, measuring model performance and documenting research findings to support practical machine learning applications.
-Deployed containerized machine learning services using Docker, Azure Kubernetes Service (AKS), and Azure Monitor, generating inventory shrinkage and sales anomaly alerts that reduced manual investigation effort by 35%; troubleshot deployment issues and monitored model reliability across store-level workflows.
-Presented findings through Tableau, Matplotlib, and Seaborn visualizations, converting large datasets and complex relationships into intuitive dashboards, compelling reports, and stakeholder presentations; participated in Agile/Scrum reviews, managed individual and team deliverables, and communicated technical recommendations directly to business customers.
-Computer vision and NVIDIA CUDA Toolkit: These were not explicitly established in your original responsibilities. Keep those additions only if you can substantiate the experience in an interview. Otherwise, describe them as research or experimental work only if you actually performed that work.
-Open-source projects, mentoring/orientation, and customer presentations: Retain these claims only if they reflect your actual responsibilities.
-Education: The job description requires a master's degree or an equivalent combination of education, training, and experience. Add your actual degree and specialization in the Education section if applicable.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume sas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="225" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in machine learning, statistical modeling, predictive analytics, and AI-driven solutions for complex business and regulated-data environments. Experienced in building scalable applications, cloud-native ML pipelines, and forecasting systems to improve operational efficiency, optimize resource allocation, and strengthen risk management. Skilled in Python, SQL, Bayesian inference, regression analysis, time-series forecasting, and patient matching algorithms for data-driven decision-making. Proficient in AWS SageMaker, AWS Athena, AWS Redshift, dbt, model monitoring, bias detection, and regulatory compliance aligned with HIPAA and GDPR. Collaborated with machine learning engineers, product managers, and cross-functional stakeholders to translate analytical insights into actionable solutions that enhance recruitment efficiency, data reliability, and patient outcomes.</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable AI-powered decision-support applications using Python, AWS SageMaker, and scikit-learn, developing patient matching and patient ranking algorithms that improved recruitment efficiency by 30% and supported patient inclusion across clinical research workflows.
-Engineered site randomization and enrollment trends forecasting models using Bayesian inference, PyMC, and mlforecast, combining regression analysis and time-series forecasting to improve enrollment prediction accuracy by 25% and optimize resource allocation across 20+ simulated trial sites.
-Optimized analytical data pipelines using AWS Athena, AWS Redshift, and dbt, transforming multi-source clinical research datasets into model-ready features while reducing data preparation time by 35% and supporting scalable machine learning workflows.
-Strengthened AI monitoring and model risk controls using Python, SHAP, and LIME, monitored performance drift, troubleshot model discrepancies, corrected prediction errors, and applied bias detection and bias mitigation techniques to improve model fairness and reliability by 20%.
-Managed cross-functional delivery with machine learning engineers, product managers, and clinical research stakeholders, participated in Agile reviews, motivated collaborative problem-solving, oriented team members to data-handling procedures, and enforced HIPAA, GDPR, and clinical data privacy requirements across 100% of designated workflows.</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Analyzed longitudinal operational and customer datasets using Python, SQL, and Pandas, computed enrollment projections, evaluated recruitment patterns, and applied regression analysis to identify resource constraints and improve forecasting accuracy by 22% across 12 business reporting cycles.
-Constructed scalable data transformation workflows with AWS Glue, Amazon S3, and dbt, integrated disparate transactional and operational records, standardized data quality checks, and reduced processing time by 30% while improving analytical data consistency across 5 source systems.
-Evaluated predictive models using Scikit-learn, XGBoost, and Bayesian methods, performed feature engineering and statistical validation, and refined model selection to improve prediction reliability by 18% for complex forecasting and risk assessment use cases.
-Deployed containerized analytical services through Docker, Kubernetes, and FastAPI, troubleshot production integration issues, modified deployment configurations, and monitored application performance to reduce manual investigation effort by 35% and improve model availability across 3 deployment environments.
-Presented actionable analytical findings through Power BI and Tableau, communicated recommendations to engineering, product, and business stakeholders, managed model documentation, and supported GDPR, HIPAA, data governance, and privacy-by-design practices to strengthen compliance readiness and reduce data-handling risks.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume careaccess</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="225" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Research Data Scientist</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in data quality engineering, healthcare informatics, machine learning, and reproducible research workflows to transform complex datasets into reliable, actionable insights. Experienced in building scalable data processing pipelines, cloud-native analytics solutions, and predictive models that support risk assessment, disease progression analysis, and treatment effectiveness research. Proficient in Python, R, SQL, AWS, Microsoft Azure Platform, Azure Synapse, and ADF, with expertise in data profiling, validation, cleansing, standardization, and automated quality monitoring. Skilled in clinical data harmonization, statistical analysis, hypothesis testing, bias and fairness assessment, and data visualization to improve research reliability and decision-making. Adept at collaborating with researchers, administrators, and technical stakeholders to establish data governance, reproducible methodologies, and efficient analytical workflows that enhance operational efficiency and reduce data quality risks.</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Architected and optimized 5 scalable informatics pipelines using Python, SQL, and AWS to integrate heterogeneous structured and unstructured datasets, applying data profiling, cleansing, standardization, validation, and data harmonization techniques that improved dataset reliability by 35%.
-Engineered predictive models using R, Scikit-learn, and XGBoost on retrospective real-world datasets to estimate disease risk, disease progression, and treatment effectiveness, incorporating hypothesis testing, observational data analysis, and bias and fairness assessments to strengthen research validity by 25%.
-Established automated data quality rules, validation frameworks, anomaly detection procedures, and quality monitoring processes using AWS SageMaker and Amazon CloudWatch, defining data quality metrics and dashboards that reduced recurring data inconsistencies by 30%.
-Integrated clinical data, healthcare data, and research data through FHIR, OMOP, UMLS, ICD, SNOMED CT, LOINC, and RxNorm standards, documenting data transformations, methodological limitations, and reproducible research methodologies to improve interoperability across 4 heterogeneous data sources.
-Collaborated as a data science subject matter expert and liaison with researchers, administrators, and internal and external stakeholders, communicating data quality findings and recommendations through Power BI reporting tools and visualization solutions while promoting data science best practices and reproducible analysis workflows that reduced manual reporting effort by 40%.</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Processed and harmonized more than 1 million records from diverse transactional, operational, and research datasets using Microsoft Azure Platform, Azure Synapse, and ADF, applying data restructuring, integration, transformation, and data quality assurance procedures that reduced processing time by 30%.
-Conducted statistical analysis, data mining, and machine learning on observational datasets using Python, R, and SQL, identifying patterns, inconsistencies, anomalies, and root causes through rigorous hypothesis testing and predictive analytics that improved analytical accuracy by 20%.
-Designed and maintained data quality dashboards and reporting solutions using MS Fabric and Tableau, tracking completeness, consistency, validity, standardization, and anomaly trends across 12 quality indicators and enabling stakeholders to identify and resolve data issues 35% faster.
-Organized and automated end-to-end data preparation and analysis steps through Azure Data Factory workflows and Microsoft Azure services, establishing reusable data quality checks, reproducible data science workflows, and validation procedures that decreased manual preparation effort by 40%.
-Documented data transformations, quality rules, analytical methodologies, model limitations, and reproducible research workflows using Git and Jupyter Notebook, assembling standardized reports and visualizations for researchers, administrators, and technical stakeholders while strengthening research reproducibility and data governance across 3 analytical projects.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume university of wisconsin</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="225" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior+ Data Scientist</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in applied machine learning, generative AI, and scalable ML applications, with a focus on production optimization, model evaluation, and data-driven experimentation. Experienced in building Python-based solutions using PyTorch, LLMs, and generative AI techniques to improve model accuracy, latency, consistency, and user experience. Skilled in designing large-scale data pipelines, evaluation frameworks, A/B testing, prompt engineering, and content safety systems to deliver measurable business outcomes. Adept at applying statistical analysis, automated evaluation, and data quality controls to reduce errors, mitigate risks, and improve production reliability. Committed to developing scalable, cloud-native AI solutions that enhance efficiency, strengthen safety, and deliver high-quality user experiences.</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable generative AI assistants using Python, GPT-5, Claude, LangChain, and AWS Bedrock, curating enterprise knowledge datasets and refining RAG workflows to improve response relevance by 40% and reduce manual customer support workloads.
-Engineered model evaluation and data quality workflows using PyTorch, BERT, Hugging Face Transformers, and Pandas, analyzing 100K+ monthly customer feedback records, correcting annotation inconsistencies, and improving classification accuracy by 25%.
-Optimized generative AI and fraud detection pipelines using XGBoost, Isolation Forest, and Autoencoders, identifying bottlenecks and failure modes, troubleshooting model outputs, and reducing false positives by 30% across transaction monitoring workflows.
-Conducted systematic prompt engineering and A/B testing using LangGraph, RAG, and FAISS, modifying prompt templates, measuring relevance and response consistency, and improving output quality across multiple customer support scenarios.
-Managed production ML lifecycle workflows using Kubeflow, Apache Airflow, MLflow, Docker, and Kubernetes, monitored 10+ production models, participated in model risk reviews, oriented cross-functional stakeholders to evaluation findings, and motivated iterative improvements through documented performance metrics.</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Built and curated large-scale retail image and transaction datasets using Python, PySpark, and Azure Databricks, organized training samples and annotation guidelines, and improved forecasting accuracy by 20% through structured data preparation and model experimentation.
-Designed scalable data ingestion and annotation quality workflows using Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, validated multi-source datasets, corrected inconsistencies across transaction and customer records, and reduced processing time by 30%.
-Evaluated model training runs and predictive outputs using Scikit-learn, TensorFlow, ARIMA, LSTM, and Prophet, computed statistical performance metrics, compared experimental results, and identified optimization opportunities across forecasting and anomaly detection models.
-Strengthened content safety and moderation evaluation practices using Random Forest, Logistic Regression, and Power BI, analyzed false-positive and false-negative patterns, assessed risk-related edge cases, and reduced manual investigation effort by 35% through improved monitoring and reporting.
-Established automated model evaluation and experiment tracking workflows using Azure Kubernetes Service (AKS), Docker, Azure Monitor, and Git, tested model changes, measured latency and reliability, participated in Agile reviews, and communicated findings to technical and business teams to support production ML improvements.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume hapiko</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="225" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in financial crime analytics, BSA/AML, OFAC/Sanctions, risk assessment, and regulatory reporting for data-driven financial services environments. Experienced in leveraging advanced SQL, Python, Excel, and Power BI to analyze complex datasets, validate data integrity, automate reporting, and strengthen risk assessment methodologies. Skilled in data governance, data lineage, quality control (QC) validation, audit-ready documentation, and analytical process optimization to improve operational efficiency and regulatory auditability. Adept at translating business and regulatory requirements into actionable insights while collaborating with technical stakeholders, data owners, and cross-functional teams. Committed to continuous improvement, risk mitigation, reporting accuracy, and accountable project delivery in fast-paced, compliance-driven environments.</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Analyzed large-scale banking transaction and customer datasets using SQL and Python to support BSA/AML, OFAC/Sanctions, and financial crime risk assessments, performing data collection, quality control (QC) validation, and quantitative reporting across 5+ data sources while improving data accuracy by 25%.
-Managed risk assessment methodologies, technical requirements, data mapping, and complex query logic for risk factor calibration and methodology enhancements; computed risk indicators, troubleshot data discrepancies, corrected mapping errors, and modified validation rules to strengthen data integrity across 10+ risk indicators.
-Orchestrated Power BI dashboard development and Excel reporting automation to deliver management reporting, thematic reviews, and risk assessment findings, reducing manual reporting effort by 35% and improving visibility into transaction anomalies, sanctions exposure, and emerging financial crime risks.
-Coordinated with Business Intelligence, Data Governance, IT, and system owners to establish data lineage, gather reporting requirements, validate assumptions, and document analytical processes; participated in cross-functional reviews, motivated stakeholder engagement, and oriented technical teams to standardized QC procedures, improving reporting consistency across 4+ stakeholder groups.
-Supported internal audit, regulatory examinations, independent reviews, and audit requests by preparing data analysis, evidence, and audit-ready procedural documentation aligned with financial crime compliance requirements; managed multiple assignments, monitored dependencies and deadlines, escalated delivery risks, and maintained accountability for 100% of assigned deliverables within agreed timelines.</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>Extracted and transformed complex banking and retail datasets from 6+ multiple source systems using Advanced SQL querying and PySpark, conducting data analysis and risk segmentation to identify anomalous transactions, customer behavior patterns, and potential financial crime indicators while reducing data processing time by 30%.
-Evaluated BSA/AML and sanctions risk assessment frameworks by applying Python-based analytical methods to customer, transaction, and operational data; assessed risk factors, validated assumptions, and supported quantitative methodology enhancements that improved risk identification and analytical consistency by 20%.
-Streamlined data transformation, data governance, and quality control (QC) validation workflows across Azure Data Factory and Azure Synapse Analytics, documenting data mappings, transformation rules, data lineage, and validation evidence to improve data completeness, auditability, and reporting reliability by 30%.
-Produced Power BI visualizations and Excel management reports to communicate key findings, risk trends, and data quality exceptions to business and technical stakeholders; facilitated requirements gathering, communicated analytical results, and reduced manual investigation effort by 35% through standardized reporting workflows.
-Supported consulting engagements involving financial crime compliance, regulatory compliance, and risk management by maintaining procedural documentation, tracking project dependencies, and coordinating with data owners on evidence collection and reporting requirements; prioritized multiple assignments, monitored delivery timelines, escalated issues, and strengthened audit readiness through documented controls and continuous improvement initiatives.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume eastwest bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="225" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Lead Data Scientist</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in experimentation, model evaluation, production monitoring, and AI/ML product measurement for scalable, cloud-native applications and data-driven business systems. Experienced in building evaluation frameworks, defining statistical baselines, and designing offline and online metrics to assess model performance, detect drift, and improve data quality when ground truth is imperfect. Proficient in Python, SQL, machine learning, statistical data processing, and production ML systems, translating complex business problems into measurable technical initiatives. Collaborated with ML engineers, domain experts, and cross-functional partners to establish validation strategies, improve evidence quality, and align technical plans with business objectives. Delivered measurable business outcomes through scalable AI solutions that enhanced operational efficiency, strengthened risk detection, improved decision-making, and supported reliable customer-facing experiences.</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable AI/ML product opportunities for banking applications using Python, SQL, and GPT-5, translating ambiguous problem spaces into scoped initiatives, technical plans, and defined success criteria that reduced Tier-1 customer support workload by 40%.
-Established experimentation and evaluation frameworks for production models using Claude, LangChain, and AWS Bedrock, defining baselines, offline metric design, online metric design, and model validation strategies that improved response quality by 25% across customer-facing applications.
-Computed statistical performance metrics and monitored production models using Pandas, NumPy, and Power BI, tracking model evaluation, measurement, and drift detection across enriched datasets to identify emerging credit risks 1–2 reporting cycles earlier.
-Troubleshot and corrected fraud detection performance issues using XGBoost, Isolation Forest, and AWS SageMaker, validating evidence quality when ground truth was imperfect and reducing false-positive alerts by 30% across AML/KYC transaction workflows.
-Managed monitoring and deployment workflows using MLflow, Kubeflow, and Kubernetes, collaborated with ML engineers and cross-functional partners, and participated in model risk management reviews to improve validation standards and maintain 10+ production models.</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Analyzed consumer software product metrics and retail behavior using PySpark, Azure Databricks, and Prophet, identified AI/ML product opportunities with domain experts, and established forecasting baselines that improved demand prediction accuracy by 20%.
-Engineered enriched datasets through Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, modified data quality checks, and monitored downstream data pipelines to reduce processing time by 30% and improve evidence quality for business decisions.
-Evaluated churn and anomaly detection models using Scikit-learn, TensorFlow, and ARIMA, designed validation strategies for imperfect ground truth, and measured performance against established baselines to reduce manual inventory-risk investigations by 35%.
-Oriented stakeholders and motivated cross-functional partners around measurement objectives using Tableau, SQL, and A/B testing, defined success criteria, and translated business requirements into technical plans for customer retention and merchandising initiatives.
-Scoped and prioritized analytical initiatives with ML engineers and business stakeholders, established offline and online measurement approaches, monitored key performance metrics, and documented model evaluation results to support reliable production systems and athlete-facing experiences.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume strava</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="315" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in predictive modeling, machine learning, and production-grade ML architectures that improve risk estimation, pricing competitiveness, and business profitability. Experienced in building scalable, cloud-native solutions using Python, SQL, and Spark to process large datasets and deliver reliable, data-driven predictions. Skilled in feature engineering, model validation, bias analysis, and backtesting to improve prediction accuracy and demonstrate measurable business lift. Applied AI and analytics expertise to financial risk, fraud detection, and customer behavior, with transferable capabilities in healthcare risk modeling, claims analysis, and member cost variance assessment. Focused on translating complex model outcomes into actionable roadmaps that strengthen decision-making, operational efficiency, and customer outcomes.</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Architected production-ready conversational AI solutions for banking operations using Python, GPT-5, Claude, LangChain, and AWS Bedrock, integrating RAG and FAISS to automate Tier-1 support, reduce agent workload by 40%, and establish scalable ML architectures for risk-related customer insights.
-Engineered predictive credit-risk features with SQL, Pandas, NumPy, and Power BI, computing member-level cost variance and account risk indicators across 100K+ records to improve risk visibility by 25% and support more competitive, profitability-focused pricing decisions.
-Fine-tuned BERT and Hugging Face Transformers models to analyze 100K+ monthly customer feedback records, corrected data-quality issues, investigated dataset bias, and evaluated cohort-level prediction gaps to improve classification accuracy by 25% and strengthen model validation.
-Strengthened fraud and financial-risk prediction using XGBoost, Isolation Forest, and AWS SageMaker, troubleshot anomalous transaction patterns, modified risk features, and evaluated model designs against historical outcomes to reduce false positives by 30% and improve risk-estimation reliability.
-Managed end-to-end model deployment and monitoring through Kubeflow, Apache Airflow, MLflow, Docker, and Kubernetes, participated in ML engineering and infrastructure improvements, motivated cross-functional adoption of validation standards, and oriented stakeholders on model governance while supporting 10+ production models.</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>Built predictive demand-forecasting and customer-churn models using Python, PySpark, Apache Spark, and Azure Databricks, analyzing millions of retail transactions to improve forecast accuracy by 20% and demonstrate measurable model lift for inventory and commercial planning.
-Orchestrated large-scale data integration through Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating claims-like transaction records, customer service data, and operational datasets into analytics-ready pipelines while reducing processing time by 30% and improving downstream model reliability.
-Evaluated ARIMA, LSTM, and Prophet forecasting approaches through historical backtesting, cohort segmentation, and feature engineering, establishing a repeatable backtesting harness to compare model performance, quantify prediction variance, and prioritize enhancements based on measurable business impact.
-Deployed anomaly-detection workflows using Docker, Azure Kubernetes Service (AKS), and Azure Monitor, monitored store-level sales and inventory deviations, investigated data-quality gaps, and reduced manual risk investigations by 35% through automated alerts and actionable analytics.
-Delivered model-performance reporting with Power BI, DAX, and SQL, presented validation findings to business stakeholders, and translated analytical results into improvement roadmaps covering risk adjustments, underwriting-style decision criteria, and actuarial risk assessment concepts to support stronger pricing and profitability decisions.
-The following target-job keywords have been incorporated into the experience and summary where relevant. Some are transferable concepts rather than confirmed prior job duties, so they should be verified before being presented as direct hands-on experience.
-Important before submitting: The original experience describes banking and retail projects, not confirmed healthcare projects. Direct healthcare data, claims-data quirks, medical loss ratio (MLR), underwriting, and actuarial sciences experience should only be stated as hands-on experience if you can substantiate it. The same applies to the suggested numerical achievements and healthcare-specific results: retain only metrics and activities that accurately reflect your work.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume arlo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="225" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Scientist III</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in advanced analytics, machine learning, experimentation, and scalable data science solutions that drive measurable business outcomes. Experienced in building robust data pipelines, predictive models, and cloud-native applications to improve operational efficiency, reduce risk, and enhance customer experiences across financial services and retail domains. Skilled in translating complex datasets into actionable insights that inform product strategy, business decisions, and long-term planning. Adept at A/B testing, statistical analysis, cross-functional collaboration, and MLOps, with a focus on delivering high-quality, production-ready solutions. Strong communicator committed to knowledge sharing, technical documentation, and data-driven decision-making for technical and business audiences.</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable conversational AI solutions for banking products using Python, GPT-5, Claude, LangChain, and AWS Bedrock, integrating large-scale customer data through RAG, FAISS, and Pinecone to automate Tier-1 support and reduce agent workload by 40%, while translating advanced analyses into actionable product and business decisions.
-Conducted statistical analyses and A/B testing on credit utilization and customer engagement workflows using SQL, Power BI, and AWS SageMaker, computing risk indicators and evaluating Logistic Regression and Gradient Boosting models to identify at-risk accounts 1–2 reporting cycles earlier and support data-driven product decisions.
-Fine-tuned BERT and Hugging Face Transformers models to analyze more than 100K monthly customer feedback records, improving classification accuracy by 25%; presented findings through Tableau visualizations and technical documentation to communicate actionable insights to technical and business audiences.
-Strengthened fraud detection across AML/KYC transaction workflows by generating synthetic data with GenAI and evaluating XGBoost, Isolation Forest, and Autoencoders, reducing false positives by 30%; troubleshot model performance issues, modified detection thresholds, and corrected data-quality inconsistencies to improve solution reliability.
-Managed production model lifecycle processes using Kubeflow, Apache Airflow, MLflow, Docker, Kubernetes, and CI/CD/CT pipelines, deploying and monitoring 10+ models while enforcing Model Risk Management (MRM) practices; participated in cross-functional planning, motivated knowledge sharing, mentored colleagues on best practices, and contributed technical direction for high-impact, long-term data science initiatives.</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>Performed advanced demand forecasting and customer churn analyses for retail products using Python, PySpark, ARIMA, LSTM, and Prophet, improving forecast accuracy by 20% and generating actionable insights for merchandising, replenishment, and customer retention decisions through large-scale product data analysis.
-Engineered scalable, robust data pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transactional, inventory, store operations, and customer support data into analytics-ready datasets and reducing processing time by 30%; managed data integration, monitored pipeline quality, and corrected inconsistencies to maintain reliable analytical outputs.
-Deployed inventory and sales anomaly detection solutions using Scikit-learn, Isolation Forest, Autoencoders, Docker, and AKS, integrating model outputs into Power BI dashboards and Azure Monitor alerts to reduce manual investigation effort by 35% and improve operational risk visibility.
-Evaluated model performance and business hypotheses through statistics, experimentation, and A/B testing, applying feature engineering, Random Forest, and XGBoost to assess customer behavior and operational outcomes; documented data science methodologies, compared model results, and recommended improvements that aligned analytical solutions with business goals.
-Collaborated with engineering, product, and analytics teams using Agile/Scrum, Jira, and Git/GitHub to integrate data science solutions into product workflows; prepared presentations, visualizations, and documentation for diverse audiences, oriented stakeholders to analytical tools and processes, participated in knowledge-sharing sessions, and contributed to long-term planning focused on solution quality, efficiency, and impact.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume indeed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="225" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Science Engineer</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in industrial AI, predictive analytics, machine learning, and scalable data engineering to deliver actionable insights and improve operational efficiency. Experienced in designing cloud-native analytics solutions, developing predictive models, and optimizing data pipelines for risk management, anomaly detection, and business-critical decision-making. Skilled in Python, SQL, R, DataBricks, Snowflake, TensorFlow, and statistical analysis, with expertise in supervised and unsupervised learning, industrial time-series analysis, and model lifecycle management. Focused on advancing System.AI, EcoCare analytics, and condition-based maintenance through industrial asset modeling, intelligent alerts, and optimized service interventions. Adept at collaborating with subject matter experts and clients to strengthen reliability, minimize operational risks, and improve service-level outcomes.</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable System.AI and EcoCare analytics solutions for predictive maintenance use cases, integrating Python, SQL, and Snowflake to process 100K+ monthly records, identify operational risks, and reduce unnecessary interventions by 30%.
-Engineered industrial time-series analytics using TensorFlow and Neural Networks, applying supervised and unsupervised learning, classification models, and cluster analysis to detect equipment anomalies and improve predictive accuracy by 25%.
-Designed and managed Industrial Asset model creations and management workflows using DataBricks, incorporating labelled client datasets, statistical analysis, data mining, and model definition to improve asset-risk identification across 50+ monitored assets.
-Collaborated with subject matter experts (SMEs) and key clients to define use cases, troubleshoot data-quality issues, correct inconsistencies, and normalize industrial time series, alerts, and alarms, reducing false-positive alerts by 30%.
-Recommended and deployed enhancements to cloud solutions, instrumentation, and edge solutions for industrial applications and services, applying Fuzzy Logic, Git, and Jira to improve analytic outcomes, optimize client SLAs, and strengthen condition-based maintenance workflows.</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>Built predictive analytics workflows for equipment reliability and service optimization using Python, R, and Azure Machine Learning, analyzing 1M+ historical operational records to improve failure-risk prediction by 20% and support condition-based maintenance planning.
-Streamlined industrial data engineering with Azure Data Factory and Azure Data Lake Storage Gen2, cleansing, transforming, and normalizing multi-source telemetry datasets to reduce data processing time by 30% and improve downstream analytics readiness.
-Constructed and maintained industrial asset models with Azure Synapse Analytics, integrating equipment hierarchies, maintenance histories, and sensor measurements across 200+ asset records to strengthen asset tracking and maintenance prioritization.
-Evaluated classification, regression, clustering, and anomaly-detection techniques using Scikit-learn and Pandas, computed statistical performance metrics, modified model parameters, and optimized intervention thresholds to reduce manual investigation effort by 35%.
-Coordinated analytics delivery through Azure Databricks, GitHub, and Jira, participated in Agile reviews, motivated cross-functional teams, oriented stakeholders to model outputs, monitored service performance, and enhanced cloud and edge integration to improve service-level compliance by 15%.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume Schneider electric</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="409.6" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>data scientist</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Data Scientist specializing in healthcare analytics, machine learning, pharmaceutical market research, and scalable cloud-native applications that transform complex data into actionable business insights. Skilled in Python, SQL, AWS, claims analytics, EHR data processing, HCP prescribing behavior, patient segmentation, and demand forecasting to improve targeting precision and support data-driven decisions. Experienced in building end-to-end data pipelines, predictive models, synthetic provider and patient personas, and API-driven data products while prioritizing data quality, governance, and HIPAA compliance. Adept at integrating quantitative datasets with qualitative research insights to strengthen patient journey mapping, audience simulation, and pharmaceutical market intelligence. Focused on delivering scalable analytics solutions, operational efficiency, risk reduction, and enhanced customer and patient experiences through reliable data products and machine learning.</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>Architected scalable healthcare and pharmaceutical analytics solutions using Python, SQL, AWS Athena, and Amazon S3, analyzing deidentified medical and pharmacy claims, EHR records, Rx/Dx data, and HCP prescribing patterns across 5+ treatment areas while adhering to HIPAA requirements.
-Engineered data integration workflows using AWS Glue, dbt, and Great Expectations to perform data cleaning, scarcity and gap analysis, identity matching, tokenization, data harmonization, and data augmentation, producing tested, version-controlled data marts and analytics workspaces that improved data readiness by 35%.
-Conducted exploratory data analysis and feature engineering with pandas, NumPy, and Amazon SageMaker, training and evaluating predictive models for HCP prescribing behavior, patient segmentation, demand forecasting, and patient journey mapping; improved model performance by 25% across defined evaluation metrics.
-Generated AI-powered synthetic provider and patient personas using GPT-5, Claude, LangChain, and FAISS, linking qualitative research insights and attitudinal segments to NPIs and observed prescribing behavior to simulate audience segments and project pharmaceutical market trends across national populations.
-Built and deployed scalable backend APIs using FastAPI, AWS ECS/Fargate, AWS App Runner, and AWS Lambda, delivering segmentation insights and synthetic data products to internal and client-facing applications; troubleshot integration issues, corrected data inconsistencies, modified model workflows, and monitored service performance to reduce processing delays by 30%.</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>Analyzed large-scale healthcare and pharmacy datasets using Python, PySpark, and Azure Databricks, combining medical claims, pharmacy claims, EHR records, and prescribing histories to model HCP behavior by drug, diagnosis, and treatment area; improved forecasting accuracy by 20% across evaluated business scenarios.
-Orchestrated end-to-end data pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, integrating claims, provider, patient, survey, and primary research datasets; resolved identity matching and data harmonization issues across 5+ source categories and reduced data processing time by 30%.
-Trained and evaluated predictive models using Scikit-learn, XGBoost, and TensorFlow to support HCP segmentation, patient personas, treatment journey analysis, and demand forecasting; computed segment-level prescribing metrics and improved identification of high-potential provider groups by 22%.
-Produced pharmaceutical market intelligence through Power BI, Tableau, and SQL, translating qualitative research insights into quantitative projections, mapping patient journeys, and associating HCP attitudinal segments with NPIs and observed prescribing behavior; reduced manual reporting effort by 35%.
-Participated in Agile delivery and model governance using Jira, GitHub, and Docker, managed version-controlled analytical workflows, oriented cross-functional stakeholders to segmentation outputs, motivated adoption of data-driven targeting, and incorporated AI coding assistants and agentic development tools to accelerate analytical delivery by 25%.
-Healthcare and compliance: EHR, HIPAA, medical claims, pharmacy claims, Rx/Dx, deidentified data.
-Pharmaceutical analytics: HCP prescribing behavior, attitudinal segments, NPIs, patient segmentation, patient personas, demand forecasting, journey mapping, audience simulation, qualitative research insights.
-Data engineering and quality: Data cleaning, scarcity analysis, gap analysis, joining, data augmentation, transformation, partitions, data marts, analytics workspaces, identity matching, tokenization, data harmonization, dbt, Great Expectations.
-AWS and application delivery: AWS Athena, S3, Glue, SageMaker, FastAPI, ECS/Fargate, App Runner, Lambda.
-Machine learning and AI: Exploratory data analysis, feature engineering, model training and evaluation, synthetic provider personas, synthetic patient personas, LLMs, AI coding assistants, agentic development tools.
-Healthcare data vendors: IQVIA, Komodo, Symphony, Definitive Healthcare.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume Biovid</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>ChatGPT said: Data Scientist specializing in **biological data** analysis, **clinical data** modeling, and **precision medicine**, with experience building scalable analytical applications and data-driven solutions for complex decision-making. Skilled in Python, SQL, **statistical methods**, and machine learning to integrate high-dimensional datasets, improve data quality, and generate actionable insights. Experienced in developing computational pipelines, automating analytical workflows, and translating research findings into clear reports and visualizations. Focused on supporting genomic data analysis, clinical evidence generation, risk reduction, and improved patient outcomes through reliable, scalable data science solutions.</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>Architected scalable analytical workflows using Python, SQL, and AWS SageMaker to integrate **biological data**, **clinical data**, and high-dimensional patient-level records from **EHR** systems, improving evidence generation and supporting **Precision Medicine** decisions by 30%.
 Engineered prototype **bioinformatics workflows** for next-generation sequencing (**NGS**) data analysis using Hugging Face Transformers and PyTorch, supporting genomic data interpretation, **assay offerings**, and the development of clinical-grade genomic analytical workflows across 5 research initiatives.
@@ -917,7 +474,7 @@
 Managed research documentation, monitored data quality, and participated in cross-functional reviews with **wet-lab** and **dry-lab** teams, applying **data science methodologies**, **genetic testing** practices, and Model Risk Management (MRM) principles to strengthen data integrity, security, and reproducibility across 10+ production models.</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Analyzed clinical and patient-level datasets using R, SQL, and Azure Databricks, applying statistical analysis and **computational methods** to identify clinically relevant trends and improve evidence-based decision-making by 20%.
 Designed scalable data integration pipelines using Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating structured and unstructured clinical records into analysis-ready datasets and reducing data preparation time by 30%.
@@ -927,24 +484,24 @@
 Important: The job description requires at least three years of data science experience in a genomics clinical laboratory, genomics health tech, or applied genomics research setting, along with a relevant master's degree. These drafts incorporate the requested ATS terminology, but genomic laboratory work, **NGS** analysis, **EHR** integration, and clinical-grade pipeline experience should remain on your résumé only where they accurately reflect your actual background.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume childeren's hospital</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="270" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="3" ht="225" customHeight="1">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in computational biology, scientific computing, and AI-driven analytics to transform complex biomedical data into actionable research insights. Experienced in building scalable **analytical workflows**, integrating multimodal datasets, and developing machine learning models to support biological discovery and clinical research. Skilled in **Python**, R, **single-cell RNA-seq**, **spatial transcriptomics**, **genomic** data analysis, and reproducible pipelines. Applied statistical modeling, hypothesis testing, and computational analysis to characterize complex patterns, improve research efficiency, and support evidence-based decisions. Committed to advancing precision medicine, **tumor microenvironment** research, and cross-functional scientific collaboration through reliable **analytical frameworks**.</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Analyzed high-dimensional **single-cell RNA-seq**, **spatial transcriptomics**, and **bulk RNA-seq** datasets using **Python**, R, and Scanpy, processing 100K+ cellular profiles to characterize the **tumor microenvironment**, **immune cell states**, and **cell-cell interactions**.
 Integrated **CosMx**, **Visium**, and **CODEX** spatial measurements with **genomic**, **proteomic**, and **clinical data**, applying multimodal analysis across 5+ data sources to identify biologically meaningful patterns and potential disease biomarkers.
@@ -953,7 +510,7 @@
 Collaborated with experimental and clinical teams to refine biological questions, interpret findings, and prepare research outputs for manuscripts, first or co-first authorship contributions, and grant development; monitored emerging computational biology methods and supported **cross-project standardization** across 4+ projects.</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Processed complex **genomic**, transcriptomic, and clinical datasets using R, **Python**, and Bioconductor, applying statistical analysis and scientific computing methods to evaluate gene expression patterns across 50K+ records.
 Investigated **immune cell states**, tumor-associated expression signatures, and **cell-cell interactions** through **single-cell RNA-seq** and **spatial transcriptomics** analysis, generating candidate biological insights and improving analytical interpretation by 20%.
@@ -963,24 +520,24 @@
 Important: The responsibilities above are tailored to the target computational biology role and include its principal research keywords. Keep only technologies, methods, and research activities you can accurately discuss in an interview. In particular, single-cell and **spatial transcriptomics** tools, **tumor microenvironment** analyses, manuscript authorship, grant contributions, and biomedical dataset experience should reflect your actual work.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume MD Anderson Cancer Center</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="225" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="4" ht="360" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in **data science**, predictive modeling, machine learning, and operational analytics to solve complex **business challenges** across **financial services** and **lending operations**. Built scalable, cloud-native analytics solutions, predictive **dashboards**, and automated **reporting** workflows that improved operational efficiency, credit **risk management**, and customer experience. Applied Python, **SQL**, Tableau, and advanced **statistical techniques** to transform **large**-scale datasets into **actionable insights** and data-driven business strategies. Strengthened **data integrity**, **data quality**, **risk management**, and **BI effectiveness** through analytics automation, **performance** monitoring, and **process improvement initiatives**. Communicated **succinct**, actionable recommendations to **executive audiences** and collaborated with cross-functional teams to support **operational decision-making** in fast-paced environments.</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Analyzed **large**-scale **financial services** and lending datasets using Python, **SQL**, and **Statistics** to identify trends, operational inefficiencies, and credit risk patterns, improving risk visibility by 30% and supporting **data-driven strategies**.
 Engineered **predictive models** and interactive Power BI **dashboards** using **machine learning techniques**, Logistic Regression, and Gradient Boosting to support **lending operations**, monitor agent **performance**, and flag at-risk accounts 1–2 **reporting** cycles earlier.
@@ -989,7 +546,7 @@
 Managed multiple **analytics deliverables** in a **fast-paced environment**, troubleshot **data quality** issues, corrected **reporting** discrepancies, and monitored Model **Risk Management** (MRM) controls while automating **reporting** and **analytics workflows** to reduce manual effort by 35%.</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Evaluated multi-source retail and financial operations datasets using PySpark, **Apache Spark**, and Azure **Databricks** to uncover business trends, solve **complex problems**, and improve forecasting accuracy by 20% through operational analytics.
 Constructed automated data integration and **reporting** pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, improving **data integrity**, strengthening **data quality**, and reducing processing time by 30% across **analytics deliverables**.
@@ -998,24 +555,24 @@
 Managed competing project deadlines, modified **analytics workflows**, and automated operational monitoring through Docker, Azure Kubernetes Service (AKS), and Azure Monitor, reducing manual investigation effort by 35% and strengthening **operational improvement** initiatives.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume chase</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="225" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="5" ht="225" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist skilled in **Python**, **SQL**, **data analysis**, **exploratory data analysis**, statistical modeling, and **machine learning** to transform complex datasets into actionable business insights. Experienced in building scalable data pipelines, automated **ETL** processes, and **AI**-driven analytical solutions that improve data quality and operational efficiency. Proficient in data cleaning, standardization, decomposition, missing **data analysis**, and **data integrity** validation to enhance **data accuracy** and reliability. Strong background in **statistical visualizations**, predictive analytics, and data-driven decision-making, with the ability to communicate findings to technical and non-technical stakeholders. Committed to cross-functional collaboration, continuous process improvement, and delivering measurable business outcomes through reliable, data-driven solutions.</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>Analyzed diverse banking datasets using **Python**, **SQL**, and Pandas, performed **exploratory data analysis** to identify correlations, **missing data**, anomalies, and **data integrity** issues, and improved **data accuracy** by 25% through systematic validation and data cleaning.
 Engineered automated **ETL** pipelines using AWS Glue and Amazon S3 to standardize, decompose, and transform large transaction and customer datasets, reducing manual data preparation efforts by 35% and improving downstream analytical readiness.
@@ -1024,7 +581,7 @@
 Managed analytical documentation and model quality controls using GitHub, Jira, and Agile/Scrum practices, troubleshot and corrected code issues, monitored pipeline performance, participated in cross-functional reviews, and motivated team members to improve documentation and data-driven decision-making.</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Processed large retail datasets using PySpark, NumPy, and **SQL**, conducted **exploratory data analysis** to uncover trends and correlations across sales, inventory, and customer behavior, and improved forecast accuracy by 20% through structured **data analysis** and validation.
 Automated and enhanced data preparation workflows using Azure Data Factory, Azure Data Lake Storage Gen2, and Azure Synapse Analytics, applying **data pre-processing**, standardization, and missing-value handling techniques to reduce processing time by 30%.
@@ -1033,24 +590,24 @@
 Collaborated with senior data scientists and business teams to review analytical approaches, provide analysis support, seek feedback, and troubleshoot code; oriented junior colleagues on **data analysis**, code documentation, data quality control, and statistical modeling, reducing manual investigation efforts by 35%.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume brewer science</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="225" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="6" ht="225" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in machine learning, statistical modeling, and scalable cloud-native applications that improve business performance and customer experience. Experienced in building predictive solutions for **lead scoring**, **churn modeling**, **pricing**, **personalization**, and **fraud detection** using Python, SQL, and advanced analytics. Skilled in feature **engineering**, model training, inference, and monitoring, with a focus on efficient, interpretable, and reliable ML solutions. Delivered measurable improvements in operational efficiency, fraud prevention, and forecasting accuracy through cross-functional collaboration and data-driven decision-making. Adept at communicating actionable insights to technical and non-technical stakeholders in fast-paced environments.</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>Architected scalable machine learning services for **lead scoring**, **churn modeling**, **pricing**, **personalization**, and **fraud detection**, using Python, **scikit-learn**, and SQL to improve customer targeting and reduce Tier-1 banking support workload by 40%.
 Computed customer risk scores and engineered predictive features with **NumPy** and **Pandas**, strengthening credit risk assessment and identifying at-risk accounts 1–2 reporting cycles earlier than traditional batch reporting.
@@ -1059,7 +616,7 @@
 Monitored model performance and presented findings through **Streamlit** dashboards, participated in cross-functional model reviews, troubleshot prediction issues, modified model features, corrected data quality inconsistencies, and motivated teams to improve deployment reliability and measurable business outcomes.</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>Developed demand forecasting and customer churn models using Python, **Scikit-learn**, and SQL, applying statistical techniques to retail transaction and loyalty data to improve forecast accuracy by 20% and support customer retention strategies.
 Engineered scalable data preparation and feature **engineering** workflows with PySpark and Azure Data Factory, consolidating sales, inventory, and customer service data while reducing processing time by 30%.
@@ -1068,24 +625,24 @@
 Collaborated with data infrastructure teams, analysts, and business stakeholders to gather requirements, manage end-to-end data science initiatives, communicate findings to technical and non-technical audiences, and align model outputs with measurable business objectives in a fast-paced environment.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume engine</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="225" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="7" ht="225" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in healthcare data analytics, statistical modeling, and machine learning to transform large-scale datasets into actionable business insights. Experienced in building scalable, cloud-native data science solutions using Python, SQL, **Databricks**, **Spark**, and **Amazon AWS** to improve **healthcare pricing** transparency, affordability, and operational efficiency. Skilled in **clustering**, **NLP**, **outlier detection**, and predictive analytics for identifying patterns, linking records, and improving data quality. Adept at designing production-ready analytical frameworks, optimizing distributed data pipelines, and translating complex findings into clear, data-driven recommendations. Focused on reducing financial risk, improving customer experience, and delivering measurable business outcomes through reliable, scalable data products.</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>Analyzed large-scale financial and healthcare-related datasets using Python, SQL, Pandas, and NumPy, applying statistical analysis and **clustering** techniques to identify pricing patterns, link records across datasets, and generate actionable insights, improving analytical accuracy by 25%.
 Engineered scalable **NLP** and machine learning models using **TensorFlow**, **PyTorch**, and **Keras** to classify unstructured customer and **healthcare pricing** information, improving classification performance by 25% across more than 100,000 monthly records.
@@ -1094,7 +651,7 @@
 Collaborated with product, engineering, and customer-facing teams to define data architecture, document analytical findings, and communicate data-driven recommendations; troubleshot data quality issues, corrected model errors, modified analytical workflows, monitored performance, motivated cross-functional participation, and oriented stakeholders toward scalable delivery practices, improving operational efficiency by 30%.</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Built predictive analytics models using Python, SQL, and Scikit-learn to evaluate complex business datasets, computed statistical measures, and identified customer and pricing trends, improving forecast accuracy by 20% and supporting data-driven planning decisions.
 Processed high-volume transactional and operational datasets using PySpark, **Databricks**, and **Spark**, optimizing distributed transformations and data preparation workflows to reduce processing time by 30% while supporting growth in downstream analytics demand.
@@ -1103,24 +660,24 @@
 Participated in Agile/Scrum delivery, independently managed analytical tasks, presented findings to stakeholders, and documented model assumptions and results; strengthened customer communication and supported **customer pipeline** scalability through careful validation, professional reporting, and recommendations for transparent **healthcare pricing**.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume serif health</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="270" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="8" ht="225" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in **statistical modeling**, predictive analytics, experimentation, and data-driven **product** strategy to improve business performance and **customer outcomes**. Experienced in building scalable analytical applications, cloud-native data solutions, and **measurement frameworks** that optimize **revenue**, **conversion**, **retention**, and **cost efficiency**. Skilled in **Python**, **SQL**, Snowflake, Spark, and AWS to transform large-scale datasets into actionable insights. Applied **machine learning**, **causal inference**, **model validation**, and AI-driven automation to strengthen **decision quality**, **experimentation velocity**, and operational efficiency. Effective cross-functional partner who translates complex analyses into business recommendations while supporting data **governance**, privacy, and measurable **product** impact.</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>Designed and executed complex **statistical modeling**, **experimental design**, **causal inference**, and **Bayesian approaches** using **Python** and **SQL** to evaluate consumer **product initiatives**, define core **KPIs**, and improve **user behavior**, **engagement**, **conversion**, and **retention**, delivering 25% better analytical accuracy.
 Managed **product** **measurement frameworks** and **predictive modeling** for banking customer journeys, computing **revenue**, **monetization**, **cost efficiency**, and customer outcome metrics; quantified **business impact** and informed **roadmap** and **prioritization** decisions that reduced Tier-1 support workload by 40%.
@@ -1129,7 +686,7 @@
 Operationalized reproducible **AI/ML tools** and **model validation** workflows through Snowflake, dbt, Airflow, Spark, and AWS, incorporating **governance**, **GDPR**/**CCPA**-aware **privacy-preserving data modeling**, and documentation practices; mentored 3 **junior data scientists** and **analysts** while reducing model-related false positives by 30%.</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Analyzed large-scale retail transactions, inventory, and loyalty datasets using R, PySpark, and Azure Databricks, applying ARIMA, Prophet, and LSTM models to forecast demand and customer churn, improving forecast accuracy by 20% and supporting merchandising and replenishment initiatives.
 Engineered scalable data integration and transformation workflows using Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating more than 10 operational data sources and reducing data processing time by 30% to support reliable business analytics.
@@ -1139,24 +696,24 @@
 Important: The bullets above incorporate the target job description's keywords, but only retain tools, methods, mentoring responsibilities, compliance experience, and numerical achievements that you can accurately substantiate in an interview. The job description asks for 5+ years of experience, and the listed roles alone may not demonstrate that threshold; do not imply additional experience unless supported by your actual employment history.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume fetch</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="225" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="9" ht="225" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in **predictive analytics**, machine learning, and advanced statistical modeling to solve complex business problems and support strategic decisions. Experienced in building **scalable analytical frameworks**, **automated solutions**, and cloud-native data systems that improve operational efficiency, reduce risk, and enhance customer experience. Skilled in **Python**, **SQL**, **exploratory data analysis**, **A/B testing**, **experimental design**, and **model validation** across **complex datasets**. Proficient in data visualization, **data quality**, **governance standards**, and translating analytical findings into actionable business recommendations. Experienced in cross-functional collaboration, stakeholder communication, and mentoring data scientists on analytical methods and best practices.</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>Architected **predictive analytics** solutions using **Python**, **SQL**, and **machine learning algorithms** to analyze complex banking datasets, identify customer behavior patterns, and reduce Tier-1 support workload by 40%.
 Computed credit risk indicators using **advanced statistical modeling techniques**, conducted **exploratory data analysis** (EDA) and **root cause analysis**, and improved early identification of at-risk accounts by 2 reporting cycles.
@@ -1165,7 +722,7 @@
 Managed **scalable analytical frameworks** and **automated solutions** using AWS SageMaker, MLflow, and Apache Airflow; participated in cross-functional reviews, motivated team members, troubleshot analytical issues, oriented junior data scientists, and established best practices that supported 10+ production models.</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail sales, inventory, and customer datasets using **Python**, PySpark, and ARIMA, identifying demand patterns and improving forecasting accuracy by 20% to support merchandising and replenishment decisions.
 Engineered reliable data preparation workflows with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, validated information across multiple business domains, and reduced data processing time by 30%.
@@ -1174,29 +731,29 @@
 Collaborated with product, engineering, and business teams to structure ambiguous analytical problems, applied **business acumen** to prioritize opportunities, communicated complex insights to stakeholders, and mentored colleagues on analytical methods and reporting best practices.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Walmart</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="270" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="10" ht="315" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Austin , TX</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in machine learning, **deep learning**, and AI-driven solutions that improve user intent understanding, workflow prediction, and **human-computer interaction**. Experienced in building scalable applications and cloud-native solutions using Python, **AWS**, **Azure**, and **GCP** to transform large-scale interaction data into actionable insights. Skilled in **regression**, **classification**, **clustering**, **data mining**, **data cleaning**, **feature engineering**, and **A/B testing** to optimize model performance and user experience. Applied **TensorFlow**, **PyTorch**, and scikit-learn to develop, evaluate, deploy, and monitor predictive models while reducing operational risks and improving efficiency. Strong collaborator who translated complex analytical findings into practical recommendations for engineering, research, and product teams.</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>Architected AI-driven collaboration and conversational applications using Python, **AWS**, and LangChain, analyzing user intent and workflow patterns to improve AI-assisted support efficiency by 40%.
 Engineered predictive models using scikit-learn, **regression**, and **classification** algorithms to identify user needs and behavioral patterns, improving early risk identification by 25%.
@@ -1205,7 +762,7 @@
 Managed production model deployment and monitoring through Docker, Kubernetes, MLflow, and **AWS** SageMaker, troubleshot performance issues, corrected data-quality defects, modified model configurations, and coordinated retraining across 10+ production models.</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>Evaluated **TensorFlow** and **PyTorch** models using **deep learning**, **clustering**, and predictive analytics to identify user behavior patterns and forecast workflow requirements, improving prediction accuracy by 20%.
 Extracted and transformed large datasets using **Azure** Data Factory, **Azure** Databricks, and **Azure** Synapse Analytics, performed **data mining** and **data cleaning**, and reduced processing time by 30%.
@@ -1215,24 +772,24 @@
 Important résumé note: The rewritten content includes the job description’s principal technical keywords and required action verbs. Before submitting, verify that the technologies, responsibilities, and numerical achievements accurately reflect your experience. The job description also requests 5+ years of experience and a relevant bachelor's degree; include these only if they match your actual qualifications.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume future secure ai</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="405" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="11" ht="225" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist skilled in **Python**, **SQL**, **Machine Learning**, **Statistics**, and **Exploratory Data Analysis** (EDA) to transform **structured and unstructured datasets** into actionable business insights. Experienced in building scalable **AI**/ML applications, cloud-native solutions, predictive **analytics**, and **Generative AI** systems that improve operational efficiency and reduce business risks. Proficient in LLMs, **Prompt Engineering**, **Retrieval-Augmented Generation** (**RAG**), **Feature Engineering**, and Responsible **AI** to deliver reliable, business-focused solutions. Adept at developing **Power BI** and **Tableau** **dashboards**, monitoring KPIs, and communicating analytical **findings** through clear **business narratives**. Strong in **analytical problem-solving**, **stakeholder management**, data quality, and cross-functional collaboration to support **data-driven decision-making** and **process optimization**.</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>Analyzed structured and unstructured banking datasets using **Python**, **SQL**, Pandas, NumPy, and **Statistics**, performing EDA, **data preprocessing**, **feature engineering**, **data validation**, and **data quality assessments** to identify **business opportunities** and improve customer support efficiency by 40%.
 Engineered **Generative AI**, **Large Language Model** (**LLM**), **Prompt Engineering**, and **Retrieval-Augmented Generation** (**RAG**) prototypes using GPT-5, Claude, LangChain, and AWS Bedrock, applying **Responsible AI principles** to improve **model reliability** and mitigate **bias** and hallucinations across banking support workflows.
@@ -1241,7 +798,7 @@
 Managed production **AI/ML Solutions** through AWS SageMaker, Kubeflow, MLflow, Docker, and Kubernetes, monitoring model performance and documenting **experiments**, **methodologies**, code, and **technical approaches**; collaborated with **Data Engineers** and cross-functional teams to maintain **scalable datasets**, reduce fraud-detection false positives by 30%, and support Responsible **AI**, **company policies**, **procedures**, and **business directives**.</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Investigated retail sales, inventory, and customer loyalty datasets using PySpark, R, and **Tableau**, applying exploratory analysis, statistical methods, and **Data Modeling Techniques** to identify demand patterns and **business opportunities**, improving forecast accuracy by 20%.
 Constructed scalable data preparation and integration workflows using Azure Data Factory, ADLS Gen2, and Azure Synapse **Analytics**, partnering with **Data Engineers** to validate source data, correct inconsistencies, assess data quality, and reduce processing time by 30%.
@@ -1254,29 +811,29 @@
 Delivery and collaboration: **AI**/ML production deployment, **scalable datasets**, **Data Engineers**, **stakeholder management**, **communication**, **process optimization**, documentation, **experiments**, **technical approaches**, **analytical problem-solving**, **company policies**, **procedures**, and **business directives**.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Optum Health</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="225" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="12" ht="225" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Mountain View , CA</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in state-of-the-art machine learning, deep learning, and scalable AI systems for complex real-world applications. Experienced in building Transformer-based architectures, **generative models**, and synthetic data solutions using Python, **PyTorch**, and **distributed computing** techniques. Skilled in developing **high-performance**, maintainable ML pipelines and deploying complex models in **production environments**. Applied **Imitation Learning**, **Reinforcement Learning**, and simulated-agent workflows to support intelligent decision-making and model optimization. Focused on delivering scalable, reliable, and efficient AI solutions that improve automation, reduce operational risks, and enhance system performance.</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>Architected scalable AI systems using Python, **PyTorch**, and **Transformers**, integrating **state-of-the-art ML models** into banking applications and improving automated customer support efficiency by 40%.
 Engineered **Imitation Learning** and **Reinforcement Learning** workflows for **physical or simulated agents**, evaluating agent behavior across 10+ simulated scenarios to improve task completion and decision-making.
@@ -1285,7 +842,7 @@
 Deployed complex ML systems in **production environments**, writing **high-performance**, **safe**, and maintainable Python and **C++** code while monitoring model reliability and supporting 10+ production model releases.</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>Researched and evaluated **state-of-the-art ML models** in research and production settings, applying TensorFlow and advanced neural architectures to retail forecasting and improving prediction accuracy by 20%.
 Built scalable agent-training experiments using **Reinforcement Learning**, **Imitation Learning**, and physical or simulated-agent environments, assessing 10+ experimental configurations to improve decision consistency.
@@ -1294,24 +851,24 @@
 Evaluated model architectures and documented experimental findings against research standards, aligning work with **NeurIPS**, **ICML**, **CoRL**, **CVPR**, and **AAAI** publication criteria while improving model evaluation coverage by 35%.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Aurora</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="270" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
+    <row r="13" ht="409.6" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in machine learning engineering, autonomous driving, **robotics**, and multimodal AI to build scalable, production-ready solutions. Experienced in reinforcement learning (**RL**), **AI Transformers**, **sensor fusion**, **trajectory planning**, and generative models for intelligent decision-making and **physical actuation**. Skilled in Python, C++, **PyTorch**, **JAX**, model distillation, and **edge deployment** to optimize inference performance under hardware constraints. Proficient in data engineering, active learning, data curation, and simulation-driven validation to identify complex edge cases and improve model reliability. Focused on delivering low-latency AI systems, robust autonomous vehicle behavior, and measurable improvements in operational efficiency and safety.</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>Researched and prototyped reinforcement learning (**RL**), **distillation techniques**, and **AI Transformers** using Python, C++, and **PyTorch** to improve **trajectory planning**, **multi-task learning**, and autonomous decision-making, targeting a 25% improvement in model evaluation performance.
 Architected end-to-end **multimodal models**, Vision-Language-Action (VLA) models, and **generative Diffusion models** integrating **Cameras**, **LiDAR**, and **Radar** through **Sensor Fusion**, **Birds-Eye-View (BEV) frameworks**, and spatial-temporal **representation learning** to translate visual perception and behavioral goals into **physical actuation**.
@@ -1320,7 +877,7 @@
 Managed MLOps, **data curation pipelines**, **active learning workflows**, and model risk management (MRM) using Kubeflow, MLflow, and Kubernetes; participated in QA and validation reviews, monitored regressions, modified model configurations, corrected performance issues, and motivated cross-functional teams to improve release readiness by 25%.</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Analyzed massive, multi-source physical datasets using Python, PySpark, and Apache Spark, applying **data mining architectures**, **data engineering frameworks**, and statistical quality metrics to identify rare driving scenarios, structural corner cases, and **ambiguous** real-world data distributions, improving usable training data quality by 30%.
 Built scalable ingestion and transformation pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics to process spatial-temporal records from **Cameras**, **LiDAR**, and **Radar**, organizing raw sensor logs into structured datasets and reducing processing time by 35%.
@@ -1330,24 +887,24 @@
 Important: The target job description combines autonomous-driving research, embedded **model optimization**, and long-tail data engineering. The responsibilities above incorporate those ATS keywords and retain the original role contexts. However, the newly introduced technologies, tools, and percentage improvements should remain on your résumé only if you can substantiate them in interviews; otherwise, replace them with your verified experience and results.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume atoms</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="270" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
+    <row r="14" ht="270" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in **AI/ML systems**, **generative AI**, **hybrid RAG**, and **production-ready** applications for **scientific and clinical workflows**. Experienced in building scalable, cloud-native solutions using Python, PyTorch, Hugging Face, LangChain, and AWS to improve system reliability, automate complex workflows, and support data-driven decisions. Skilled in **predictive modeling**, **ETL** pipelines, evaluation harnesses, and model fine-tuning, with a focus on grounded outputs, error analysis, **security**, and **human oversight**. Applied AI engineering practices to strengthen model performance, reduce operational risks, and deliver measurable business outcomes. Focused on translating complex requirements into **production-ready** AI tools, reusable architectures, and reliable enterprise solutions.</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>Architected **AI/ML systems** for recurring **scientific and clinical workflows** using Python, GPT-5, Claude, LangChain, and AWS Bedrock, integrating **hybrid RAG** and FAISS to improve domain-context grounding and reduce customer-support workload by 40%.
 Evaluated **AI-assisted prototypes** from AIDE and Systems **Immunology**, debugged **technical and scientific failure modes**, and hardened PyTorch and Hugging Face Transformers applications with prompt engineering, fine-tuning, and evaluation harnesses, improving model classification accuracy by 25% across 100K+ monthly records.
@@ -1356,7 +913,7 @@
 Established CI/CD and Docker deployment workflows with Kubernetes, MLflow, and AWS CloudWatch, promoting internal tools from alpha to beta, monitoring system quality, correcting failures, and defining production-readiness criteria that supported 10+ model deployments with **human oversight** and documented limitations.</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Built predictive models for scientific and clinical analytics using Python, PySpark, TensorFlow, and scikit-learn, improving forecasting accuracy by 20% while evaluating **generative AI**, **agentic systems**, **biological foundation models**, and **translational AI methods** for research-oriented workflows.
 Engineered research data integration using Azure Data Factory, Azure Data Lake Storage Gen2, and Azure Synapse Analytics, processing **multi-omics data** such as **RNA-seq**, **proteomics**, **GWAS**, **spatial transcriptomics**, and **single-cell** datasets while reducing data-processing time by 30%.
@@ -1366,24 +923,24 @@
 Important: The rewrite incorporates the target job description's key ATS terms, including scientific AI, clinical workflows, multi-omics, **biological foundation models**, evaluation, build-vs-buy, and production hardening. Before submitting, verify that the added tools, research modalities, platforms, and numerical results accurately reflect your actual experience. In particular, direct experience with **immunology** research, biological models, and **TypeScript**/**React** should not be claimed unless you can substantiate it in an interview.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume pfizer</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="225" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
+    <row r="15" ht="270" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in **reinforcement learning**, **LLM agents**, **inference optimization**, and scalable **AI infrastructure** for complex engineering workflows. Experienced in building cloud-native **ML systems**, **distributed experimentation** pipelines, reward evaluation frameworks, and automated optimization solutions that improve model **correctness**, **performance**, and **reliability**. Skilled in Python, **PyTorch**, **TensorFlow**, **Kubernetes**, and **reproducible evaluation** systems for model training and deployment. Applied **RLHF**, **reward modeling**, agentic workflows, and **benchmark-driven development** to streamline experimentation, reduce operational overhead, and enhance system efficiency. Collaborated with research, engineering, and infrastructure teams to translate experimental results into measurable model and business improvements.</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>Architected scalable **LLM agents** and **reinforcement learning** workflows using Python, **PyTorch**, LangChain, and **Ray**, integrating **RLHF**, **GRPO**, **preference optimization**, **reward shaping**, and **post-training systems** to improve engineering task automation by 35%.
 Engineered distributed inference and **tool-use systems** with **Kubernetes**, **CUDA**, and AWS, optimizing **batching**, **sampling**, **caching**, **latency**, **throughput**, **model serving**, and **reliability** to reduce inference overhead by 30%.
@@ -1392,7 +949,7 @@
 Managed MLflow-based **experiment tracking** and distributed **job orchestration** across **data pipelines**, **workflow engines**, and **benchmark harnesses**; troubleshot failures, monitored **observability** and **reliability** metrics, corrected evaluation defects, modified **optimization workflows**, motivated cross-functional contributors, oriented engineering teams to reproducible run practices, and participated in shipping 10+ production **ML systems**.</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Developed Python-based post-training and **optimization workflows** using **JAX**, **TensorFlow**, and Scikit-learn, evaluating **reward modeling**, **preference optimization**, **candidate generation**, **scoring**, and **long-horizon** tasks to improve experimental success rates by 22%.
 Built distributed **data pipelines** and **job orchestration** using Apache Airflow, **Slurm**, and Apache Spark, standardizing datasets, evaluation definitions, **run logs**, **leaderboards**, **failure taxonomies**, and **data collection** to reduce experiment preparation time by 30%.
@@ -1401,24 +958,24 @@
 Collaborated with **AI researchers** and engineering teams on **RL infrastructure**, **inference services**, **evaluation platforms**, and **hardware/software co-design**, publishing experiment findings and delivering shipped system improvements through reproducible **dashboards**, **validation systems**, and **performance**-focused **optimization workflows** that increased pipeline **reliability** by 20%.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Amd</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="225" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
+    <row r="16" ht="225" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in **Python**, **TypeScript**, AI-driven automation, and scalable application development, delivering practical solutions that improve operational efficiency and business performance. Experienced in building AI **agent workflows**, integrating APIs, and automating complex business processes using **low-code/no-code** platforms and intelligent tools. Skilled in **data extraction**, validation, transformation, workflow optimization, and AI output evaluation to improve reporting accuracy and decision-making. Applied cloud-native technologies, cross-functional collaboration, and software development best practices to deliver reliable, maintainable solutions. Committed to responsible AI, architectural standards, continuous improvement, and compliance with AI governance policies.</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>Collaborated with Business Systems Analysts and cross-functional teams to identify operational bottlenecks and automate banking workflows using **Python**, **TypeScript**, and **Microsoft Power Platform**, reducing manual customer support workloads by 40%.
 Configured **Pega** **low-code/no-code** workflows and **API integrations** to connect business applications, streamline **data extraction** and transformation, and improve reporting accuracy by 30%.
@@ -1427,7 +984,7 @@
 Monitored automation performance metrics, troubleshot workflow failures, corrected **data validation** issues, and promoted compliance with the **AI Acceptable Use Policy**, motivating teams to adopt responsible AI practices and increasing process efficiency by 35%.</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail business requirements and participated in cross-functional planning sessions to translate operational challenges into practical automation solutions, improving demand planning efficiency by 20% through **Python** and PySpark.
 Engineered automated **data extraction** and validation pipelines using Azure Data Factory and Azure Synapse Analytics, integrating transaction, inventory, and customer service data while reducing processing time by 30%.
@@ -1436,29 +993,29 @@
 Managed solution testing, troubleshooting, and release coordination through GitHub, Jira, and Agile/Scrum practices; oriented team members on automation standards, shared knowledge of AI coding methods, and supported continuous improvement across business systems.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume meketa</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="270" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+    <row r="17" ht="225" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in Python, distributed systems, AI infrastructure automation, and machine learning for scalable, cloud-native applications. Experienced in building intelligent automation workflows, **predictive failure detection** systems, and infrastructure monitoring solutions that improve reliability and operational efficiency. Skilled in Kubernetes, Linux, Terraform, Ansible, and AI agents for automated deployment, incident triage, root-cause analysis, and **autonomous remediation**. Applied predictive analytics, distributed computing, and hardware health monitoring concepts to optimize resource utilization, minimize operational risks, and improve system performance. Focused on building resilient infrastructure platforms that support large-scale AI training, inference workloads, and reliable GPU operations.</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>Architected automated infrastructure workflows using Python, **Rust**, and Linux to provision, validate, deploy, upgrade, and retire GPU clusters, reducing manual operational effort by 40% across recurring deployment tasks.
 Built **AI Infrastructure Agents** with LangChain, RAG, and AWS Bedrock to automate incident triage, root-cause analysis, and **autonomous remediation**, reducing Tier-1 support workload by 40%.
@@ -1467,7 +1024,7 @@
 Automated **predictive failure detection** and hardware health monitoring for firmware, thermals, storage, and accelerator performance using PyTorch, XGBoost, and MLflow, reducing false-positive alerts by 30% and supporting proactive infrastructure repair.</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Developed distributed backend services using Python, Go, and Apache Spark to analyze large-scale AI training and inference workloads, improving processing efficiency by 30% and supporting reliable infrastructure operations.
 Engineered automated data and infrastructure provisioning workflows with Apache Airflow, Terraform, and Ansible, managing resource configuration, lifecycle operations, and repeatable deployment procedures to reduce manual processing effort by 35%.
@@ -1477,24 +1034,24 @@
 Important: The job description emphasizes infrastructure engineering rather than conventional data science. These versions incorporate its keywords, but retain only technologies and accomplishments you can substantiate in an interview. **Rust**, Go, CUDA, NCCL, InfiniBand/RoCE, **NVLink/NVSwitch**, Terraform, Ansible, and GPU fleet operations should not be presented as hands-on experience unless you can credibly explain your work with them.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume together ai</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="225" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
+    <row r="18" ht="225" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in AI-powered applications, **large language models** (LLMs), agentic AI, and enterprise software integration, delivering scalable, secure, and cloud-native solutions. Experienced in Microsoft Azure AI Services, **retrieval-augmented generation** (RAG), **semantic search**, AI agents, and intelligent automation to improve operational efficiency and customer experience. Skilled in application architecture, API development, secure data handling, and AI-assisted software engineering to strengthen code quality and accelerate delivery. Applied responsible AI, data governance, testing, and model validation practices to reduce risks and support reliable enterprise deployments. Collaborated with cross-functional teams to translate business requirements into maintainable solutions that delivered measurable business value.</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>Architected scalable enterprise AI applications using C#, .NET Core, ASP.NET Core, and Web Application Architecture patterns, integrating **Microsoft Copilot Studio**, Microsoft 365, and Power Platform to automate business workflows and reduce manual support workload by 40%.
 Evaluated and integrated **Azure OpenAI Services**, **large language models** (LLMs), prompt engineering, **retrieval-augmented generation** (RAG), **RAG patterns**, and **semantic search** with **Azure AI Search**, **Pinecone**, and **Qdrant**, improving enterprise knowledge retrieval and response relevance by 30%.
@@ -1503,7 +1060,7 @@
 Managed unit testing, integration testing, AI component validation, and prompt regression testing before QA and production releases; troubleshot defects, corrected code issues, reviewed design documentation, and enforced responsible AI, bias mitigation, transparency, confidentiality, and data governance, reducing production issues by 30%.</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail business requirements and designed scalable application solutions using .NET Framework, C#, and ASP.NET, applying established design patterns and coding standards to improve workflow efficiency by 25% and support multiple concurrent business projects.
 Built and consumed REST APIs to connect business applications with AI services, using Python, SQL Server, and Azure OpenAI Service to integrate intelligent automation and language-model capabilities, reducing manual data processing by 30%.
@@ -1512,24 +1069,24 @@
 Monitored application performance and resolved technical issues through structured troubleshooting, root-cause analysis, and secure coding practices; motivated team participation, oriented stakeholders to AI capabilities and limitations, managed competing priorities, and maintained confidential client data while supporting cross-functional delivery in a fast-paced environment, reducing investigation effort by 35%.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume ropes and gray</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="225" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
+    <row r="19" ht="225" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in applied AI, **machine learning**, generative AI, and scientific data analytics to solve complex business and **operational challenges**. Experienced in designing scalable AI solutions, cloud-native applications, predictive models, and intelligent workflows that improve decision-making, **quality**, and efficiency. Skilled in **Python**, R, **natural language processing**, **computer vision**, **retrieval-augmented generation** (RAG), and **agentic AI** for building reliable, explainable, and scalable systems. Focused on **responsible AI**, model validation, **data quality**, **governance**, and **performance monitoring** to deliver measurable **business value**. Adept at cross-functional collaboration, translating **technical outputs** into actionable insights, and advancing AI **adoption** while preserving **human judgment**.</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>Led 5 cross-functional applied AI initiatives by defining project scope, milestones, resources, risks, and **measurable success criteria**; coordinated **scientific subject matter experts**, business stakeholders, and **technology partners** to align AI solutions with operational priorities and improve delivery efficiency by 30%.
 Designed and prototyped **machine learning**, **supervised and unsupervised learning**, **deep learning**, **reinforcement learning**, and **hybrid modeling** solutions using **Python**, R, and **comparable tools**; evaluated **predictive analytics**, **optimization**, and AI-enabled digital twin approaches to improve **model performance**, **reliability**, and **scientific validity** by 25%.
@@ -1538,7 +1095,7 @@
 Established AI **adoption** measures across 10+ production models, monitored scientific and business **outcomes**, and participated in roadmap **prioritization**, **stakeholder communication**, and lessons-learned reviews; motivated teams to adopt **reusable practices** and **responsible AI** solutions that improved **quality**, cycle time, and operational efficiency by 25%.</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Translated complex scientific and **operational challenges** into **AI use cases** by partnering with **process development**, **analytical**, **manufacturing**, and **business teams**; defined **user requirements**, **data needs**, **expected outcomes**, and **measurable success criteria**, improving forecasting accuracy by 20% and supporting evidence-based decisions.
 Built scalable scientific **data platforms** and ETL/ELT pipelines using PySpark, Apache Spark, Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics; integrated fragmented data sources, assessed **data readiness** and **technical feasibility**, and reduced data processing time by 30%.
@@ -1547,29 +1104,29 @@
 Coordinated **internal data science teams**, **technology partners**, **academic collaborators**, and **vendors** to evaluate **external developments** and **best practices**; oriented stakeholders on AI **adoption**, managed project dependencies, and contributed to the **Cell &amp; Gene Therapy** **AI roadmap** through **prioritization**, reusable solutions, and measurable **quality** and efficiency **outcomes**, targeting **biotechnology**, pharmaceutical, and **biologics development** needs.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Johnsin</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="270" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+    <row r="20" ht="270" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>New York , NY</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in AI-powered applications, LLM workflows, and scalable, cloud-native solutions that improve business efficiency and customer outcomes. Experienced in building production-ready **Python** applications, **RAG** pipelines, AI **agents**, **prompt orchestration**, and automated data workflows for financial services. Skilled in integrating enterprise data, predictive models, and secure AI solutions to support **credit** risk, **fixed income**, **actuarial**, and Asset-Liability Management (**ALM**) use cases. Focused on translating business challenges into practical AI products, reducing manual effort, strengthening risk management, and delivering measurable business impact through cross-functional collaboration.</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>Architected and shipped production-ready **Python** applications using **RAG**, AI **agents**, and **prompt orchestration** with LangChain and AWS Bedrock, automating banking and insurance support workflows and reducing Tier-1 workload by 40%.
 Engineered financial analytics workflows integrating **credit** data, portfolio indicators, and predictive models through SQL, Power BI, and AWS SageMaker, identifying at-risk accounts 1–2 reporting cycles earlier and improving decision-making for finance stakeholders.
@@ -1578,7 +1135,7 @@
 Managed production deployment and lifecycle monitoring through MLflow, Docker, Kubernetes, and CI/CD/CT pipelines, supporting 10+ production models while strengthening security, compliance, model governance, and collaboration between engineering and business teams.</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>Built demand forecasting and customer behavior models using **Python**, PySpark, and Azure Databricks, applying ARIMA, LSTM, and Prophet to improve forecast accuracy by 20% and support planning across finance and operations.
 Engineered scalable data pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transactions, operational records, and financial datasets while reducing data processing time by 30%.
@@ -1588,24 +1145,24 @@
 Important: The target job description emphasizes hands-on production engineering and insurance-domain collaboration. The rewritten bullets incorporate its requested keywords, including **Python**, **RAG**, **agents**, **prompt orchestration**, **credit**, **fixed income**, **actuarial**, and **ALM**. Before submitting, verify that the insurance-domain work, tools, and quantified achievements accurately reflect your actual experience.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume kkr insurance</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="315" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
+    <row r="21" ht="225" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>**ChatGPT** said: Data Scientist specializing in AI agents, conversational assistants, workflow automation, and scalable AI applications that improve operational efficiency and user experience. Experienced in building solutions with **Microsoft 365 Copilot**, **Copilot Studio**, **ChatGPT**, **Claude**, **Python**, **SQL**, **APIs**, and **low-code platforms** to streamline business processes and support informed decision-making. Skilled in prompt engineering, **knowledge bases**, solution testing, API integrations, and AI evaluation to improve **accuracy**, reliability, and usability. Committed to **responsible AI**, **data governance**, **privacy**, **security**, **intellectual property** protection, and **human oversight** throughout the solution lifecycle. Effective at translating business needs into practical AI tools, creating reusable resources, training users, and delivering measurable business outcomes.</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>Architected and deployed AI agents and conversational assistants using **Microsoft 365 Copilot**, **Copilot Studio**, **ChatGPT**, **Claude**, and AWS Bedrock, integrating LangChain, **APIs**, and **connectors** to automate banking support workflows and reduce Tier-1 agent workload by 40%.
 Translated staff and business requirements into production-ready automation solutions using Power Automate, Zapier, Make, **Python**, and **SQL**, connecting forms, documents, and business systems to reduce manual processing time by 35%.
@@ -1614,7 +1171,7 @@
 Managed project plans, priorities, and progress updates while monitoring **responsible AI**, **privacy**, **security**, **data governance**, **intellectual property**, and **human oversight** requirements, participating in governance reviews and documenting safeguards for 10+ production AI solutions.</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Developed AI-powered retail and insurance workflow prototypes using **JavaScript**, **ChatGPT**, **Claude**, and **low-code platforms**, gathering requirements from business stakeholders and converting operational needs into practical assistants that improved task completion efficiency by 30%.
 Integrated business applications, customer records, and digital documents through REST **APIs**, webhooks, **connectors**, and **JSON**, managed information flows across multiple systems, and reduced repetitive data-entry effort by 25%.
@@ -1625,24 +1182,24 @@
 Important: The job description lists several tools and practices as preferred or helpful rather than mandatory. Only retain technologies and achievements you can explain accurately in an interview. The original experience details support some AI and automation achievements, but they do not establish hands-on experience with every newly introduced platform.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume independent insurance</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="225" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
+    <row r="22" ht="270" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in **AI/LLM Security**, **Web Application &amp; API Security**, security analytics, and scalable enterprise applications across financial services and banking. Experienced in analyzing suspicious traffic, supporting **WAF Policy Tuning &amp; False Positive Analysis**, and applying **OWASP Top 10** principles to strengthen application security. Skilled in **Incident Response**, threat analysis, root-cause analysis, and AI-driven security monitoring to reduce risks and improve operational efficiency. Adept at supporting **Akamai WAF**, **Akamai Kona Site Defender**, **Akamai Bot Manager**, **Akamai API Security**, and DDoS Protection initiatives, alongside **enterprise-scale application migration** and security architecture consulting.</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>Managed **Akamai WAF** onboarding and **enterprise-scale application migration** activities for banking applications, transitioning security policies from monitor/alert mode to deny/mitigation mode and strengthening protection across 20+ application endpoints.
 Configured and tuned **Akamai Kona Site Defender** policies using **WAF Policy Tuning &amp; False Positive Analysis**, applying **OWASP Top 10** principles to correct rule conflicts and reduce unnecessary security alerts by 30%.
@@ -1651,7 +1208,7 @@
 Partnered with application owners, infrastructure teams, security leadership, and Akamai engineering teams on **Security Architecture &amp; Consulting**, DNS, load balancer, proxy, firewall, and traffic cutover activities; prepared security dashboards, executive reports, quarterly policy reviews, and upgrade updates to improve migration readiness and security visibility.</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Analyzed enterprise application traffic and financial transaction patterns using Python, SQL, and Scikit-learn, computing risk indicators and suspicious activity metrics that improved security reporting accuracy by 20% for financial services stakeholders.
 Supported web application and API security assessments by reviewing **OWASP Top 10** risks, evaluating access patterns, and recommending remediation actions that strengthened application controls across 15+ business workflows.
@@ -1660,24 +1217,24 @@
 Motivated and oriented cross-functional teams on security reporting standards, managed quarterly control reviews, monitored remediation progress, and prepared risk dashboards and technology roadmap updates that improved stakeholder visibility into application vulnerabilities and mitigation status by 25%.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume imr soft</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="405" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
+    <row r="23" ht="405" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in machine learning, statistical modeling, **fraud** detection, and **fintech** analytics to solve complex, high-impact business problems. Experienced in building scalable, production-ready DS/ML solutions that support real-time decision-making, **risk operations**, and customer-focused **product development**. Skilled in Python, SQL, feature engineering, data integration, and end-to-end model development, from **planning** and success metrics to deployment and performance monitoring. Delivered measurable improvements in **fraud** detection, forecasting accuracy, operational efficiency, and **data quality** through iterative experimentation and data-driven strategies. Adept at collaborating with engineering and business stakeholders to communicate analytical outcomes and translate insights into actionable decisions.</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>Architected **fintech** conversational AI solutions using Python, GPT-5, Claude, LangChain, AWS Bedrock, RAG, FAISS, and Pinecone, applying iterative development and new data source integration to reduce Tier-1 support workload by 40% and improve customer decision support.
 Engineered credit risk analytics using SQL, Power BI, AWS SageMaker, Logistic Regression, and Gradient Boosting, defining success criteria, computing risk metrics, and delivering production-ready insights that identified at-risk accounts 1–2 reporting cycles earlier.
@@ -1686,7 +1243,7 @@
 Managed end-to-end MLOps, Kubeflow, Apache Airflow, MLflow, Docker, Kubernetes, CI/CD/CT, and Model Risk Management (MRM) workflows for 10+ production models; wrote **production code** and **tests**, troubleshot deployment issues, corrected **data quality** problems, monitored model performance, and communicated progress to senior management and stakeholders.</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Researched and refined retail demand forecasting and customer churn solutions using Python, PySpark, Azure Databricks, ARIMA, LSTM, and Prophet, improving forecast accuracy by 20% and informing **sales efforts**, **marketing** priorities, inventory **planning**, and customer retention strategies.
 Integrated transaction, inventory, store operations, and customer service data through Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, reducing data processing time by 30% while coordinating **data acquisition**, access requirements, validation, and quality checks with engineering and business teams.
@@ -1699,29 +1256,29 @@
 Execution: Production deployment, monitoring, troubleshooting, correction, **planning**, solution scoping, model evaluation, high-impact problem solving, Agile/Scrum.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume sentilink</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="225" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
+    <row r="24" ht="225" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said:</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in ML infrastructure, scalable AI applications, and production-ready training and inference systems across cloud and on-premise environments. Experienced in **Python**, distributed computing, model serving, GPU optimization, and automated ML pipelines to improve latency, throughput, and operational efficiency. Skilled in **AWS**, **GCP**, **Kubernetes**, and **Docker** for reliable, secure, and scalable deployments. Applied reinforcement learning (RL) concepts, experiment tracking, model versioning, and **performance profiling** to support evolving AI models. Focused on enterprise-grade security, **SOC 2** compliance, **data residency**, and cost-effective AI solutions that reduce risk and improve business outcomes.</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>Architected scalable AI training and inference infrastructure using **Python**, **Rust**, **C++**, and **Go**, integrating **vLLM**, **TensorRT**, **Triton**, and **ONNX Runtime** to optimize model serving and reduce inference latency by 35%.
 Optimized cloud and on-premise deployments across **AWS**, **GCP**, and **GPU computing** environments, applying **distributed systems** principles and **performance profiling** to improve throughput by 30% while managing infrastructure costs.
@@ -1730,24 +1287,24 @@
 Collaborated with research scientists to productionize new algorithms through **GGUF quantization**, **TensorRT-LLM**, **CoreML**, and **QNN**, evaluating **NVIDIA DGX** infrastructure and enforcing **SOC 2**, **data residency**, and enterprise security requirements.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Pokee</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="225" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
+    <row r="25" ht="270" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in AI **automation**, **agentic workflows**, and scalable, cloud-native applications that streamline complex business processes and improve operational efficiency. Experienced in designing production-ready AI solutions, integrating structured and unstructured data, and building reliable **APIs**, **internal tools**, and intelligent **workflow orchestration** systems. Skilled in Python, machine learning, LLMs, **human-in-the-loop** systems, and automated evaluation to improve accuracy, reduce costs, and accelerate decision-making. Focused on measurable business outcomes through **performance monitoring**, **regression testing**, continuous improvement, and responsible **AI adoption**. Adept at translating business requirements into maintainable solutions while strengthening team productivity, operational reliability, and **institutional knowledge**.</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>Architected end-to-end **agentic workflows** using Python, LangChain, LangGraph, and AWS Bedrock, connecting **APIs**, MCP servers, and **AI tools** to automate banking support processes and reduce manual agent workload by 40%.
 Engineered production-ready deterministic applications and CLI utilities for credit-risk operations, integrating SQL, AWS SageMaker, and **data warehouses** to process account records and surface high-risk cases 2 reporting cycles earlier.
@@ -1756,7 +1313,7 @@
 Monitored production **KPIs** through MLflow, Kubeflow, and Airflow, computed **workflow** performance metrics, and modified deployment pipelines using Docker, Kubernetes, and CI/CD/CT; documented operational **playbooks**, motivated **AI adoption**, and oriented team members toward reusable **automation** practices.</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Analyzed structured and unstructured retail data using Python, PySpark, and Azure Databricks to map business workflows, identify processing bottlenecks, and deploy ARIMA, LSTM, and Prophet forecasting models that improved demand prediction accuracy by 20%.
 Streamlined ETL/ELT pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transaction, inventory, and customer-service records while reducing data processing time by 30%.
@@ -1765,24 +1322,24 @@
 Collaborated with business and engineering teams through Agile/Scrum and Jira, troubleshot pipeline failures, corrected data inconsistencies, and maintained Git-based code reviews and **regression testing** practices to improve solution reliability and support continuous process improvement.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume cookunity</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="315" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
+    <row r="26" ht="270" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in LLM applications, agentic AI, **prompt engineering**, and enterprise AI solutions across financial services and regulated environments. Experienced in building scalable, cloud-native applications using **AWS**, **GCP**, and **Azure**, translating customer requirements into production-ready technical solutions. Skilled in **Claude Code**, **Claude for Work**, **Cowork**, **agent design**, **evaluation frameworks**, and AI-powered developer productivity workflows. Proficient in **CI/CD**, **SDLC practices**, deployment strategies, and MLOps to improve software delivery, reliability, and operational efficiency. Strong collaborator across engineering teams and business stakeholders, driving AI adoption, reducing operational risks, and delivering measurable business outcomes.</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>Led customer-facing AI workshops and technical demonstrations using **Claude Code**, **Claude for Work**, **Cowork**, and the Claude **developer platform**, guiding engineering and business teams from initial experimentation to production adoption and reducing Tier-1 banking support workload by 40%.
 Transformed customer discovery findings into technical roadmaps by assessing engineering toolchains, business workflows, organizational needs, risks, milestones, and dependencies, using Python, SQL, and **AWS** to prioritize credit-risk solutions and identify at-risk accounts 1–2 reporting cycles earlier.
@@ -1791,7 +1348,7 @@
 Managed **CI/CD** and **SDLC practices** across Docker, Kubernetes, MLflow, and **AWS** **deployment configurations**, codifying reusable implementation patterns, troubleshooting release issues, monitoring production models, correcting defects, and strengthening Model Risk Management (MRM) while supporting 10+ production models.</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>Assessed enterprise engineering processes and customer requirements in a consulting environment, participated in technical discovery sessions, and translated business needs into scalable AI implementation plans using Python, PySpark, and **Azure** Databricks, improving retail demand-forecast accuracy by 20%.
 Engineered cloud-native data integration workflows with **Azure** Data Factory, ADLS Gen2, and **Azure** Synapse Analytics, consolidating transactions, inventory, and customer-service data into reliable analytical datasets and reducing processing time by 30%.
@@ -1802,29 +1359,29 @@
 Important: Before submitting, verify that the named Claude products, **MCP servers**, **GCP** Vertex AI, and the specific customer-facing workshop and software-development activities accurately reflect your experience. Keywords can be included for ATS alignment, but the résumé should not claim hands-on experience you cannot substantiate in an interview.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume forgd</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="270" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+    <row r="27" ht="225" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>New York , NY</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in scientific machine learning, **physics-based modeling**, and scalable **engineering applications** that accelerate simulation-driven design and improve computational efficiency. Experienced in building **surrogate models**, automating data pipelines, and applying Python, PyTorch, and **numerical methods** to complex modeling problems. Skilled in integrating **physical constraints**, **engineering knowledge**, and **hardware measurements** into model development, validation, and **optimization workflows**. Focused on delivering reliable, reproducible, cloud-native solutions that reduce simulation time, improve prediction accuracy, and support data-driven engineering decisions. Knowledgeable in **active learning**, **neural operators**, and **physics-informed machine learning** for advanced electrical, thermal, and electromagnetic simulation applications.</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>Architected automated workflows for **electrical simulations**, **thermal simulations**, and **electromagnetic simulations** using Python and PyTorch, reducing repetitive modeling tasks by 35% and accelerating engineering design evaluations.
 Engineered **surrogate models** using **JAX** and **neural operators** to approximate computational solver outputs, improving **inference** speed by 45% while maintaining reliable predictions across complex simulation scenarios.
@@ -1833,7 +1390,7 @@
 Managed **active learning**, **optimization workflows**, and **reproducible pipelines** for data generation, model training, evaluation, and deployment, prioritizing promising designs and reducing unnecessary simulation runs by 30%.</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Computed engineering performance estimates using Python, **numerical methods**, and **applied mathematics**, applying machine learning to **scientific applications** and improving predictive accuracy by 20% across complex modeling tasks.
 Automated simulation tools and **computational solvers** through Apache Airflow and Azure Data Factory, streamlining data preparation and reducing processing time by 30% across large-scale analytical workflows.
@@ -1843,24 +1400,24 @@
 Important before submitting: The job description lists a degree in physics, **applied mathematics**, **computer science**, **electrical engineering**, or a related field, with a **PhD** preferred for certain research areas. Include **PhD** only if you hold one, and retain the electrical, thermal, electromagnetic simulation, **JAX**, and physics-informed modeling claims only if you can substantiate them in an interview. The percentages above should also be verified against your actual work.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume root access</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="225" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
+    <row r="28" ht="225" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in enterprise AI platforms, generative AI, and responsible AI governance, with experience building scalable, cloud-native solutions for financial and enterprise applications. Skilled in AI platform evaluation, **security controls**, **data protection**, **access management**, and model risk assessment to support secure and compliant AI adoption. Experienced in assessing LLM capabilities, **vendor ecosystems**, **AI service operations**, and deployment strategies while reducing operational risks and improving service efficiency. Adept at translating **technical requirements** into practical **governance controls**, monitoring frameworks, and enterprise AI solutions. Effective in **cross-functional collaboration**, stakeholder communication, and aligning AI innovation with business priorities, **privacy commitments**, and **regulatory requirements**.</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>Architected enterprise AI service strategies using OpenAI, Anthropic Claude, Google Gemini, Azure AI, and AWS Bedrock, evaluating **model capabilities**, **AI platform vendors**, deployment options, and **technical roadmaps** to support secure enterprise adoption and reduce Tier-1 support workload by 40%.
 Managed AI platform governance and **configuration management** through **administrative consoles**, **enterprise identity integration**, **user provisioning**, **access controls**, **data protection policies**, **DLP integration**, and **audit logging**, strengthening **governance controls** across 5 core **security** areas.
@@ -1869,7 +1426,7 @@
 Established **AI service operations** and **lifecycle management** using Kubeflow, MLflow, Docker, and Kubernetes, monitoring **usage patterns**, **adoption metrics**, **platform health**, **model releases**, and **AI usage monitoring** while coordinating testing, validation, **model upgrade procedures**, and **change management** for 10+ production models.</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>Evaluated enterprise AI service patterns and institutional needs using Python, PySpark, and Azure Databricks, translating **academic**, **research**, and **administrative** requirements into technical recommendations for scalable AI adoption and improving forecasting accuracy by 20%.
 Computed AI usage and governance metrics through SQL, Power BI, and Azure Synapse Analytics, monitoring adoption trends, **platform health**, service tiers, lifecycle expectations, and **operational standards** while communicating findings to **senior leaders** and improving reporting efficiency by 25%.
@@ -1878,29 +1435,29 @@
 Motivated and oriented cross-functional stakeholders across **research**, **academic**, **administrative**, technology, **security**, **privacy**, legal, and governance teams, delivering **enterprise-wide architectural guidance** and clear written and verbal briefings on **responsible AI requirements**, **regulatory requirements**, **model behavior**, **third-party integrations**, testing and validation, and risk **mitigations**, reducing manual investigation effort by 35%.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Northwestern university</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="270" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+    <row r="29" ht="270" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Dallas , TX</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in building AI-powered applications, scalable **backend services**, and cloud-native solutions that improve business productivity and customer experience. Experienced in Python, **TypeScript**, **React**, RESTful **APIs**, **LLM APIs**, and AI frameworks to develop intelligent copilots, automate workflows, and integrate enterprise systems. Skilled in software testing, debugging, CI/CD, cloud deployment, and application **monitoring** to improve reliability, security, and maintainability. Applied LangChain, **Claude**, Gemini, and generative AI to deliver conversational assistants and automation solutions for finance and enterprise workflows. Focused on writing quality code, collaborating with cross-functional teams, and delivering measurable business outcomes.</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>Architected **React**, **TypeScript**, and Next.js interfaces for internal AI agents and copilots, integrating **Claude**, OpenAI **APIs**, and Gemini to streamline banking workflows and reduce Tier-1 support workload by 40%.
 Engineered Python and FastAPI **backend services**, Node.js integrations, and Bash **automation scripts** to process financial data, orchestrate workflows, and connect enterprise applications through RESTful **APIs**, improving processing efficiency by 30%.
@@ -1909,7 +1466,7 @@
 Managed **Git** version control, CI/CD workflows, cloud **deployment practices**, and AWS application operations; added **logging**, **monitoring**, **error handling**, **security practices**, and **access control**, while maintaining technical documentation and communicating progress and blockers to engineering and business stakeholders.</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>Developed enterprise web application components using Python, Java, and FastAPI to support retail forecasting and employee-facing business tools, improving forecast accuracy by 20% through automated data-driven workflows.
 Built and maintained data processing services with PySpark, Azure Data Factory, and Azure Synapse Analytics, integrating transaction, inventory, and customer data through RESTful **APIs** and database connections while reducing processing time by 30%.
@@ -1919,24 +1476,24 @@
 Important: The responsibilities above incorporate the job description's technologies and keywords for ATS alignment. Only retain tools, platforms, and achievements you can accurately discuss in an interview. In particular, verify hands-on experience with **React**, **TypeScript**, Next.js, Node.js, OpenAI, Glean, Workato, Boomi, **Cursor**, **GitHub Copilot**, and **Codex** before submitting.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume coreweave</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="270" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
+    <row r="30" ht="225" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in **Python**, **SQL**, machine learning, **data science**, and **solutions engineering**, delivering scalable applications and customer-focused technical solutions. Experienced in translating complex operational challenges into **proofs of concept**, **bespoke prototypes**, and **working demos** that support technical sales and business decisions. Skilled in exploring **client datasets**, quantifying **business impact**, and communicating **machine learning concepts** to **engineers**, **client stakeholders**, and **business leaders**. Experienced in supporting **product walkthroughs**, **trials**, **pilots**, **rollouts**, and cloud-native deployments across financial services and **retail** environments. Recognized for a **build-it-yourself attitude**, rapid learning of **unfamiliar tools**, and delivering measurable improvements in efficiency, risk reduction, and customer experience.</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>Engaged **client stakeholders** to identify **data-heavy operational problems** in banking, translated business requirements for **engineers** and **business leaders**, and delivered tailored **product walkthroughs** that demonstrated **machine learning concepts** and reduced Tier-1 support workload by 40%.
 Built bespoke **proofs of concept**, **working demos**, and technical prototypes using **Python**, **SQL**, LangChain, and AWS Bedrock, aligning proposed solutions with the **sales process** and helping technical teams demonstrate measurable business value.
@@ -1945,7 +1502,7 @@
 Monitored production deployments through Docker, Kubernetes, MLflow, and CI/CD/CT pipelines, participated in technical reviews, motivated cross-functional teams to resolve deployment challenges, and strengthened Model Risk Management (MRM) practices while supporting scalable **rollouts** of 10+ machine learning models.</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Collaborated with **client stakeholders** across **retail** operations to investigate forecasting, inventory, and customer-retention challenges, oriented **mixed audiences** toward data-driven recommendations, and improved demand-forecast accuracy by 20% using **Python**, PySpark, and Azure Databricks.
 Designed and presented client-specific **proofs of concept** using **SQL**, ARIMA, LSTM, and Prophet, demonstrated practical applications of machine learning to merchandising and replenishment teams, and supported technical product discussions with measurable operational outcomes.
@@ -1955,24 +1512,24 @@
 Important: The job description also requests an **undergraduate degree** in a **quantitative or scientific discipline** and experience with a **machine learning platform vendor**, an **early-stage startup**, or a **leading management consultancy**. Include your degree and relevant experience in your résumé's education and employment sections only if accurate. The bullets above incorporate the target keywords, but claims about specific client-facing duties, product sales, and **rollouts** should be retained only where they reflect work you actually performed.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume raydar</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="225" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
+    <row r="31" ht="225" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in Python, **PyTorch**, generative AI, and production-ready machine learning systems for scalable model integration and deployment. Experienced in adapting image and video **generation models**, building provider API integrations, and optimizing **inference pipelines** for reliable performance. Skilled in **Hugging Face**, **Diffusers**, **model-serving frameworks**, and cloud-native solutions that streamline model launches and improve operational efficiency. Proven ability to troubleshoot model behavior, automate deployment workflows, and coordinate cross-functional teams to deliver production systems. Focused on reducing integration time, improving reliability, and accelerating the delivery of AI-powered applications.</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>Prototyped and deployed image and video **generation models** using Python, **PyTorch**, **Hugging Face**, and **Diffusers**, adapting **model code** and **inference pipelines** to validate outputs and reduce initial model setup time by 35%.
 Built reusable **provider APIs**, FastAPI integrations, and Modelverse connectors for multi-model serving, enabling product engineers to launch 8+ generative AI models with consistent parameters, examples, and developer instructions.
@@ -1981,7 +1538,7 @@
 Managed end-to-end integration testing for **generation models**, validating output quality, API error handling, serving configurations, and documented limitations; participated in production releases and monitored 10+ deployed models to improve launch readiness and operational reliability.</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>Adapted unfamiliar Python and **PyTorch** **model code** for generative AI prototypes, evaluated model weights and sample outputs, and modified inference configurations to shorten proof-of-concept development time by 25%.
 Engineered reusable **Hugging Face** Transformers components and **ComfyUI** workflows to test multiple generation interfaces, standardize input parameters, and improve prototype reproducibility across 6 model variants.
@@ -1990,29 +1547,29 @@
 Monitored production behavior using Google Cloud Logging, Git, and GitHub, troubleshot failed requests, corrected integration defects, and documented known limitations and handoff procedures, reducing recurring support issues by 25%.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume nunchux</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="270" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="32" ht="270" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>Boston , MA</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in **machine learning for scientific problems**, advanced algorithm development, and scalable computational systems. Experienced in building high-performance software, designing predictive models, and optimizing data-intensive workflows to improve efficiency and operational reliability. Skilled in Python, scientific computing, simulation methodologies, and model evaluation, with an emphasis on translating complex research into practical solutions. Strong written and verbal communication skills, with a focus on **quantum computing**, **quantum error correction**, and research-driven innovation. Committed to collaborating with research and experimental teams to advance reliable computing systems and measurable technical outcomes.</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>Architected scalable scientific machine learning workflows using Python, NumPy, and SciPy to evaluate complex computational problems, improving processing efficiency by 35% and supporting research-oriented algorithm development.
 Simulated **quantum error correction** protocols and evaluated error patterns using Qiskit, **quantum computing** frameworks, and statistical analysis, documenting experimental results across 1,000+ simulated test cases.
@@ -2021,7 +1578,7 @@
 Managed **real-time operations**, monitored system performance, troubleshot computational failures, modified simulation workflows, and corrected software defects; participated in research reviews, motivated cross-functional contributors, oriented team members to technical procedures, and communicated findings through written reports and publication-focused documentation.</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>Investigated scientific machine learning problems using R, TensorFlow, and scikit-learn, comparing predictive approaches across 10+ experimental datasets and improving model evaluation accuracy by 20%.
 Designed numerical experiments for **quantum computing** research using Cirq and Python, computed error rates, and assessed simulated **quantum error correction** protocols across 500+ test scenarios.
@@ -2031,29 +1588,29 @@
 Important: The target role emphasizes **quantum computing** research, error correction, hardware experiments, and publications. The quantum-specific tools and experience above were added to align with the job description, but they should only remain on your résumé if you can substantiate them in an interview. An **exceptional publication record** and a PhD or equivalent research experience are also significant selection criteria; do not imply publications or qualifications you do not have.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume quera</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="270" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="33" ht="315" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Mountain View , CA</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in **machine learning**, **natural language processing** (NLP), search **personalization**, and **recommendation** systems to improve customer experiences and business outcomes. Experienced in designing, building, and shipping production-ready models, scalable applications, and LLM-powered search solutions that capture user interactions and deliver relevant, context-aware results. Skilled in **Python**, **Java**, PyTorch, TensorFlow, RAG, and large language models (LLMs) for domain adaptation, ranking optimization, and complex question answering. Proven ability to improve model accuracy, reduce operational costs, and strengthen decision-making through robust data analysis and cloud-native **machine learning** systems. Collaborative and **proactive** **team player** committed to writing maintainable code, troubleshooting complex challenges, mentoring engineers, and taking ownership of impactful features.</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>Architected **customer-focused** search **personalization** and conversational AI solutions using **Python**, GPT-5, Claude, and LangChain, **combining LLMs** with AWS Bedrock and RAG to answer complex banking questions and reduce Tier-1 support workload by 40%.
 Engineered a **machine learning** **ranking system** with Scikit-**learn**, Logistic Regression, and Gradient Boosting, inventing new customer signals and modeling interactions between credit and behavioral features to improve risk identification by 25%.
@@ -2062,7 +1619,7 @@
 Managed Kubeflow, MLflow, Docker, and Kubernetes deployment workflows with CI/CD/CT pipelines, writing robust, readable, testable code; troubleshot production issues, mentored **junior engineers**, and took ownership of 10+ production models while collaborating with cross-functional teams.</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Analyzed customer, transaction, and product behavior using **Python**, SQL, and PySpark, computed actionable features for search relevance and **personalization**, and improved demand forecast accuracy by 20% through data-driven modeling.
 Built scalable data preparation and feature engineering workflows with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multiple customer and product data sources and reducing processing time by 30%.
@@ -2072,24 +1629,24 @@
 Important: The job description's education requirement and **Go**/**C++** proficiency were not established by the supplied work history. Add them to your résumé only if accurate. The rewritten responsibilities align your existing experience with the target role without claiming that an unverified degree or programming proficiency has been confirmed.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Glean</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="225" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
+    <row r="34" ht="225" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in **Python backend development**, PySpark, **Databricks**, and scalable data engineering solutions for financial applications. Experienced in **system design**, **application development**, **testing**, **debugging**, and maintaining secure, high-quality production code in enterprise environments. Skilled in AI-assisted software development, **automated testing**, code optimization, and responsible AI practices to improve engineering **productivity** and software reliability. Proficient in AWS, distributed data processing, database management, and financial data analytics to identify hidden patterns, reduce operational risks, and enhance system **performance**. Adept at collaborating with cross-functional teams to deliver cloud-native applications, maintainable data pipelines, and **scalable technical solutions** aligned with enterprise architecture standards.</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D34" s="1" t="inlineStr">
         <is>
           <t>Architected scalable financial applications using Python, PySpark, and **Databricks**, applying **software engineering concepts**, **system design**, **application development**, and **testing** practices to process **large** financial datasets, improve processing efficiency by 35%, and maintain **operational stability** in **production environments**.
 Engineered and optimized **Snowflake**, **SQL**, and **NoSQL** data workflows, integrating **Apache Spark** and **Kafka** to support distributed data processing, troubleshoot complex technical issues, and improve data pipeline **performance** by 30% across enterprise financial systems.
@@ -2098,7 +1655,7 @@
 Managed **deployment**, maintenance, and **ongoing operational support** for **AWS EMR**, AWS **Glue**, Amazon **ECS**, and Amazon **EKS** (**Elastic Kubernetes Service**) workloads, monitored production **performance**, corrected system defects, and contributed reusable engineering patterns that improved **deployment** reliability by 25%.</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>Developed and maintained enterprise data processing modules using Python, PySpark, and **Databricks**, applying **debugging**, **module development**, **deployment**, and operational support practices to **large** financial datasets and reducing processing time by 30%.
 Gathered, analyzed, and synthesized diverse financial data using **DB2**, **SQL**, and Pandas, computed **performance** metrics, and developed Tableau visualizations and **reporting** that identified hidden data patterns and improved business decision-making by 25%.
@@ -2107,24 +1664,24 @@
 Collaborated with product managers, **architects**, and **cross-functional engineering teams** to **translate finance business requirements** into scalable AWS and AI/ML data platform solutions; motivated and oriented peers on safe AI coding practices, secure data handling, and automation improvements, increasing team delivery **productivity** by 20%.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume chase</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="225" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
+    <row r="35" ht="405" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in Generative AI, Agentic AI, and scalable, cloud-native data architectures that support enterprise automation and intelligent decision-making. Experienced in designing **Retrieval-Augmented Generation** (RAG) pipelines, real-time data ingestion, **advanced classification**, and secure API integrations to improve operational efficiency and customer experience. Skilled in **Python**, **PySpark**, **LangGraph**, **AWS Bedrock**, and LLMOps for building reliable, production-ready AI solutions. Focused on data quality, model observability, responsible AI governance, and measurable business outcomes across financial and enterprise applications. Demonstrated strength in cross-functional collaboration, technical leadership, mentoring, and translating complex business requirements into **innovative**, **scalable solutions**.</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>Architected scalable, modular **GenAI-enabled** banking platforms using **Python**, **PySpark**, **AWS Bedrock**, and **LangGraph**, integrating **Retrieval-Augmented Generation** (RAG), **LlamaIndex**, **FAISS**, **PGVector**, and **Weaviate** to reduce Tier-1 support workload by 40% and improve enterprise knowledge retrieval.
 Engineered secure, end-to-end ingestion and transformation pipelines for structured Excel and semi-structured JSON data using **FastAPI**, **FastMCP**, **SQL**, and **OAuth2**, incorporating real-time ingestion, **transformation logic**, and **schema evolution** to improve data processing efficiency by 35%.
@@ -2133,7 +1690,7 @@
 Led and mentored **cross-functional technical teams** through MLOps, LLMOps, CI/CD/CT, **secure API architecture**, and **data quality reporting and observability**; monitored production pipelines, troubleshot integration failures, modified validation rules, corrected data defects, and delivered 10+ production AI/ML models while reducing fraud-detection false positives by 30%.</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>Conducted **Exploratory Data Analysis** (EDA) using **Python**, **PySpark**, and **SQL** across retail transactions, inventory, and customer records; computed business trends, oriented analytical findings toward stakeholder priorities, and improved demand forecast accuracy by 20% through ARIMA, LSTM, and Prophet models.
 Built enterprise data engineering workflows using Azure Data Factory, Azure Data Lake Storage Gen2 (ADLS Gen2), and Azure Synapse Analytics, integrating structured and semi-structured sources with automated **transformation logic** and **schema evolution** to reduce processing time by 30%.
@@ -2142,24 +1699,24 @@
 Motivated engineering and analytics stakeholders to adopt **software engineering principles**, Agile/Scrum, Git, and Jira for collaborative delivery, documented technical decisions, communicated model results to business teams, and aligned **AI/ML enablement** initiatives with **measurable client outcomes**, improving reporting turnaround by 30%.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume kearney</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="270" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
+    <row r="36" ht="225" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in **AI infrastructure**, backend engineering, and scalable AI-powered applications that improve system reliability, performance, and operational efficiency. Experienced in building **resilient production systems**, supporting **model training** and **serving platforms**, and integrating **search infrastructure** with enterprise AI solutions. Skilled in Python, **TypeScript**, **Ruby**, and **system design**, with a focus on production debugging, platform scalability, and engineering best practices. Collaborated with product, research, and infrastructure teams to deliver reliable, cloud-native solutions and improve developer productivity. Demonstrated success in reducing operational workload, strengthening system performance, and delivering business-focused AI capabilities.</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>Architected scalable **AI infrastructure** using Python, **TypeScript**, and AWS Bedrock, integrating LangChain and RAG to deliver reliable conversational AI features and reduce Tier-1 support workload by 40%.
 Engineered resilient backend services and **system design** patterns for credit risk applications, using AWS SageMaker, SQL, and FastAPI to improve risk identification by 2 reporting cycles and strengthen production performance.
@@ -2168,7 +1725,7 @@
 Managed model **serving platforms**, Docker, Kubernetes, and CI/CD/CT pipelines; troubleshot complex production issues across services, monitored reliability metrics, mentored 4 engineers, and collaborated with product, research, and infrastructure teams to improve platform roadmaps and engineering best practices.</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>Built scalable forecasting and customer analytics applications using Python, **Ruby**, PySpark, and Azure Databricks, applying ARIMA, LSTM, and Prophet to improve demand forecast accuracy by 20% and support business planning.
 Orchestrated enterprise data integration through Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, optimizing shared data workflows and reducing processing time by 30%.
@@ -2178,29 +1735,29 @@
 Important: The target job emphasizes software engineering and **AI infrastructure** rather than traditional data science alone. Keep the technologies and responsibilities that accurately reflect your experience. In particular, include **Ruby**, **TypeScript**, mentoring, and leadership claims only if you can confidently discuss them in an interview.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume figma</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="225" customHeight="1">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="37" ht="225" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Atlanta , GA</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in AI-driven **software development**, Large Language Models (**LLMs**), Generative AI, and scalable enterprise applications across healthcare and financial services. Experienced in building **RAG** pipelines, AI agents, intelligent document processing, and **cloud**-native solutions that improve operational efficiency and customer experience. Skilled in **Python**, **TensorFlow**, **PyTorch**, prompt engineering, model fine-tuning, and AI system evaluation to optimize **precision**, **recall**, **F1-score**, and **AUC-ROC**. Proficient in AWS, **Docker**, **Kubernetes**, **MLOps**, and cost-efficient AI deployment, with a focus on secure, reliable, and scalable solutions. Adept at translating clinical and business requirements into practical AI applications, communicating complex technical concepts to non-technical stakeholders, and collaborating across engineering, product, and DevOps teams.</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>Architected scalable, enterprise-quality AI-driven applications for banking and healthcare use cases using **Python**, **OpenAI** APIs, **GPT-4**, **GPT-3.5**, o1 reasoning models, and **LangChain**, integrating **voice recognition**, **image** parsing, **document parsing**, and text-to-speech capabilities to reduce customer support workload by 40%.
 Engineered context-aware **RAG** systems from scratch using **LlamaIndex**, FAISS, Pinecone, and **vector databases**, while maintaining prompt libraries and applying prompt engineering, **prompt caching**, **batching**, and **quantization** to improve response relevance and reduce LLM operating costs by 25%.
@@ -2209,7 +1766,7 @@
 Managed scalable **MLOps** deployments across AWS, **Docker**, and **Kubernetes**, used **GitHub Copilot**, **Cursor**, and **Codeium/Windsurf** to troubleshoot **new and legacy codebases**, documented code and application workflows, and communicated AI performance and cost trade-offs to technical teams and non-technical stakeholders, supporting 10+ production models.</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>Developed AI-enhanced forecasting and predictive analytics solutions using **Python**, PySpark, Scikit-learn, and Azure Databricks, analyzing clinical, operational, and customer datasets to translate healthcare and business needs into actionable insights and improve prediction accuracy by 20%.
 Designed and optimized AI training and testing datasets through Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, integrating structured and unstructured records into reliable data pipelines and reducing processing time by 30%.
@@ -2218,24 +1775,24 @@
 Participated in Agile/Scrum delivery, managed version control and collaborative development using **Git**, troubleshot pipeline and deployment issues, modified model configurations, corrected data inconsistencies, monitored performance metrics, and documented technical workflows while adapting to changing project requirements and communicating findings to **non-technical audiences**.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume CoverMyMeds</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="270" customHeight="1">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
+    <row r="38" ht="315" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist with expertise in **LLMs**, **AI/ML workloads**, **inference** optimization, **distributed systems**, and cloud infrastructure for scalable, customer-facing applications. Experienced in transitioning AI solutions from proof of concept to production, improving latency, throughput, reliability, and cost efficiency across high-load environments. Skilled in **vLLM**, **TensorRT**, **GPU workloads**, **AI infrastructure**, and MLOps to strengthen deployment stability and accelerate time-to-value. Proven ability to troubleshoot performance bottlenecks, manage production incidents, and collaborate with **technical customers** and engineering teams. Applied a **structured**, **proactive**, **and solution-oriented mindset** to production **ownership**, continuous improvement, and business outcomes in **B2B environments**.</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>Owned the production transition of customer-facing LLM applications built with GPT-5, Claude, LangChain, and AWS Bedrock, reducing proof-of-concept-to-production time by 35% and lowering Tier-1 banking support workload by 40% through reliable deployment and scalable **inference**.
 Monitored and optimized **vLLM**, **TensorRT**, **GPU workloads**, and **inference** frameworks for high-load AI applications, troubleshooting latency and throughput bottlenecks and improving **inference** performance by 30% through **structured** benchmarking and **proactive** capacity analysis.
@@ -2244,7 +1801,7 @@
 Provided **structured** feedback to Product and Infrastructure teams using MLflow, Kubernetes, and CI/CD/CT pipelines, motivated cross-functional **execution**, participated in technical reviews, oriented stakeholders toward best practices, and identified opportunities that increased customer workload adoption by 20%.</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>Deployed production-ready forecasting and customer analytics models using Python, PySpark, Azure Databricks, ARIMA, LSTM, and Prophet, improving prediction accuracy by 20% and helping customer engineering teams move validated AI solutions into operational workflows.
 Engineered scalable data processing and distributed computing pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, processing multi-source datasets 30% faster while improving workload stability and supporting high-volume business applications.
@@ -2254,24 +1811,24 @@
 Important: The job description emphasizes hands-on production **ownership**, **inference** optimization, and customer engineering. The bullets above include the requested ATS keywords, but verify that you can substantiate direct experience with **vLLM**, **TensorRT**, **GPU workloads**, **SRE**, and production incident management before submitting. Do not present tools or responsibilities you have not actually used as established work experience.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume nebius</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="225" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="39" ht="270" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>ChatGPT said: Data Scientist specializing in **Agentic AI**, Transformer-Based Deep Learning Models, and scalable machine learning solutions for enterprise applications. Experienced in building, training, and deploying models using Python, **PyTorch**, **PySpark**, and **Hugging Face** to process millions of language records and generate reliable inferences. Skilled in large-scale data processing with **Spark**, **SparkSQL**, **Google BigQuery**, and **GCP**, with experience adapting existing scripts and optimizing model performance. Focused on developing cloud-native AI solutions, improving predictive accuracy, reducing operational risks, and enhancing customer experiences. Demonstrated strong communication, teamwork, flexibility, and the ability to learn quickly in dynamic, cross-functional environments.</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>Architected enterprise **Agentic AI** assistants using Python, **PyTorch**, and **Hugging Face** Transformers, integrating Transformer-Based Deep Learning Models to automate banking customer support and reduce Tier-1 agent workload by 40%.
 Engineered scalable data processing workflows using **PySpark**, **Spark**, and **SparkSQL** to analyze millions of customer language records, improving data preparation efficiency by 35% and enabling timely model inferences.
@@ -2280,7 +1837,7 @@
 Adapted peer-developed notebooks and command-line scripts, troubleshot model and data pipeline issues, modified preprocessing workflows, and monitored inference quality; participated in cross-functional reviews, motivated collaborative problem-solving, oriented quickly to changing tasks, and corrected data inconsistencies to reduce model-related errors by 30%.</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>Built retail demand forecasting and customer behavior models using Python, Pandas, and NumPy, analyzing transaction, inventory, and loyalty datasets to improve forecast accuracy by 20% and support replenishment decisions.
 Processed high-volume retail datasets with Apache **Spark** and distributed data transformation techniques, consolidating transactions, store operations, and customer service records while reducing data processing time by 30%.
@@ -2289,29 +1846,29 @@
 Collaborated with diverse engineering and business teams using Git, Jira, and Agile/Scrum practices; communicated model findings clearly, demonstrated a can-do attitude, learned new tools quickly, and adapted to changing priorities while reducing manual investigation effort by 35%.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Wipro</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="225" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="40" ht="225" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Washington , DC</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **graph analytics**, **fraud detection**, and machine learning to identify hidden relationships, anomalous patterns, and cross-program risks across complex datasets. Experienced in building scalable **graph data pipelines**, knowledge graphs, and cloud-based analytical solutions to improve investigative efficiency and data quality. Applied Python, **Neo4j**, **Cypher**, and advanced graph theory techniques to support relationship discovery, risk assessment, and actionable intelligence. Focused on **data governance**, model integrity, reproducible analytics, and clear communication of technical findings to business and investigative stakeholders.</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="D40" s="1" t="inlineStr">
         <is>
           <t>Architected scalable **Neo4j** knowledge graphs using **Cypher**, Python, and NetworkX to connect financial entities and transactions across **multi-program** datasets, uncovering hidden relationships and improving fraud investigation efficiency by 35%.
 Computed **network topology**, **centrality measures**, **community detection**, and **shortest-path algorithms** to identify suspicious transaction networks, emerging fraud schemes, and high-risk entities, accelerating investigative lead generation by 30%.
@@ -2320,7 +1877,7 @@
 Managed **graph analytics**, **knowledge graph development**, and **data governance** documentation; troubleshot query performance, modified analytic rules, monitored model outputs, corrected data inconsistencies, and participated in stakeholder reviews to validate findings and improve investigative workflows by 25%.</t>
         </is>
       </c>
-      <c r="E52" s="1" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>Designed and optimized **graph-based intelligence products** using Python, Scikit-learn, and SQL to analyze interconnected retail, financial, and operational records, identifying suspicious entity relationships and improving risk detection coverage by 28%.
 Conducted exploratory data analysis and data profiling across **multi-agency** and **multi-program** datasets, integrating structured and third-party information into graph-ready formats and reducing data preparation time by 30%.
@@ -2329,24 +1886,24 @@
 Evaluated emerging **graph analytics** tools, AI/ML technologies, and data sources; contributed technical documentation and risk assessments aligned with the NIST AI Risk Management Framework, OMB M-25-22, OMB M-25-21, and OMB M-26-04, motivating continuous improvement that increased analytic reproducibility by 25%.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume knowesis</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="270" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="41" ht="270" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>Data Scientist with expertise in **Python**, SQL, causal inference, and **data analysis tools** to transform complex datasets into actionable business and **policy** insights. Experienced in building scalable data pipelines, measurement frameworks, and dashboards that maintain consistent reporting across internal and external audiences. Applied **quasi-experimental designs**, regression analysis, and **observational data** to evaluate program effectiveness, identify trends, and support evidence-based decisions. Skilled in leveraging **AI tools** and public data sources to monitor regulatory developments, assess emerging risks, and communicate findings to technical and nontechnical stakeholders. Delivered measurable improvements in operational efficiency, analytical accuracy, and risk management across financial and business environments.</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>Partnered with product, business, and **policy**-facing stakeholders to analyze financial and **external and public data sources** using **Python**, SQL, and **data analysis tools**, producing evidence-based data collateral for **policy** position papers, partnership discussions, and external communications while improving reporting efficiency by 35%.
 Managed executive dashboards and data pipelines using Power BI, AWS Redshift, and AWS Glue, established consistent metrics for legislators, regulators, and public audiences, and aligned reporting with **investor-relations** requirements and **financial-disclosure data standards**, reducing reporting discrepancies by 30%.
@@ -2355,7 +1912,7 @@
 Conducted **applied causal inference** using **observational data**, **instrumental variables**, and matching techniques to evaluate **policy**-related outcomes; translated **ambiguous** findings into actionable recommendations, troubleshot data inconsistencies, corrected reporting gaps, and motivated cross-functional teams to make evidence-based decisions in **fast-moving environments**.</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
         <is>
           <t>Analyzed customer, transaction, and market datasets using **Python**, R, and Pandas, incorporating **external and public data sources** to identify emerging business trends and support research-backed recommendations, improving analytical accuracy by 20%.
 Engineered scalable data integration workflows with Azure Data Factory, Azure Data Lake Storage Gen2, and Azure Synapse Analytics, standardizing published metrics and audit-ready datasets to reduce data preparation time by 30% and support reliable external reporting.
@@ -2365,24 +1922,24 @@
 Important: The job description requests 6+ years of **hands-on data science experience** and direct **policy**, **government affairs**, or regulatory-team exposure. These drafts incorporate the requested ATS terminology, but the added tools, methods, responsibilities, and metrics should be retained in your résumé only if you can substantiate them in an interview. Your listed employment dates alone do not establish six years of experience.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume anthropic</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="270" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="42" ht="270" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **Python**, **Microsoft SQL Server**, **machine learning**, and **statistical modeling** to deliver scalable data science solutions and measurable business outcomes. Experienced in **data analysis**, **feature engineering**, **model evaluation**, and **automation** to improve operational efficiency, data accuracy, and risk detection. Skilled in cloud-based workflows using **AWS**, **Azure**, and **Snowflake**, with expertise in **Docker**, version control, and secure programming practices. Adept at translating complex analytical findings into actionable insights through strong communication, cross-functional collaboration, and data-driven decision-making. Committed to **data integrity**, continuous improvement, and delivering reliable solutions within demanding project deadlines.</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>Architected scalable **machine learning** solutions using **Python**, **Microsoft SQL Server**, and **AWS**, applying **statistical modeling**, data extraction, and transformation techniques to analyze banking data and reduce Tier-1 customer support workload by 40%.
 Engineered automated credit risk analytics using Microsoft Excel, PowerShell, and **Visual Studio** Code, applying advanced **feature engineering** and **model evaluation** to identify at-risk accounts 1–2 reporting cycles earlier while maintaining **data integrity** and security.
@@ -2391,7 +1948,7 @@
 Managed 10+ production model deployments using **AWS**, Linux, **CLI/Shell**, and **Microsoft PowerShell**, monitored data quality and model performance, troubleshot deployment issues, modified scripts, and corrected inconsistencies while coordinating with department managers and external partners. Participated in cross-functional reviews, motivated team members toward shared goals, and remained organized, **detail-oriented**, **proactive**, and flexible with project deadlines and company events.</t>
         </is>
       </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>Computed demand forecasts and customer behavior trends using **Python**, **Azure**, and **Snowflake**, applying **machine learning** and statistical analysis to retail transactions, inventory, and loyalty data to improve forecast accuracy by 20% and support replenishment decisions.
 Streamlined data integration and transformation through **Microsoft SQL Server**, **Azure** Data Factory, and **Azure** Synapse Analytics, consolidating multiple operational datasets and reducing processing time by 30% while preserving data accuracy and secure access.
@@ -2401,29 +1958,29 @@
 Important before submitting: The responsibilities above incorporate the job description's required and preferred keywords, including tools and programming languages. Keep only technologies and duties you can accurately discuss in an interview. In particular, **Rust**, **C#**, **Emacs**, **Vim**, **Notepad++**, PowerShell, and **Microsoft SQL Server** should remain only if you have relevant experience or can substantiate them through projects or training.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Westport Properties</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="270" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="43" ht="225" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>New York , NY</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **user growth forecasting**, predictive analytics, and statistical modeling to support product strategy and business decisions. Experienced in building scalable, cloud-native forecasting systems and repeatable data pipelines using Python, SQL, and modern data engineering ecosystems. Translated complex analytical findings into actionable insights, improving forecast accuracy, operational efficiency, and risk visibility. Skilled in **AI analysis tools**, methodological validation, stakeholder collaboration, and **investor-grade reporting** to support strategic planning in dynamic business environments.</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr">
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>Architected scalable **user growth forecasting** solutions using Python, SQL, and **AI analysis tools**, combining customer behavior, engagement trends, and product metrics to improve forecast reliability by 25% across 3 business planning cycles.
 Computed and validated statistical forecasts, growth scenarios, and sensitivity analyses using Pandas, NumPy, and Scikit-learn, correcting data inconsistencies and testing assumptions to reduce forecasting errors by 20%.
@@ -2432,7 +1989,7 @@
 Mentored 3 junior data scientists, motivated team participation in forecasting reviews, monitored model performance, troubleshot data quality issues, and modified validation processes to strengthen forecast consistency and repeatability by 30%.</t>
         </is>
       </c>
-      <c r="E55" s="1" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>Forecasted customer acquisition, retention, and demand patterns using R, ARIMA, Prophet, and time-series analysis, evaluating 24 months of historical data to improve forecast accuracy by 20% and support business planning.
 Engineered reliable ETL/ELT pipelines with Azure Data Factory, Azure Data Lake Storage Gen2, and Azure Synapse Analytics, consolidating 12+ operational datasets and reducing data processing time by 30%.
@@ -2442,24 +1999,24 @@
 Important: The job description emphasizes **user growth forecasting** and **investor-grade reporting**. The numerical achievements and tools above should be retained only if you can substantiate them in interviews. The graduate degree requirement should also be listed in your education section if applicable.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume duolingo</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="225" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="44" ht="270" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **fraud detection**, machine learning, **statistical modeling**, and financial risk analytics to identify suspicious activities and strengthen risk decisioning. Experienced in building scalable, cloud-native applications and predictive models for **account opening**, **account takeover**, identity verification, credit risk, and financial crime. Skilled in **Python**, **PySpark**, **XGBoost**, **TensorFlow**, and **scikit-learn** to process **large datasets**, engineer meaningful features, and improve **model performance**. Applied **model evaluation**, **explainability**, **experimentation**, and model **governance** to reduce false positives, mitigate fraud losses, and balance security with customer experience. Collaborated with **engineering** and analytics teams to move machine learning solutions into **production** through automated pipelines, model monitoring, and reliable decisioning systems.</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>Investigated large-scale identity, transactional, device, behavioral, temporal, velocity, network, and **third-party data** using **Python**, **PySpark**, **pandas**, and **NumPy**, conducting **exploratory analysis** and **fraud label development** to identify emerging **fraud patterns**, **attack methods**, and **behavioral signals** across **account opening** and **account takeover**.
 Translated ambiguous **fraud and risk problems** into testable **hypotheses**, **analytical plans**, **model requirements**, and **measurable success criteria**; engineered meaningful **predictive features** and developed **XGBoost** and **scikit-learn** **supervised learning** models for **fraud detection**, **identity risk**, credit risk, and financial-crime prevention, reducing false positives by 30%.
@@ -2468,7 +2025,7 @@
 Managed **production** model monitoring and **validation** through AWS SageMaker, MLflow, and CloudWatch, monitored **feature quality**, **model performance**, **population changes**, **fraud-pattern drift**, and **model behavior**, and presented **tradeoffs**, **risks**, and **recommendations** while maintaining **data privacy**, **model documentation**, **explainability**, and **governance** standards.</t>
         </is>
       </c>
-      <c r="E56" s="1" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Analyzed large-scale customer, payment, account, and operational datasets using **Python**, **PySpark**, **pandas**, and **NumPy**, uncovering suspicious behavioral trends and developing fraud labels to support identity-risk assessments, account-opening reviews, account-takeover investigations, and credit-risk analysis; improved forecasting and risk-analysis accuracy by 20%.
 Constructed and refined **TensorFlow** and **scikit-learn** **machine learning models** using **supervised learning**, **statistical modeling**, feature **engineering**, and **feature selection** to detect unusual transaction activity and **changing attack patterns**, reducing manual risk-investigation effort by 35%.
@@ -2477,29 +2034,29 @@
 Collaborated with **engineering** and analytics teams to move validated **models beyond experimentation** into **production** using Docker, Kubernetes, and CI/CD pipelines; presented **model behavior**, **risks**, and **recommendations** through Tableau dashboards and maintained **model documentation**, **data privacy**, **explainability**, and **governance** controls to support reliable deployment and monitoring.</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume experian</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="225" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="45" ht="270" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Orlando , FL</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **statistical modeling**, machine learning, and predictive analytics to solve business and operational challenges. Experienced in building scalable analytical solutions for demand forecasting, customer behavior analysis, risk assessment, and operational planning using Python, **Pandas**, **scikit-learn**, and **SQL**. Skilled in transforming complex datasets into actionable insights, measurable business KPIs, and stakeholder-ready visualizations using **Power BI** and **Tableau**. Applied diverse analytical methodologies to improve forecasting accuracy, optimize decision-making, reduce operational risks, and enhance business efficiency. Collaborated with cross-functional teams and technology partners to integrate data-driven solutions into business workflows.</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>Translated banking and customer service challenges into analytical solutions using Python, **Pandas**, and **scikit-learn**, building statistical and **machine learning models** that reduced Tier-1 support workload by 40% and improved operational decision-making.
 Prepared, cleaned, and transformed over 100K monthly customer feedback records using **SQL**, identifying relevant data sources and variables that improved predictive model accuracy by 25% and supported customer trend analysis.
@@ -2508,7 +2065,7 @@
 Managed cross-functional data initiatives with operations, technology, analytics, and external data partners; participated in project planning, troubleshot data quality issues, modified analytical workflows, monitored model performance, corrected reporting discrepancies, and motivated stakeholders to adopt data-driven decisions.</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>Developed **machine learning models** and **time series forecasting** solutions for retail demand planning using Python and **scikit-learn**, improving forecast accuracy by 20% and supporting inventory replenishment, staffing optimization, and commercial planning.
 Engineered structured analytical datasets from transaction, inventory, store operations, and customer service data using **SQL** and PySpark, reducing data processing time by 30% and improving data readiness for statistical analysis.
@@ -2517,29 +2074,29 @@
 Collaborated independently and within cross-functional operations, technology, and analytics teams to prioritize data initiatives, communicate complex analytical concepts to technical and non-technical stakeholders, establish relationships with internal and external technology partners, and improve analytics capabilities for operational planning.</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume signature aviation</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="225" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="46" ht="225" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Las Vegas , NV</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>Data Scientist with expertise in machine learning, statistical analysis, advanced analytics, and big data to solve complex business problems and deliver actionable insights. Experienced in building scalable data models, predictive algorithms, and cloud-native analytical solutions that improve operational efficiency, strengthen risk management, and support commercial strategy. Proficient in Python, SQL, R, **Java**, Tableau, Power BI, and Looker, with hands-on experience in model deployment, automation, and MLOps/CI-CD workflows. Skilled in data management, data lifecycle practices, business intelligence, and translating industry trends into measurable business outcomes. Strong communicator who collaborated with cross-functional teams to present analytical findings, recommend data-driven improvements, and measure model performance.</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>Architected scalable machine learning and advanced analytics solutions using Python, SQL, and **Java** to address complex banking business problems, delivering actionable insights that reduced Tier-1 customer support workload by 40% and supported commercial strategy.
 Computed credit risk indicators and statistical analyses using R and Python, managed analytical data models, and evaluated business performance metrics to identify at-risk accounts 1–2 reporting cycles earlier and improve decision-making.
@@ -2548,7 +2105,7 @@
 Operationalized machine learning models through MLOps, CI/CD workflows, and automated deployment processes, monitored 10+ production models, measured business outcomes, and collaborated with enterprise data, BI, and insights teams to communicate recommendations to audiences of varying sizes.</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
         <is>
           <t>Planned and completed complex forecasting and customer analytics projects using PySpark, ARIMA, LSTM, and Prophet, analyzing retail sales, inventory, and customer data to improve forecast accuracy by 20% and support commercial planning.
 Engineered large-scale data integration workflows using Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multiple operational sources and reducing data processing time by 30% through improved data lifecycle management.
@@ -2557,24 +2114,24 @@
 Presented analytical recommendations and model performance results to technical and nontechnical audiences, managed project deliverables through Agile/Scrum practices, and measured deployed model impacts to improve reporting efficiency by 30% and support data-driven business decisions.</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Aristocrat</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="270" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="47" ht="225" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **statistical analysis**, machine learning, and data **engineering** to solve complex business problems and improve operational efficiency. Experienced in building scalable data pipelines and cloud-native analytics solutions that support data-driven decisions across financial services and retail domains. Proficient in Python, SQL, and R for data extraction, manipulation, statistical modeling, and quantitative problem-solving. Applied **t-tests**, descriptive statistics, and root cause analysis to identify trends, validate hypotheses, and uncover business performance issues. Delivered measurable improvements in forecasting accuracy, fraud detection, reporting efficiency, and customer experience through reliable, data-driven solutions.</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>Extracted and manipulated over 100K monthly banking and customer records using SQL and Python, computed descriptive statistics, and applied **t-tests** to validate performance differences, identify significant trends, and improve analytical accuracy by 25%.
 Managed scalable data pipelines for financial transaction and customer support data, integrating structured datasets for **statistical analysis** and reducing manual data preparation effort by 35%.
@@ -2583,7 +2140,7 @@
 Participated in cross-functional analytical reviews, motivated stakeholders to adopt evidence-based decisions, troubleshot data inconsistencies, and oriented business teams toward validated findings that improved customer support efficiency by 40%.</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E47" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail sales, inventory, and customer datasets using R and Python, computed descriptive statistics, conducted **t-tests**, and evaluated business trends to improve demand forecasting accuracy by 20%.
 Created and maintained automated data pipelines using Azure Data Factory and Azure Synapse Analytics, consolidated multiple data sources, and reduced data processing time by 30%.
@@ -2593,24 +2150,24 @@
 Important: The job description specifically requires SQL, data pipeline creation, Python or R, **t-tests**, descriptive statistics, and quantitative root cause analysis. All six requirements are included above. Keep the numeric achievements and tools only where you can confidently support them with your actual experience during an interview.</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Google</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="225" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="48" ht="270" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in predictive analytics, statistical modeling, and revenue intelligence to improve business performance and executive decision-making. Experienced in building **scalable dashboards**, cloud-native data solutions, and forecasting models that enhance **sales productivity**, **customer expansion**, **renewals**, and **churn analysis**. Skilled in Python, SQL, **SaaS** analytics, and large-scale operational data processing to improve **reporting consistency**, data quality, and **KPI governance**. Delivered measurable business outcomes through operational intelligence, data-driven process optimization, and cross-functional collaboration with **Revenue Operations**, Finance, and Data Engineering teams.</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr">
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>Architected predictive forecasting models and **pipeline analytics frameworks** using Python, SQL, and statistical modeling to evaluate **sales productivity**, **customer behavior**, **revenue trends**, and pipeline performance, improving forecasting visibility by 30%.
 Computed sales performance metrics and built **scalable dashboards** with Power BI and DAX, delivering **advanced reporting** on **customer expansion**, **renewals**, **churn analysis**, and revenue attainment that improved executive decision-making efficiency by 25%.
@@ -2619,7 +2176,7 @@
 Translated technical findings into business recommendations through **operational intelligence solutions**, identifying inefficiencies in **marketplace**, **channel**, and **consumption-based business models**; motivated stakeholders to adopt data-driven improvements that increased sales process efficiency by 20%.</t>
         </is>
       </c>
-      <c r="E60" s="1" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
         <is>
           <t>Developed customer demand and revenue forecasting models using PySpark, ARIMA, LSTM, and Prophet to analyze sales patterns, **customer behavior**, and **operational efficiency** across large retail datasets, improving forecast accuracy by 20%.
 Engineered automated data preparation and integration workflows with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transaction, inventory, and customer data into reliable analytical datasets and reducing processing time by 30%.
@@ -2628,29 +2185,29 @@
 Participated in **forecasting transformation initiatives**, **business analysis**, and cross-functional stakeholder reviews; oriented business teams toward standardized metrics, scalable reporting practices, and data-driven recommendations, improving **operational efficiency** by 20%.</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume megaport</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="225" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="49" ht="225" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Reach Triangle Park , NC</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in R programming, **causal inference**, and **real-world healthcare data** to deliver reliable, reproducible research and actionable clinical insights. Experienced in transforming complex relational databases, **deidentified administrative claims**, and **electronic health record (EHR) data** into scalable analytic-ready datasets and longitudinal cohorts. Applied **biostatistics**, **epidemiology**, and observational study methods to evaluate treatment outcomes, patient characteristics, and healthcare risks. Strengthened research quality through SQL, automated analytical pipelines, statistical diagnostics, code reviews, and reproducible reporting. Collaborated with cross-functional scientific and technical teams to improve research efficiency, data quality, and evidence-based decision-making.</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>Queried large-scale relational databases using R, **dbplyr**, and SQL to transform **deidentified administrative claims** and **electronic health record (EHR) data** into analysis-ready cohorts, processing 100K+ monthly patient and transaction records while preserving clinical event relationships.
 Applied **causal inference**, **causalRisk**, and **observational data** methods to evaluate treatment outcomes, calculated **propensity score distributions**, assessed **weight behavior**, and examined **covariate balance** to identify analytical concerns and support evidence-based research decisions.
@@ -2659,7 +2216,7 @@
 Managed reproducible research repositories through **GitLab**, established automated **quality control procedures**, participated in **code review** and **testing**, performed **double coding** and an **independent check** of the **primary implementation**, and coordinated with the **study design team** throughout the **study lifecycle** to maintain reliable research outputs.</t>
         </is>
       </c>
-      <c r="E61" s="1" t="inlineStr">
+      <c r="E49" s="1" t="inlineStr">
         <is>
           <t>Analyzed **real-world healthcare data** from **hospital chargemaster** systems, **registry data**, and electronic health record (EHR) sources, applying R, dplyr, and tidyr to standardize clinical records and improve data consistency across 50K+ longitudinal patient observations.
 Designed observational research cohorts using **biostatistics**, **epidemiology**, and **health economics** principles, interpreted clinical diagnoses, procedures, medications, and laboratory results, and aligned patient selection and outcome definitions with approved study protocols.
@@ -2668,29 +2225,29 @@
 Collaborated with the **study design team** and cross-functional scientific stakeholders, motivated consistent documentation and knowledge sharing, oriented team members to reproducible coding standards, and participated in independent validation, **testing**, and reporting activities across the research lifecycle, including projects involving **bioinformatics** and clinical outcomes.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume headwater science</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="270" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="50" ht="270" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>New York , NY</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>Data Scientist with expertise in Python, SQL, **statistical inference**, **experimental design**, and predictive modeling, translating ambiguous business challenges into rigorous analyses and actionable recommendations. Experienced in building scalable AI applications, cloud-native analytics solutions, and data-driven systems that improved operational efficiency, reduced risk, and enhanced customer experiences. Skilled in AI research, machine learning experimentation, and modern data stack technologies, including BigQuery, dbt, Looker, and Airflow. Demonstrated leadership in managing complex analytical roadmaps, mentoring cross-functional teams, and communicating concise, evidence-based insights. Applied an empathetic, collaborative leadership approach to accelerate delivery, improve decision-making, and align data science initiatives with business outcomes.</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr">
+      <c r="D50" s="1" t="inlineStr">
         <is>
           <t>Architected scalable banking AI assistants using Python, SQL, LangChain, and AWS Bedrock, integrating retrieval-augmented generation (RAG) with FAISS and Pinecone to reduce Tier-1 customer support workload by 40% and translate ambiguous customer needs into measurable analytical objectives.
 Computed credit risk metrics using Power BI, Amazon SageMaker, and predictive modeling techniques, including Logistic Regression and Gradient Boosting, identifying at-risk accounts 1–2 reporting cycles earlier and delivering concise, actionable recommendations to business stakeholders.
@@ -2699,7 +2256,7 @@
 Led complex, multi-workstream AI delivery through Kubeflow, MLflow, Docker, Kubernetes, and Git, coordinating the deployment and retraining of 10+ production models; monitored model performance, troubleshot pipeline failures, corrected data-quality issues, and motivated team members through empathetic collaboration and continuous improvement.</t>
         </is>
       </c>
-      <c r="E62" s="1" t="inlineStr">
+      <c r="E50" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail demand, inventory, and customer behavior using Python, PySpark, and ARIMA, LSTM, and Prophet forecasting models, improving forecast accuracy by 20% and converting ambiguous merchandising questions into structured analytical problems and business recommendations.
 Engineered data preparation and transformation workflows using Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transaction, store operations, and customer service datasets while reducing processing time by 30% and improving analytics readiness.
@@ -2709,29 +2266,29 @@
 ATS keywords covered: SQL, Python, Git, **statistical inference**, **experimental design**, predictive modeling, BigQuery, dbt, Looker, Airflow, AI research, analytical problem-solving, ambiguity management, multi-workstream roadmaps, actionable narratives, team leadership, mentoring, empathy, and stakeholder communication.</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume cohere</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="225" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="51" ht="225" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Minneapolis , MN</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in statistical analysis, machine learning, and **quantitative analysis** to solve complex business problems and deliver measurable outcomes. Experienced in building scalable applications, cloud-native data solutions, and distributed processing pipelines for financial, retail, and customer analytics. Applied **operations research**, experimental design, and predictive modeling to improve **inventory optimization**, **supply chain** efficiency, and risk management. Skilled in mining structured and unstructured data using Python, R, Scala, and Apache Spark to generate actionable insights. Collaborated with cross-functional teams to deploy reliable, data-driven solutions that enhanced operational efficiency, reduced risks, and supported strategic decision-making.</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>Applied Python, statistical analysis, and **quantitative analysis** to banking datasets, designing predictive models and scalable data-driven solutions that improved credit risk identification by 35% and supported business decision-making.
 Conducted **design and analysis of experiments** and A/B testing to evaluate machine learning strategies, measure customer engagement, and optimize banking service recommendations, improving campaign effectiveness by 20%.
@@ -2740,7 +2297,7 @@
 Collaborated with product, engineering, and business teams to deploy scalable AWS machine learning solutions, managed model monitoring, troubleshot data quality issues, corrected model inconsistencies, and communicated actionable findings to technical and nontechnical stakeholders, improving deployment reliability by 25%.</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>Performed **operations research** and **inventory optimization** using R, ARIMA, and Prophet to analyze demand patterns, optimize replenishment decisions, and improve retail forecasting accuracy by 20% across multiple product categories.
 Managed distributed data pipelines with Azure Data Factory, Azure Databricks, and ADLS Gen2, integrating more than 500,000 monthly sales, inventory, and customer records while reducing data preparation time by 30%.
@@ -2749,29 +2306,29 @@
 Participated in cross-functional analytics initiatives spanning **healthcare**, **cybersecurity**, and retail business scenarios; oriented stakeholders on analytical findings, motivated adoption of data-driven practices, and monitored model performance through Azure Monitor, reducing manual investigation effort by 35%.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Accenture</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="225" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="52" ht="225" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Rochester , MN</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in data science methods, machine learning, and **structured and unstructured data** analysis to solve complex business and clinical challenges. Experienced in building scalable applications, automating **data management**, and creating efficient **data extraction** and analytical workflows to improve decision-making and operational efficiency. Skilled in interpreting complex datasets, conducting scientific analysis, and translating findings into actionable business insights. Proficient in Python, SQL, statistical modeling, and data visualization, with a focus on reducing risks, improving data quality, and enhancing customer outcomes. Effective collaborator with **subject matter experts** and business stakeholders, delivering clear reports, practical recommendations, and insights that support business and **clinical practice**.</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>Analyzed **structured and unstructured data** using Python, SQL, and AWS Bedrock to deliver actionable **data insights** for banking business problems, identifying key **data types**, **topics**, and **scientific challenges** while reducing Tier-1 support workload by 40%.
 Executed **analytical procedures** for project work requests using Pandas, NumPy, and Power BI, computing credit risk indicators and presenting findings through clear reports that helped business stakeholders identify at-risk accounts 2 reporting cycles earlier.
@@ -2780,7 +2337,7 @@
 Managed and monitored analytical workflows using AWS SageMaker, MLflow, and Docker, troubleshot data and model issues, corrected inconsistencies, and participated in model risk management (MRM) reviews; motivated and oriented stakeholders through practical guidance that reduced fraud detection false positives by 30%.</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>Investigated retail business and operational challenges using PySpark, Azure Databricks, and ARIMA, extracting insights from sales, inventory, and customer datasets to improve demand forecast accuracy by 20% and support replenishment decisions.
 Designed and optimized **data extraction** and ETL pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transactions, store operations, and customer service records while reducing data processing time by 30%.
@@ -2789,24 +2346,24 @@
 Participated in project reviews with **subject matter experts** and stakeholders, interpreted analytical results, prepared findings and reports, and provided dataset explanations, training, and improvement suggestions to strengthen data quality, **analytical procedures**, and business reporting.</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume mayoclinic</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="225" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="53" ht="270" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in financial services analytics, **lending operations**, predictive modeling, and operational intelligence to improve business performance and customer experience. Built scalable, cloud-native machine learning solutions and analytics workflows that improved forecasting accuracy, reduced fraud detection errors, and streamlined operational reporting. Applied Python, SQL, **Alteryx**, and Tableau to analyze large-scale datasets, strengthen **data integrity**, and deliver actionable insights for risk management and operational decision-making. Leveraged **Agentic AI**, advanced statistical techniques, and business intelligence (BI) solutions to improve **agent performance**, **automate reporting**, and support data-driven process improvements. Translated complex analytical findings into executive-ready recommendations while supporting cross-functional collaboration, model governance, and measurable business outcomes.</t>
         </is>
       </c>
-      <c r="D65" s="1" t="inlineStr">
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>Analyzed large-scale **lending operations** and customer transaction datasets using Python, SQL, and **Alteryx**, applying statistical techniques to identify operational inefficiencies, evaluate **agent performance**, and improve reporting accuracy by 30%.
 Engineered **predictive models** using machine learning and advanced statistical modeling to assess credit risk, prioritize at-risk accounts, and strengthen lending decisions, improving early risk identification by 25%.
@@ -2815,7 +2372,7 @@
 Presented analytical findings and recommendations to **senior executives** and cross-functional business, technology, and analytics teams; managed multiple project deadlines, mentored junior analysts, and strengthened data-driven decision-making across **lending operations**.</t>
         </is>
       </c>
-      <c r="E65" s="1" t="inlineStr">
+      <c r="E53" s="1" t="inlineStr">
         <is>
           <t>Examined high-volume financial and operational datasets using PySpark, Pandas, and NumPy to uncover performance trends, detect process bottlenecks, and improve operational efficiency by 20%.
 Constructed **predictive models** using Scikit-learn, XGBoost, and Logistic Regression to forecast customer behavior, assess portfolio risks, and support quantitative operational decisions, improving forecast accuracy by 20%.
@@ -2824,24 +2381,24 @@
 Coordinated analytics initiatives using Agile/Scrum, Jira, and Git, participated in management consulting engagements, troubleshot data discrepancies, modified reporting logic, corrected **data quality** issues, and motivated collaborative teams to deliver reliable analytical solutions on schedule.</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume jpmorganchase</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="270" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="54" ht="270" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **statistical analysis**, **Operations Research**, machine learning, and data-driven solutions for complex product and business problems. Experienced in building scalable applications and cloud-native solutions that improve operational efficiency, strengthen risk management, and enhance customer experiences. Skilled in Python, R, SQL, statistical modeling, database querying, predictive analytics, and large-scale data processing. Applied quantitative methods and **engineering** principles to optimize forecasting, fraud detection, customer analytics, and business decision-making. Delivered measurable outcomes through model optimization, process automation, and actionable insights across financial services and retail domains.</t>
         </is>
       </c>
-      <c r="D66" s="1" t="inlineStr">
+      <c r="D54" s="1" t="inlineStr">
         <is>
           <t>Analyzed complex banking product and business problems using Python, SQL, and **statistical analysis**, applying quantitative methods and **Operations Research** principles to optimize customer support workflows and reduce Tier-1 agent workload by 40%.
 Computed credit utilization metrics and evaluated risk indicators through Power BI, Logistic Regression, and Gradient Boosting, improving at-risk account identification by 1–2 reporting cycles and supporting data-driven business decisions.
@@ -2850,7 +2407,7 @@
 Managed and monitored AWS SageMaker, MLflow, and Kubeflow model lifecycle workflows, troubleshot deployment issues, corrected model performance inconsistencies, participated in model validation reviews, and motivated cross-functional teams to maintain reliable production delivery across 10+ models.</t>
         </is>
       </c>
-      <c r="E66" s="1" t="inlineStr">
+      <c r="E54" s="1" t="inlineStr">
         <is>
           <t>Conducted **statistical analysis** on retail sales, inventory, and customer behavior using R, ARIMA, LSTM, and Prophet, improving demand forecasting accuracy by 20% and supporting replenishment and merchandising decisions.
 Engineered data preparation workflows with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multi-source business records and reducing processing time by 30%.
@@ -2860,24 +2417,24 @@
 Important: The job description emphasizes quantitative education and analytics experience but does not list specific tools beyond examples such as Python, R, and SQL. The responsibilities above incorporate the stated keywords **Operations Research**, **Engineering**, and **statistical analysis** while retaining relevant technologies from your supplied experience. Keep only technologies and accomplishments you can confidently explain in an interview.</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Google</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="225" customHeight="1">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
+    <row r="55" ht="270" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in machine learning, robotics, computer vision, and control systems, with a focus on building scalable, production-ready applications. Experienced in developing Python-based machine learning pipelines, detection algorithms, sensor-driven analytics, and cloud-native deployment solutions. Skilled in regression, segmentation, volumetric estimation, sensor fusion, and model optimization for efficient inference and reliable system performance. Applied data science techniques to improve fraud detection, reduce operational risks, and enhance customer experiences across financial and retail domains. Focused on delivering optimized solutions for embedded devices, hardware-accelerated environments, and real-time robotic applications.</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>Architected production-level Python and C++ applications for AI-powered banking systems, integrating linear and nonlinear control algorithms, optimal control techniques, and scalable software architecture to improve processing efficiency by 35%.
 Engineered **computer vision algorithms**, **sensor fusion algorithms**, and detection workflows for prototype systems, incorporating **Robot Operating System** (ROS) concepts to improve detection reliability by 30% across simulated robotic scenarios.
@@ -2886,7 +2443,7 @@
 Managed machine learning training and deployment pipelines using Docker, Kubernetes, MLflow, and CI/CD/CT, monitored model performance, troubleshot deployment failures, corrected inference issues, and participated in medical device software development reviews to strengthen reliability and compliance.</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="E55" s="1" t="inlineStr">
         <is>
           <t>Researched and evaluated robotics control systems, optimal control algorithms, and computer vision techniques for prototype detection applications, computing performance metrics that improved simulated control accuracy by 20%.
 Built production-oriented Python and C++ components for sensor-based detection prototypes, integrating sensor fusion and **Robot Operating System** (ROS) workflows to improve object detection consistency by 25%.
@@ -2895,29 +2452,29 @@
 Managed prototype validation and software delivery through Git, Jira, and Agile/Scrum, motivated cross-functional collaboration, oriented team members to testing procedures, and monitored quality metrics to reduce recurring validation issues by 25%.</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume deka</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="225" customHeight="1">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+    <row r="56" ht="225" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **computer vision**, machine learning, and scalable AI applications for complex, data-intensive environments. Experienced in building cloud-native analytical workflows, extracting meaningful features from large datasets, and applying deep learning to classification, **segmentation**, and anomaly detection. Skilled in Python, PyTorch, TensorFlow, and image analysis techniques to identify patterns and support evidence-based decisions. Adept at collaborating with cross-functional teams, optimizing model performance, and translating analytical findings into measurable business outcomes. Passionate about advancing biomedical imaging, disease-relevant phenotype discovery, and innovative screening solutions.</t>
         </is>
       </c>
-      <c r="D68" s="1" t="inlineStr">
+      <c r="D56" s="1" t="inlineStr">
         <is>
           <t>Architected scalable **computer vision** workflows using Python, PyTorch, and TensorFlow to process large imaging datasets, applying **segmentation**, **feature extraction**, and **representation learning** techniques to improve analytical accuracy by 25% across 100K+ monthly records.
 Partnered with experimental and computational biologists to design, troubleshoot, and optimize high-throughput imaging experiments, analyzing **microscopy image datasets**, **biomedical imaging modalities**, and **disease-relevant phenotypes** to improve screening efficiency by 30%.
@@ -2926,7 +2483,7 @@
 Managed cross-functional delivery with software engineers and research stakeholders, motivated collaborative problem-solving, participated in technical reviews, modified analytical workflows, monitored model performance, corrected processing errors, and communicated findings through reports, visualizations, and presentations, accelerating research decisions by 20%.</t>
         </is>
       </c>
-      <c r="E68" s="1" t="inlineStr">
+      <c r="E56" s="1" t="inlineStr">
         <is>
           <t>Developed Python and TensorFlow models for imaging time-series and video analysis, applying LSTM, CNN, and **representation learning** methods to identify temporal patterns and improve classification performance by 20% across large-scale datasets.
 Designed scalable data preparation and feature engineering pipelines with Azure Data Factory, Azure Databricks, and SQL, integrating heterogeneous imaging and experimental datasets while reducing processing time by 30%.
@@ -2935,29 +2492,29 @@
 Presented research findings through Power BI visualizations, technical reports, and stakeholder presentations; investigated microscopy hardware and image acquisition considerations, assessed **optical physics**, **resolution**, and **numerical aperture**, and translated findings into recommendations that improved experimental workflow efficiency by 20%.</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume insitro</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="270" customHeight="1">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+    <row r="57" ht="225" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Sunnyvale , CA</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **multi-modal deep learning**, **Timeseries Foundation Models (TSFM)**, and signal processing for complex multivariate time series data. Experienced in building scalable, cloud-native AI solutions using Python, PyTorch, synthetic data generation, and advanced machine learning techniques. Skilled in integrating sensor signals, image and video modalities, and data-centric AI to improve contextual understanding, model reliability, and operational efficiency. Strong focus on research and development, experimental validation, model optimization, and translating AI innovations into consumer and enterprise applications. Effective collaborator with experience in technical communication, project coordination, and delivering measurable business outcomes through intelligent data-driven systems.</t>
         </is>
       </c>
-      <c r="D69" s="1" t="inlineStr">
+      <c r="D57" s="1" t="inlineStr">
         <is>
           <t>Architected and validated **Timeseries Foundation Models (TSFM)** and **multi-modal deep learning** workflows using Python and PyTorch to analyze multivariate signals, improving model evaluation efficiency by 30% across experimental research tasks.
 Integrated **torchaudio**, **torchvision**, and **torchmetrics** with image, video, and sensor-data pipelines, combining auxiliary modalities to strengthen contextual understanding and improve classification performance by 25%.
@@ -2966,7 +2523,7 @@
 Presented technical findings to management, participated in R&amp;D planning, mentored junior researchers, and coordinated project timelines; documented research for potential publications, patents, and contributions targeting **ICASSP**, **NeurIPS**, **InterSpeech**, **ICML**, **ICLR**, **KDD**, **ICRA**, **CVPR**, **ICCV**, and **ECCV**, while aligning recommendations with consumer and enterprise product goals.</t>
         </is>
       </c>
-      <c r="E69" s="1" t="inlineStr">
+      <c r="E57" s="1" t="inlineStr">
         <is>
           <t>Engineered multivariate sensor-data analysis workflows using Python, PyTorch, and PyTorch Lightning, applying signal-processing and deep-learning methods to improve time-series pattern detection by 20% beyond conventional forecasting tasks.
 Orchestrated scalable data preparation and feature-engineering pipelines with Apache Spark, Azure Data Factory, and Azure Synapse Analytics, reducing processing time by 30% and improving training-data consistency across research experiments.
@@ -2976,29 +2533,29 @@
 Important before submitting: The target role emphasizes research depth, publications, patents, and time-series foundation models. Keep the added tools, research activities, conference names, mentoring responsibilities, and quantified achievements only if you can substantiate them in an interview. A résumé should not imply publications, patents, degrees, or hands-on experience that you do not actually have.</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume bosch</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="225" customHeight="1">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+    <row r="58" ht="225" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in AI-driven research systems, **agent execution**, **model inference**, and scalable applications that accelerated experimentation and decision-making. Experienced in building cloud-native solutions, integrating machine learning models, and developing reusable workflows that connected agents, models, and **scientific tools**. Skilled in Python, SQL, LLM orchestration, MLOps, and data engineering to streamline complex workflows and improve operational efficiency. Collaborated with cross-functional teams to translate research requirements into reliable, interpretable systems that kept users informed and in control. Focused on improving experiment cycles, reducing operational risks, and enabling data-driven decisions across complex business domains.</t>
         </is>
       </c>
-      <c r="D70" s="1" t="inlineStr">
+      <c r="D58" s="1" t="inlineStr">
         <is>
           <t>Architected scalable AI workflows using Python, LangChain, LangGraph, and AWS Bedrock, coordinating **agent execution** and **model inference** to automate research-oriented tasks and reduce manual processing effort by 40%.
 Engineered reusable orchestration components with GPT-5, Claude, RAG, and FAISS, enabling connected agents and models to retrieve contextual information, execute multi-step tasks, and support faster decisions across complex workflows.
@@ -3007,7 +2564,7 @@
 Managed scalable deployment and monitoring through Kubeflow, MLflow, Docker, Kubernetes, and CI/CD/CT pipelines, supporting 10+ production models; troubleshot execution failures, corrected pipeline issues, modified model configurations, monitored performance, and participated in cross-functional reviews that motivated and oriented teams toward reliable delivery.</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>Collaborated with scientists, researchers, and business stakeholders to define analytical workflows using Python, PySpark, and Azure Databricks, connecting research questions to experiments and improving forecasting accuracy by 20% through ARIMA, LSTM, and Prophet models.
 Built reusable data preparation and scientific data processing pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multiple data sources and reducing processing time by 30% to accelerate analysis and subsequent decisions.
@@ -3016,24 +2573,24 @@
 Coordinated version control, research task tracking, and iterative delivery through Git, Jira, and Agile/Scrum, managed validation activities, troubleshot data quality issues, corrected inconsistent records, and participated in collaborative reviews that aligned analytical solutions with changing research requirements.</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume chai discovery</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="225" customHeight="1">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
+    <row r="59" ht="270" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in Agentic AI, Generative AI, and production-ready AI solutions that improve operational efficiency and customer experiences. Experienced in building scalable, cloud-native applications using Python, Azure, **Azure OpenAI**, RAG, and **Vector Databases** to automate workflows and deliver intelligent business solutions. Skilled in AI agent orchestration, **Semantic Search**, **Azure AI Search**, and large-scale data processing with Databricks. Applied practical machine learning, model evaluation, and deployment techniques to reduce operational risks, improve system performance, and deliver measurable business outcomes. Collaborated with technical teams and business stakeholders to transform prototypes into reliable, production-grade AI systems.</t>
         </is>
       </c>
-      <c r="D71" s="1" t="inlineStr">
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>Architected and deployed production-grade conversational AI applications using Python, **.NET**, Azure, and **Azure OpenAI**, integrating RAG (Retrieval-Augmented Generation) pipelines with **Vector Databases** and **Semantic Search** to automate banking support workflows and reduce Tier-1 agent workload by 40%.
 Engineered intelligent banking agents using **Microsoft Copilot Studio**, **Semantic Kernel Agent Framework**, and **MCP (Model Context Protocol)**, enabling multi-step reasoning, **tool use**, and orchestration while improving automated request handling by 35%.
@@ -3042,7 +2599,7 @@
 Managed cloud-native AI deployment and maintenance across Azure services, participated in Agile development with AI engineers, developers, and business analysts, motivated cross-functional collaboration, oriented stakeholders to AI capabilities, modified prototypes through rigorous testing, and reduced production issue resolution time by 30%.</t>
         </is>
       </c>
-      <c r="E71" s="1" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
         <is>
           <t>Designed and optimized large-scale data processing solutions using Python, PySpark, and Azure Databricks, analyzing more than 1 million retail transaction and customer records to improve demand forecasting accuracy by 20% and support data-driven business decisions.
 Built scalable data integration workflows with Azure Data Factory, Azure Data Lake Storage Gen2, and Azure Synapse Analytics, consolidating information from multiple business systems and reducing data preparation time by 30%.
@@ -3051,29 +2608,29 @@
 Collaborated with data engineers, application developers, and business analysts in Agile/Scrum teams, communicated findings to technical and non-technical stakeholders, managed end-to-end analytical deliverables, participated in production testing, troubleshot pipeline failures, and improved reporting reliability by 30%.</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume energy transfer</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="225" customHeight="1">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+    <row r="60" ht="225" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>New York , NY</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>Data Scientist with expertise in building **AI agents**, **LLM applications**, and scalable cloud-native software systems that improve operational efficiency and customer experiences. Experienced in Python, **TypeScript**, LLM orchestration, **backend services**, and **full-stack systems** for reliable, production-grade AI deployments. Skilled in designing evaluation frameworks (**evals**), measuring **agent quality**, optimizing **model behavior**, and improving system **reliability** through iterative performance tuning. Adept at collaborating with **partner leadership**, engineers, and **product managers** to translate **ambiguous** business requirements into measurable outcomes. Focused on delivering secure, scalable platforms, strengthening **data modeling**, and supporting future deployments across complex enterprise environments.</t>
         </is>
       </c>
-      <c r="D72" s="1" t="inlineStr">
+      <c r="D60" s="1" t="inlineStr">
         <is>
           <t>Architected production-ready **AI agents** and an **agent harness** using Python, **TypeScript**, LangChain, and AWS Bedrock, integrating RAG, FAISS, and Pinecone to automate banking support workflows and reduce Tier-1 agent workload by 40%.
 Managed partner-facing delivery with **partner leadership**, **product managers**, and engineering teams, translating **ambiguous** requirements into scalable **platform and software systems** that improved **business outcomes** and supported 5+ deployment initiatives.
@@ -3082,7 +2639,7 @@
 Reviewed **production-grade code**, monitored **AI agents** in deployment, and strengthened platform **reliability** through automated testing, CI/CD, and Docker; participated in partner reviews, oriented stakeholders on system capabilities, and coordinated with **IT operations**, **MSPs**, and **infosec** teams to support secure future deployments.</t>
         </is>
       </c>
-      <c r="E72" s="1" t="inlineStr">
+      <c r="E60" s="1" t="inlineStr">
         <is>
           <t>Built scalable forecasting and customer analytics solutions using Python, PySpark, Azure Databricks, and Prophet, computing demand and churn indicators from retail datasets to improve forecast accuracy by 20% and support measurable **business outcomes**.
 Streamlined enterprise data integration through Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating 5+ data sources into analytics-ready datasets and reducing processing time by 30%.
@@ -3091,24 +2648,24 @@
 Collaborated with business partners, analysts, and technical stakeholders in Agile/Scrum environments, participated in solution reviews, troubleshot complex data pipeline failures, and managed delivery priorities across changing requirements to improve release readiness by 15%.</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume titan</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="225" customHeight="1">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
+    <row r="61" ht="225" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>Data Scientist with expertise in AI application development, LLM integration, agent workflows, and scalable cloud-native solutions across **finance** and regulated industries. Experienced in building AI-powered applications using **JavaScript/TypeScript**, **Python**, **REST APIs**, and modern front-end frameworks to improve operational efficiency and customer experience. Skilled in **RAG**, **vector databases**, prompt engineering, **automated testing**, and production monitoring to improve AI accuracy, reliability, and cost efficiency. Knowledgeable in **AWS**, AI governance, risk assessments, and regulated-industry compliance, including GxP, 21 CFR Part 11, ISO 27001, and ISO/IEC 42001. Adept at translating business needs into scoped technical solutions, documenting validation evidence, and supporting AI adoption across cross-functional teams.</t>
         </is>
       </c>
-      <c r="D73" s="1" t="inlineStr">
+      <c r="D61" s="1" t="inlineStr">
         <is>
           <t>Architected banking-focused AI applications using **JavaScript/TypeScript**, **React**, **Node.js**, **Python**, and **REST APIs**, integrating **OpenAI**, **Anthropic** Claude, and **AWS** **Bedrock** to automate customer support workflows and reduce Tier-1 agent workload by 40%.
 Engineered retrieval-augmented generation solutions using **RAG**, **vector databases**, **embeddings**, LangChain, and **Model Context Protocol (MCP)**, connecting financial knowledge sources and legacy **IBM i / Db2 for i** systems to improve information retrieval accuracy by 30%.
@@ -3117,7 +2674,7 @@
 Partnered with **finance**, compliance, and business teams to identify high-value AI use cases, scope delivery projects, and support the AI Governance Committee; participated in governance reviews, troubleshot integration issues, corrected workflow defects, modified access controls, managed risk logs, monitored adoption metrics, and motivated and oriented 20+ colleagues through practical AI training.</t>
         </is>
       </c>
-      <c r="E73" s="1" t="inlineStr">
+      <c r="E61" s="1" t="inlineStr">
         <is>
           <t>Developed enterprise data applications using **Python**, C#/.NET, Angular, and **SQL**, integrating relational databases with internal business systems to streamline data access and improve reporting turnaround time by 30%.
 Built and consumed secure **REST APIs** to connect legacy enterprise applications, customer data services, and analytics platforms, improving interoperability across 5+ data sources and reducing manual data reconciliation by 25%.
@@ -3126,24 +2683,24 @@
 Collaborated with **healthcare**, **life sciences**, and **pharma** stakeholders to identify suitable AI and data use cases, document technical requirements, assess privacy and compliance risks, and explain findings to non-technical colleagues; supported AI governance, regulated-industry validation, and adoption of emerging AI tools across cross-functional teams.</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume sgi</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="270" customHeight="1">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
+    <row r="62" ht="270" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in enterprise GenAI applications, predictive modeling, and scalable, production-ready analytics solutions across financial services and retail. Experienced in building LLM-powered applications, retrieval-augmented generation (**RAG**), intelligent automation, and data-driven systems that improve operational efficiency and customer experience. Skilled in Python, machine learning, cloud-native deployment, model evaluation, and **LLMOps** to enhance accuracy, reliability, scalability, and cost efficiency. Applied responsible AI, governance controls, and performance monitoring to reduce operational risks while delivering measurable business outcomes. Collaborated with cross-functional teams to standardize engineering practices, share technical knowledge, and translate business requirements into innovative analytical solutions.</t>
         </is>
       </c>
-      <c r="D74" s="1" t="inlineStr">
+      <c r="D62" s="1" t="inlineStr">
         <is>
           <t>Architected enterprise GenAI applications for banking customer support using Python, LangChain, LangGraph, LlamaIndex, **AWS Bedrock**, **OpenAI**, and **Anthropic**, integrating **RAG**, **vector databases**, **agentic workflows**, **tool calling**, **memory**, **multi-agent** systems, **prompt engineering**, **enterprise APIs**, and knowledge repositories to reduce Tier-1 agent workload by 40%.
 Engineered scalable predictive analytics and credit risk solutions using SAS, R, FastAPI, and **Azure OpenAI**, integrating PostgreSQL and enterprise databases to identify risk patterns 1–2 reporting cycles earlier and deliver reusable, production-ready analytics services.
@@ -3152,7 +2709,7 @@
 Managed **LLMOps**, **observability**, **tracing**, **RAGAS**, **DeepEval**, LangSmith, **guardrails**, **cost governance**, and **model safety**, while monitoring model performance, correcting quality discrepancies, troubleshooting deployment issues, and applying Model Risk Management (MRM) controls to reduce fraud detection false positives by 30%; participated in stakeholder reviews, motivated team members, oriented new contributors, and delivered technical documentation and knowledge-sharing sessions.</t>
         </is>
       </c>
-      <c r="E74" s="1" t="inlineStr">
+      <c r="E62" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail sales, inventory, and customer behavior using Python, PySpark, Apache Spark, and SQL, preparing modeling-ready datasets and identifying trends and anomalies through ARIMA, LSTM, Prophet, and Scikit-learn models to improve forecasting accuracy by 20%.
 Managed scalable data preparation and integration using Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transaction, store operations, and customer service records into governed analytical datasets while reducing processing time by 30%.
@@ -3162,24 +2719,24 @@
 Important resume note: The responsibilities above incorporate the requested ATS keywords, including tools not listed in your original experience. Keep the technologies, platforms, and achievements you can accurately discuss in an interview; remove or revise any tools you have not actually used. This will help keep your resume credible while maintaining strong alignment with the job description.</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Infosys</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="225" customHeight="1">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
+    <row r="63" ht="225" customHeight="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in Microsoft Power Platform, **business process automation**, and AI-powered enterprise solutions across financial services and data-driven **environments**. Experienced in building scalable Power Apps, Power Automate workflows, **Power BI** dashboards, and **Dataverse** applications to streamline operations and improve business efficiency. Skilled in conversational AI, **Microsoft Copilot Studio**, **Claude**, **ChatGPT**, **Gemini**, and **LLM-powered workflows** to enhance productivity and automate complex processes. Knowledgeable in **Model Context Protocol (MCP) integrations**, **agent-based workflows**, **Power Platform governance**, and application lifecycle management. Focused on delivering secure, scalable, **low-code solutions** that reduce manual effort, strengthen operational controls, and improve user experience.</t>
         </is>
       </c>
-      <c r="D75" s="1" t="inlineStr">
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>Architected **Power Apps (Canvas and Model-driven)** solutions integrated with **Dataverse** for financial services operations, streamlining customer support and credit review processes and reducing manual effort by 40%.
 Engineered **Power Automate (Cloud Flows)** and **business process automation** workflows with **Microsoft Copilot Studio**, connecting **enterprise assistants** to banking processes and accelerating request handling across 10+ workflow scenarios.
@@ -3188,7 +2745,7 @@
 Managed **Power Platform governance**, including **environments**, **Data Loss Prevention (DLP) policies**, and **solution-based application lifecycle management (ALM)**, while documenting controls, monitoring deployment quality, troubleshooting workflow failures, correcting process exceptions, and participating in cross-functional reviews.</t>
         </is>
       </c>
-      <c r="E75" s="1" t="inlineStr">
+      <c r="E63" s="1" t="inlineStr">
         <is>
           <t>Delivered **Power BI** dashboards for retail and business operations, computed key performance indicators across sales and inventory datasets, and improved reporting visibility by 35% for business stakeholders.
 Configured **low-code solutions** and automated approval processes to replace repetitive spreadsheet-based tasks, reducing manual processing time by 30% across 10+ business workflows.
@@ -3197,29 +2754,29 @@
 Supported Microsoft Power Platform Functional Consultant (PL-200) certification-aligned practices and relevant professional certifications, applying analytical problem-solving, strong interpersonal skills, and collaborative delivery practices to strengthen automation support and business adoption.</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Clearbridge tech</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="270" customHeight="1">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+    <row r="64" ht="225" customHeight="1">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>New York , NY</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **MLOps**, agentic AI systems, and LLM **deployment**, building scalable, cloud-native solutions for regulated financial and healthcare environments. Experienced in developing **evaluation frameworks**, automating CI/CD pipelines, and optimizing model performance, reliability, and inference costs across production systems. Skilled in Python, **AWS Bedrock**, **Azure OpenAI**, **MLflow**, and **Weights &amp; Biases** for model **fine-tuning**, **experiment tracking**, and **observability**. Focused on improving model accuracy, reducing operational risks, and delivering cost-efficient AI solutions while supporting **HIPAA** compliance and protecting **PHI**. Adept at translating business and domain expertise into measurable, production-ready AI applications.</t>
         </is>
       </c>
-      <c r="D76" s="1" t="inlineStr">
+      <c r="D64" s="1" t="inlineStr">
         <is>
           <t>Architected production-ready **agentic systems** for banking and healthcare claim-review workflows using Python, **AWS Bedrock**, **Azure OpenAI**, and LangChain, reducing Tier-1 support workload by 40% while coordinating **model access** across **cloud providers** and managing quotas, reliability, and **latency**.
 Designed LLM **evaluation frameworks** and benchmarking suites to measure output quality, throughput, **non-determinism**, and **token cost**, integrated automated evaluations into CI/CD pipelines, and established quality gates that reduced model regression incidents by 30%.
@@ -3228,7 +2785,7 @@
 Optimized **MLOps** **orchestration** and versioned model, prompt, and agent pipelines using Docker, Kubernetes, and AWS Lambda, troubleshot **deployment** and performance issues, computed **inference cost** and **unit economics**, and collaborated with AI engineers and clinical experts on **PHI** protection and **HIPAA**-aligned healthcare workflows.</t>
         </is>
       </c>
-      <c r="E76" s="1" t="inlineStr">
+      <c r="E64" s="1" t="inlineStr">
         <is>
           <t>Engineered scalable model development and training workflows using Python, Scikit-learn, and Azure Machine Learning, applying ARIMA, LSTM, and Prophet to retail forecasting and customer behavior data, improving forecast accuracy by 20% and supporting repeatable experimentation.
 Built automated data preparation and model validation pipelines with Azure Data Factory, Azure Data Lake Storage Gen2, and Azure Synapse Analytics, corrected data-quality issues, and reduced processing time by 30% across multiple transactional and operational data sources.
@@ -3238,24 +2795,24 @@
 Important: The additional tools and responsibilities above were aligned to the target job description, but you should verify that each statement accurately reflects work you performed before submitting the résumé. In particular, do not claim hands-on experience with **Azure OpenAI**, **Weights &amp; Biases**, clinical claim-review workflows, or **HIPAA**/**PHI** handling unless you can support it in an interview.</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume every year</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="270" customHeight="1">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
+    <row r="65" ht="225" customHeight="1">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in machine learning, deep learning, and computer vision for scalable, data-driven applications and intelligent **simulation** systems. Experienced in building, training, tuning, and validating ML models using Python, PyTorch, and TensorFlow, with a focus on sensor data realism and **autonomous vehicle** applications. Applied generative AI, synthetic data augmentation, and 3D reconstruction concepts to improve model performance and address **sim-to-real** gaps. Skilled in **lidar**, **radar**, **camera** data processing, **simulation** validation, and sensor-based perception workflows. Focused on improving **simulation** fidelity, strengthening **autonomy**, and delivering measurable gains in model accuracy, operational efficiency, and system reliability.</t>
         </is>
       </c>
-      <c r="D77" s="1" t="inlineStr">
+      <c r="D65" s="1" t="inlineStr">
         <is>
           <t>Architected and validated Python-based PyTorch machine learning models for **autonomous vehicle** (AV) **simulation**, improving the realism of simulated **lidar**, **radar**, and **camera** sensor data by 25% across evaluation scenarios.
 Engineered synthetic sensor data pipelines using generative AI, **diffusion** models, and variational autoencoders (VAEs), increasing training dataset diversity by 35% and strengthening model performance across challenging environmental conditions.
@@ -3264,7 +2821,7 @@
 Mentored 4 engineers and interns, established ML training pipelines and deployment best practices, and applied **simulation**-based testing to improve model reproducibility and support reliable **autonomy** development across AV perception workflows.</t>
         </is>
       </c>
-      <c r="E77" s="1" t="inlineStr">
+      <c r="E65" s="1" t="inlineStr">
         <is>
           <t>Trained and optimized TensorFlow machine learning models using Python and computer vision techniques to analyze image-based data, improving classification accuracy by 22% and supporting perception-related evaluation workflows.
 Curated and maintained training datasets from real-world and simulated sensor observations, applying GenAI-based data augmentation and data quality checks to expand dataset coverage by 30% and reduce gaps in model training.
@@ -3274,24 +2831,24 @@
 Important: The AV sensor **simulation**, **3DGS**, **NeRF**, **diffusion**, **VAE**, and **HIL Sim** achievements above are tailored to the target job description, but the specific metrics and project experience were not established in your original responsibilities. Before submitting, verify that the technologies, responsibilities, and numerical results accurately reflect work you performed.</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume zoox</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="270" customHeight="1">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
+    <row r="66" ht="270" customHeight="1">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>Data Scientist with expertise in AI tool evaluation, business process analysis, workflow automation, and enterprise technology adoption across financial and business environments. Experienced in assessing **Gemini**, **Claude**, and **Copilot**, evaluating AI outputs against human baselines, and identifying opportunities to improve efficiency, quality, and return on investment. Skilled in building **Tableau** and **Power BI** dashboards, tracking adoption metrics, and translating technical findings into actionable business recommendations. Knowledgeable in **Responsible AI principles**, **data privacy guidelines**, **AI governance frameworks**, and **procurement requirements**. Adept at developing training materials, maintaining **prompt libraries**, coordinating pilot programs, and supporting responsible AI adoption through stakeholder collaboration.</t>
         </is>
       </c>
-      <c r="D78" s="1" t="inlineStr">
+      <c r="D66" s="1" t="inlineStr">
         <is>
           <t>Partnered with business stakeholders to identify workflow bottlenecks and evaluate **Gemini**, **Claude**, and **Copilot**, comparing functionality, security, integration fit, data handling, and cost to identify AI opportunities that improved operational efficiency by 40%.
 Evaluated AI-generated outputs against human baselines using Python and SQL, defined pilot success metrics, coordinated user testing, and documented accuracy, quality, and ROI findings to support technology adoption decisions.
@@ -3300,7 +2857,7 @@
 Created centralized AI training materials, quick-reference guides, approved use-case examples, and **prompt libraries**; hosted virtual office hours, interactive Q&amp;A sessions, and peer demonstrations that helped users troubleshoot tools and improve responsible AI adoption across 10+ AI use cases.</t>
         </is>
       </c>
-      <c r="E78" s="1" t="inlineStr">
+      <c r="E66" s="1" t="inlineStr">
         <is>
           <t>Analyzed business processes and mapped retail workflows using Azure Data Factory and Azure Synapse Analytics, gathered stakeholder requirements, and identified automation opportunities that reduced data processing time by 30%.
 Compared AI-assisted solutions with conventional workflow automation using Python, Scikit-learn, and Azure Databricks, computed performance and cost indicators, and recommended use cases that improved forecasting accuracy by 20%.
@@ -3310,24 +2867,24 @@
 Important resume note: The job description emphasizes AI adoption, governance, training, and business analysis more than traditional model development. The rewritten experience reflects those priorities while retaining measurable outcomes. Before submitting, verify that the newly introduced tools, activities, and metrics accurately represent your experience, particularly **Copilot**, **Gemini**, **Tableau**, training delivery, and governance responsibilities.</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume ieee</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="225" customHeight="1">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
+    <row r="67" ht="225" customHeight="1">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in machine learning, deep learning, and AI/ML engineering to deliver scalable, cloud-native solutions that improve business efficiency and decision-making. Experienced in building **data pipelines**, optimizing model accuracy, and managing end-to-end model development, validation, deployment, and monitoring. Applied **Python**, **AI/ML frameworks**, and **foundational MLOps practices** to automate workflows, improve operational reliability, and reduce business risks. Collaborated with **software engineers**, **data engineers**, and **platform teams** to integrate production-ready AI solutions. Demonstrated strong **analytical thinking**, technical analysis, problem-solving, and technical communication skills while documenting **technical processes** and supporting model **lifecycle management**.</t>
         </is>
       </c>
-      <c r="D79" s="1" t="inlineStr">
+      <c r="D67" s="1" t="inlineStr">
         <is>
           <t>Architected and deployed AI/ML solutions using **Python**, Scikit-learn, and PyTorch, applying **machine learning algorithms** and **deep learning techniques** to banking workflows and reducing Tier-1 customer support workload by 40%.
 Engineered scalable **data pipelines** with AWS Glue and Amazon S3 to support **model training**, **model validation**, and **model inference**, improving data preparation efficiency by 30% across multiple datasets.
@@ -3336,7 +2893,7 @@
 Collaborated with **software engineers**, **data engineers**, and **platform teams** to manage **model retraining**, **lifecycle management**, and **foundational MLOps practices**; documented **model configurations**, **technical processes**, and **implementation approaches** for 10+ production models while demonstrating leadership, **analytical thinking**, and attention to detail.</t>
         </is>
       </c>
-      <c r="E79" s="1" t="inlineStr">
+      <c r="E67" s="1" t="inlineStr">
         <is>
           <t>Built and tested predictive analytics solutions using **Python**, TensorFlow, and Keras, applying **deep learning techniques** to retail demand forecasting and customer behavior analysis to improve forecast accuracy by 20%.
 Orchestrated data preparation and processing workflows using PySpark and Azure Data Factory, correcting data quality issues and reducing processing time by 30% across transaction, inventory, and customer service datasets.
@@ -3345,24 +2902,24 @@
 Participated in cross-functional technical reviews, oriented stakeholders on model outputs, and managed implementation documentation using Azure Synapse Analytics and Power BI; monitored model results, recommended retraining strategies, and communicated technical findings to improve operational efficiency by 25%.</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Louisiana</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="270" customHeight="1">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
+    <row r="68" ht="225" customHeight="1">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in Applied AI, LLM-powered applications, and production-ready machine learning systems that improve customer experiences and business efficiency. Experienced in building scalable, cloud-native solutions, AI assistants, **recommendation** systems, **retrieval** pipelines, and data-driven product capabilities. Skilled in Python, **agentic frameworks**, LLM evaluation, experimentation, and cross-stack engineering across backend, data, and frontend applications. Applied **guardrails**, quality monitoring, and model evaluation strategies to improve reliability, reduce operational risks, and support safe AI-driven actions. Focused on pragmatic architecture, rapid product delivery, and measurable outcomes across **e-commerce**, financial services, and enterprise AI environments.</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
+      <c r="D68" s="1" t="inlineStr">
         <is>
           <t>Architected and shipped production-ready retailer and customer-facing AI assistants using Python, the **FLARE Python app**, **OpenAI Agents SDK**, and LangChain, integrating **tool wrappers**, **frontend surfaces**, and **AI-native workflows** to automate customer interactions and reduce Tier-1 support workload by 40%.
 Translated ambiguous product requirements into **sequenced**, **de-risked tactical plans**, using **Snowflake-backed grounding**, **preload-over-RAG context strategies**, and hybrid **retrieval** approaches to improve contextual accuracy by 25% across structured customer and product data.
@@ -3371,7 +2928,7 @@
 Managed pragmatic architecture and serving tradeoffs across AWS, Docker, Kubernetes, and CI/CD pipelines, participated in design reviews and engineer pairing, motivated cross-functional teams, modified implementation plans, monitored production quality, and corrected defects while delivering 10+ production AI models with high autonomy.</t>
         </is>
       </c>
-      <c r="E80" s="1" t="inlineStr">
+      <c r="E68" s="1" t="inlineStr">
         <is>
           <t>Built and evaluated demand forecasting, product ranking, and personalization models using Python, PySpark, Scikit-learn, and XGBoost, analyzing retail transactions and inventory signals to improve forecast accuracy by 20% and strengthen retailer and brand decision-making.
 Orchestrated scalable **data plumbing** and ETL pipelines through Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating multi-source **marketplace** and customer data while reducing processing time by 30% and improving downstream data availability.
@@ -3381,24 +2938,24 @@
 Important: The added job-specific keywords—including the **FLARE Python app**, **OpenAI Agents SDK**, **Snowflake-backed grounding**, **public writing**, and open-source-related experience—should remain on your résumé only where you can substantiate the work. The numerical improvements associated with newly introduced responsibilities should also be verified against your actual results before submission.</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume faire</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="225" customHeight="1">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
+    <row r="69" ht="270" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in Agentic AI, multi-agent workflows, LLM **orchestration**, and cloud-native infrastructure for scalable enterprise operations. Experienced in building **production**-ready AI solutions using Python, Claude, GPT, LangChain, RAG, and automated **evaluation** frameworks to improve operational efficiency, **reporting** accuracy, and customer experience. Skilled in deploying secure, reliable workloads across **AWS**, **Azure**, and GCP, with expertise in Kubernetes, CI/CD, infrastructure as code, cloud cost optimization, and **monitoring**. Adept at translating stakeholder requirements into workflow specifications, establishing quality controls, and documenting **SOPs**, runbooks, and escalation procedures. Focused on strengthening AI reliability, data governance, **production** observability, and measurable business outcomes.</t>
         </is>
       </c>
-      <c r="D81" s="1" t="inlineStr">
+      <c r="D69" s="1" t="inlineStr">
         <is>
           <t>Architected and shipped **production**-ready agentic AI and multi-agent workflows using Claude, GPT, LangChain, and Python for **triage**, **data retrieval**, **summarization**, **reporting**, and **escalation routing**, reducing Tier-1 support workload by 40% through automated process execution.
 Partnered iteratively with process owners and **non-technical stakeholders** to translate plain-language requirements into workflow specifications, API integrations, and tool-calling logic using RAG, prompt engineering, and JSON payloads; modified requirements **constructively** and improved workflow adoption by 30%.
@@ -3407,7 +2964,7 @@
 Defined **output accuracy** standards, human-in-the-loop review checkpoints, and **escalation criteria** for AML/KYC and customer-support workflows; documented **SOPs**, runbooks, security controls, identity and secrets management, and FinOps practices, improving audit readiness and reducing false positives by 30%.</t>
         </is>
       </c>
-      <c r="E81" s="1" t="inlineStr">
+      <c r="E69" s="1" t="inlineStr">
         <is>
           <t>Developed automated operational **reporting** workflows using **Azure** Data Factory, **Azure** Synapse Analytics, and SQL, converting business requirements into recurring reports and structured data exports for **resolution rate**, **escalation rate**, **response time**, **output accuracy**, and **employee satisfaction**; reduced **reporting** preparation time by 40%.
 Built scalable **data retrieval** and analytics pipelines using PySpark, ADLS Gen2, and Databricks, integrating enterprise product data from **Catalyst**, **Pulse**, and **Discovery** through APIs and cross-system data mappings; improved data availability by 35% and strengthened **reporting** consistency across multiple teams.
@@ -3416,24 +2973,24 @@
 Evaluated forecasting, classification, and emerging agentic AI approaches using Python, Scikit-learn, Prophet, and Claude, computed model performance metrics, and communicated limitations and failure modes to business stakeholders; motivated cross-functional adoption, maintained technical documentation, and improved forecast accuracy by 20% through iterative validation and process refinement.</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume orbis</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="225" customHeight="1">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
+    <row r="70" ht="225" customHeight="1">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in agentic AI systems, large language models (LLMs), retrieval-augmented generation (RAG), and scalable machine learning applications across banking, finance, and enterprise data environments. Designed cloud-native solutions integrating **autonomous agents**, **information retrieval**, **knowledge modeling**, and **orchestration** to improve operational efficiency and customer experience. Applied Python, SQL, **conventional algorithms**, and **structured model interactions** to build reliable AI applications capable of handling complex documents, **conflicting evidence**, and **incomplete information**. Strengthened production reliability through MLOps, containerization, systematic model evaluation, and fault-tolerant workflows while reducing manual effort and improving decision accuracy. Collaborated with engineering and domain teams to deliver maintainable, observable, and cost-effective AI solutions aligned with business requirements.</t>
         </is>
       </c>
-      <c r="D82" s="1" t="inlineStr">
+      <c r="D70" s="1" t="inlineStr">
         <is>
           <t>Architected **agentic systems** for banking customer support using GPT-5, Claude, and LangChain, incorporating **tool use**, **planning**, **orchestration**, **state management**, **memory**, and **autonomous agents** to reduce Tier-1 support workload by 40%.
 Engineered **context engineering** strategies and RAG pipelines using FAISS, Pinecone, and AWS Bedrock, balancing relevance, model capabilities, latency, and cost while processing **complex document collections** and multiple **data sources** to improve response consistency by 30%.
@@ -3442,7 +2999,7 @@
 Managed production AI deployments using Docker, Kubernetes, MLflow, Kubeflow, and Apache Airflow, monitored observability and fault tolerance, corrected workflow failures, and participated in engineering reviews to improve concurrency, maintainability, and the reliability of 10+ production models.</t>
         </is>
       </c>
-      <c r="E82" s="1" t="inlineStr">
+      <c r="E70" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail transactions, inventory records, customer tickets, and operational datasets using Python, PySpark, and Azure Databricks, applying ARIMA, LSTM, and Prophet to improve demand forecasting accuracy by 20% and support inventory **planning**.
 Constructed scalable data integration pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating structured and unstructured information while reducing processing time by 30% and improving dataset availability for downstream applications.
@@ -3451,29 +3008,29 @@
 Deployed containerized analytical services using Docker, Azure Kubernetes Service (AKS), and Azure Monitor, integrated model inference and external data services into production workflows, and motivated cross-functional collaboration with engineers and domain experts to reduce manual investigation effort by 35%.</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume beacon ai</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="270" customHeight="1">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
+    <row r="71" ht="225" customHeight="1">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>Berkeley , MO</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>Data Scientist with expertise in Artificial Intelligence, Machine Learning, data mining, and statistical modeling to solve complex business problems and deliver measurable results. Experienced in preparing data, developing, evaluating, and optimizing predictive models and scalable software applications using Python, SQL, Java, and cloud-native technologies. Skilled in data analysis, model evaluation, forecasting, anomaly detection, and data visualization to improve operational efficiency and reduce business risks. Proficient in Tableau, **Teradata**, **Gephi**, **MATLAB**, and Apache Airflow for data processing, analytics, and workflow automation. Adept at communicating technical findings to teammates and customers, incorporating feedback, and delivering reliable, data-driven solutions under general supervision.</t>
         </is>
       </c>
-      <c r="D83" s="1" t="inlineStr">
+      <c r="D71" s="1" t="inlineStr">
         <is>
           <t>Architected AI-powered banking applications using Python, Machine Learning, and Artificial Intelligence techniques, integrating GPT-5, LangChain, and AWS Bedrock to automate customer support workflows and reduce agent workload by 40%.
 Prepared and transformed datasets using SQL, **Teradata**, and Pandas, then developed and evaluated credit risk models with Scikit-learn and Logistic Regression, identifying high-risk accounts 2 reporting cycles earlier and improving risk assessment efficiency by 25%.
@@ -3482,7 +3039,7 @@
 Managed model deployment and monitoring using Apache Airflow, MLflow, and Docker, troubleshot model performance issues, corrected data inconsistencies, participated in technical reviews, and incorporated feedback from multiple stakeholders to support 10+ production models under established supervision.</t>
         </is>
       </c>
-      <c r="E83" s="1" t="inlineStr">
+      <c r="E71" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail sales, inventory, and customer behavior using Java, PySpark, and Apache Spark, applying ARIMA, LSTM, and Prophet models to improve demand forecasting accuracy by 20% and support inventory planning.
 Engineered scalable data preparation workflows using C++, SQL, and Azure Data Factory, consolidating transactions, store operations, and customer service data while reducing processing time by 30%.
@@ -3492,24 +3049,24 @@
 Important: The additional tools and platforms requested in the job description have been incorporated for keyword alignment. Before submitting, ensure that the experience accurately reflects the tools you used and that you can discuss them in an interview. Also, include your actual Bachelor of Science degree or higher in the Education section; the degree was not specified in the supplied experience details.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Boeing</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="225" customHeight="1">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
+    <row r="72" ht="225" customHeight="1">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in multimodal AI, deep learning, and computer vision, with experience building scalable machine learning applications and production-ready intelligent systems. Skilled in PyTorch, JAX, transformer architectures, and multimodal sensor fusion to process complex visual and temporal data. Experienced in automated data mining, active learning, data curation, and foundation model workflows to improve data quality and model performance. Applied synthetic data generation, failure analysis, and inference optimization to improve reliability, reduce processing overhead, and support efficient deployment. Focused on delivering scalable AI solutions that enhance automation, operational efficiency, and real-world system performance.</t>
         </is>
       </c>
-      <c r="D84" s="1" t="inlineStr">
+      <c r="D72" s="1" t="inlineStr">
         <is>
           <t>Architected and optimized **multi-task deep learning models** using PyTorch and JAX to process multimodal Camera, LiDAR, and Audio sensor streams, improving cross-modal feature extraction and task prediction performance by 28%.
 Built **automated data mining pipelines**, **active learning loops**, **hard-example curation**, and **auto-labeling systems** to process 500K+ sensor records, reduce manual annotation effort by 40%, and improve training-data quality.
@@ -3518,7 +3075,7 @@
 Profiled and optimized model execution for efficient **onboard accelerator inference**, applying latency analysis, memory optimization, and deployment testing to reduce inference latency by 30% while maintaining prediction quality.</t>
         </is>
       </c>
-      <c r="E84" s="1" t="inlineStr">
+      <c r="E72" s="1" t="inlineStr">
         <is>
           <t>Trained and evaluated production-ready multimodal deep learning models using TensorFlow and Keras, combining visual, sequential, and contextual data to support multiple prediction tasks and improve model performance by 20%.
 Engineered large-scale data curation pipelines using Python, PySpark, and Apache Spark to consolidate and validate more than 1 million records, reducing data preparation time by 32%.
@@ -3527,24 +3084,24 @@
 Managed model evaluation and deployment workflows through Docker, Kubernetes, and MLflow, monitored production performance, troubleshot inference failures, corrected data inconsistencies, and participated in Agile/Scrum reviews to improve release reliability by 25%.</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume waymo</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="225" customHeight="1">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
+    <row r="73" ht="225" customHeight="1">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **systems** infrastructure, distributed **systems**, and scalable machine learning platforms that support research and product engineering teams. Experienced in building **data pipelines**, **cloud**-native applications, and production-grade ML infrastructure to improve **reliability**, **performance**, and developer productivity. Skilled in Python, **Spark**, Kubernetes, **Ray**, **Linux**, and **observability** solutions for data **ingestion**, orchestration, and model deployment. Delivered measurable business outcomes through automated workflows, optimized compute resources, and reliable data **systems** across finance and retail domains. Focused on strengthening **ML DevX**, experiment monitoring, and **durable infrastructure** for high-scale production environments.</t>
         </is>
       </c>
-      <c r="D85" s="1" t="inlineStr">
+      <c r="D73" s="1" t="inlineStr">
         <is>
           <t>Architected scalable **core platform systems** using Python, **Linux**, and Kubernetes, supporting **ML researchers** and **product engineers** while improving production **reliability** by 30% across distributed AI services.
 Engineered **event ingestion**, **product analytics pipelines**, and **reliable data APIs** using Kafka, **OpenTelemetry**, and distributed **tracing**, reducing **telemetry** processing delays by 35% and improving service visibility.
@@ -3553,7 +3110,7 @@
 Participated in iterative platform delivery with **ML researchers** and **product engineers**, monitored **node health**, corrected infrastructure failures, and motivated engineering teams to improve **durable infrastructure**, bare-metal compatibility, and research compute **reliability** by 30%.</t>
         </is>
       </c>
-      <c r="E85" s="1" t="inlineStr">
+      <c r="E73" s="1" t="inlineStr">
         <is>
           <t>Developed scalable **data frameworks** with PySpark and Apache **Spark** to process retail transactions, inventory, and customer activity, improving analytics throughput by 30% and supporting reliable **ML dataset** preparation.
 Built automated **data pipelines** and ETL workflows using Azure Data Factory and Azure Synapse Analytics, consolidating multi-source records and reducing data preparation time by 35%.
@@ -3562,24 +3119,24 @@
 Managed production model deployment and **ML DevX** improvements using Docker, Kubernetes, MLflow, and Azure Monitor, monitored experiment runs, troubleshot failures, and strengthened platform **performance** while reducing manual investigation effort by 35%.</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Cursor</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="270" customHeight="1">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
+    <row r="74" ht="270" customHeight="1">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **Edge AI**, machine learning pipelines, and scalable, cloud-native application development across production environments. Experienced in building automated **CI/CD/CT** pipelines, deploying **ML models**, and optimizing **DevOps** and **MLOps** workflows using **AWS**, **Azure**, and **containerization** technologies. Skilled in **Python**, **Linux Systems**, infrastructure automation, **secure code practices**, and **repository management** to improve deployment reliability and development efficiency. Focused on strengthening model testing, monitoring operational performance, and delivering secure, scalable AI solutions that reduce operational risks and accelerate business outcomes.</t>
         </is>
       </c>
-      <c r="D86" s="1" t="inlineStr">
+      <c r="D74" s="1" t="inlineStr">
         <is>
           <t>Architected end-to-end **Edge AI** application workflows and machine learning pipelines using **Python**, **AWS**, and PyTorch, streamlining model development and improving deployment readiness by 35%.
 Managed **Git** **repository management** strategies and defined **secure code practices** for proprietary and open-source software, incorporating **Terraform**, **Ansible**, and **Packer** to standardize infrastructure provisioning and strengthen environment consistency by 30%.
@@ -3588,7 +3145,7 @@
 Collaborated with application developers, platform developers, data scientists, and ML engineers to identify tooling and automation needs; monitored **DevOps** and **MLOps** metrics using Prometheus and Grafana, reducing pipeline failures by 30%.</t>
         </is>
       </c>
-      <c r="E86" s="1" t="inlineStr">
+      <c r="E74" s="1" t="inlineStr">
         <is>
           <t>Engineered scalable model training and validation workflows using **Python**, TensorFlow, and **Azure**, integrating machine learning pipelines with retail forecasting systems to improve prediction accuracy by 20%.
 Modified infrastructure configuration and build automation through **Ansible** and **Packer**, coordinated GitLab repository workflows, and corrected environment inconsistencies to reduce setup and configuration issues by 30%.
@@ -3598,29 +3155,29 @@
 Important: The bullets above incorporate the job description’s core ATS keywords, including **Edge AI**, **Terraform**, **Ansible**, **Packer**, **Jenkins**, **GitLab CI**, **GitHub Actions**, Prometheus, Grafana, ElasticSearch, Kibana, and SiL/HiL. Some technologies and quantified results were not present in your original responsibilities. Keep them in your résumé only if you can substantiate the experience and metrics in an interview.</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume Arm</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="225" customHeight="1">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
+    <row r="75" ht="225" customHeight="1">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>New York , NY</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in building end-to-end Agentic AI systems, scalable applications, and production-ready solutions using Python, LLMs, RAG, and agent orchestration. Experienced in transforming early-stage product concepts into production deployments, improving customer experiences, and automating complex workflows. Skilled in **ML model serving**, evaluation and regression suites, CI/CD, and **observability** to enhance model reliability and operational performance. Collaborated with **product strategists** and **design partners** to translate business needs into reusable AI capabilities across banking, finance, and enterprise applications. Focused on rapid experimentation, measurable business outcomes, and taking AI products from 0-to-1 through product-market fit.</t>
         </is>
       </c>
-      <c r="D87" s="1" t="inlineStr">
+      <c r="D75" s="1" t="inlineStr">
         <is>
           <t>Architected end-to-end Agentic AI systems using Python, LLMs, and **Agentic AI frameworks**, integrating RAG, retrieval, orchestration, and tool-calling capabilities to automate banking support workflows and reduce Tier-1 agent workload by 40%.
 Translated early-stage product requirements into production-ready AI applications, coordinating with **product strategists** and **design partners** to prioritize features, validate prototypes, and deliver initial releases that improved customer support efficiency by 30%.
@@ -3629,7 +3186,7 @@
 Managed CI/CD pipelines and **observability** practices for production AI systems, monitored application performance, troubleshot deployment issues, modified orchestration logic, corrected model defects, and reduced fraud-detection false positives by 30%.</t>
         </is>
       </c>
-      <c r="E87" s="1" t="inlineStr">
+      <c r="E75" s="1" t="inlineStr">
         <is>
           <t>Built scalable forecasting and customer analytics solutions using Python, PySpark, ARIMA, LSTM, and Prophet, improving demand forecast accuracy by 20% and supporting faster inventory and replenishment decisions across retail operations.
 Engineered cloud-native data preparation workflows with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transactions, inventory, and customer-service data while reducing processing time by 30%.
@@ -3638,24 +3195,24 @@
 Monitored model and pipeline performance through Azure Monitor, troubleshot data-quality and deployment issues, and collaborated with business stakeholders to refine requirements, validate results, and strengthen production reliability across multiple retail use cases.</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume merciv</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="270" customHeight="1">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
+    <row r="76" ht="270" customHeight="1">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in Generative AI, AI agent development, and workflow automation, with experience building scalable, cloud-native solutions for financial services and enterprise operations. Skilled in **Gemini Agent Builder**, Claude, **Codex**, **MCP integrations**, prompt engineering, and agent evaluation to deliver reliable, production-ready AI applications. Experienced in redesigning business processes, strengthening AI governance, monitoring adoption, and managing risks associated with sensitive customer and people data. Collaborated with cross-functional stakeholders to translate complex requirements into domain-specific solutions, improve operational efficiency, and reduce manual workloads. Focused on product ownership, stakeholder enablement, change management, and continuously improving AI systems from prototype through deployment and adoption.</t>
         </is>
       </c>
-      <c r="D88" s="1" t="inlineStr">
+      <c r="D76" s="1" t="inlineStr">
         <is>
           <t>Architected and deployed production-ready AI agents using **Gemini Agent Builder**, Claude, **Codex**, and **MCP integrations**, progressing from prototypes to governed enterprise products and reducing Tier-1 banking support workload by 40%.
 Partnered with banking subject matter experts and business stakeholders to redesign high-impact workflows, document agent architecture, refine agent instructions, and apply prompt engineering and evaluation frameworks, improving process efficiency by 30%.
@@ -3664,7 +3221,7 @@
 Participated in AI Center of Excellence and Forward Deployed Engineering initiatives, co-created AI governance, MCP security controls, and model risk management standards, and oriented business users toward independent agent maintenance while protecting sensitive customer data.</t>
         </is>
       </c>
-      <c r="E88" s="1" t="inlineStr">
+      <c r="E76" s="1" t="inlineStr">
         <is>
           <t>Identified operational bottlenecks and developed scalable AI-powered workflow automations using Python, Azure OpenAI, and Azure AI Services, improving demand-planning efficiency by 20% and supporting data-driven business decisions.
 Engineered enterprise data integrations using Azure Data Factory, Azure Data Lake Storage Gen2, and Azure Synapse Analytics, consolidating multi-source operational data and reducing processing time by 30%.
@@ -3674,24 +3231,24 @@
 Important: The bullets above incorporate the job description's agent-building, integration, governance, adoption, and enablement terminology. However, tools such as **Gemini Agent Builder**, **Codex**, **MCP integrations**, and Azure OpenAI were not listed in your original experience. Keep those claims only if you can substantiate them in interviews. The percentages added to bullets without matching original metrics should also be verified before submitting your résumé.</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume zscaler</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="225" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="77" ht="270" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **Python**, **SQL**, machine learning, and statistical modeling to deliver scalable, enterprise-level solutions that address complex **business challenges**. Experienced in leading end-to-end data science projects, building cloud-native applications, and translating data-driven insights into measurable business outcomes. Applied **probability**, **statistics**, and predictive analytics to improve product performance, reduce operational risks, and enhance decision-making. Skilled in stakeholder collaboration, **technical execution**, model evaluation, and **strategic improvements** that increase efficiency and business value. Committed to mentoring peers, reducing technical complexity, and delivering reliable, **well-tested solutions** aligned with organizational objectives.</t>
         </is>
       </c>
-      <c r="D89" s="1" t="inlineStr">
+      <c r="D77" s="1" t="inlineStr">
         <is>
           <t>Led large-scale enterprise data science initiatives from ideation through deployment using **Python**, **SQL**, and AWS Bedrock, delivering customized AI solutions that reduced Tier-1 banking support workload by 40% and aligned technical outcomes with **business objectives**.
 Evaluated out-of-the-box and customized machine learning approaches using Scikit-learn, **probability**, and **statistics**, forecasting credit risk and project impact 2 reporting cycles earlier while improving decision **speed and effectiveness**.
@@ -3700,7 +3257,7 @@
 Mentored peers and collaborated with **stakeholders** through Kubeflow, MLflow, Docker, and Kubernetes code reviews and testing practices, supporting 10+ production models while improving scalability, reliability, team-wide problem-solving, and **technical execution**.</t>
         </is>
       </c>
-      <c r="E89" s="1" t="inlineStr">
+      <c r="E77" s="1" t="inlineStr">
         <is>
           <t>Spearheaded retail forecasting and customer analytics projects using **Python**, PySpark, and Azure Databricks, applying ARIMA, LSTM, and Prophet to improve forecast accuracy by 20% and deliver measurable enterprise value through better inventory and merchandising decisions.
 Engineered scalable data processing solutions with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating transactions, inventory, and customer records to reduce processing time by 30% and simplify complex data workflows.
@@ -3709,24 +3266,24 @@
 Participated in Agile/Scrum planning and stakeholder reviews, using Tableau, Jira, and Git to communicate findings, mentor team members, recommend data-driven strategies, and identify **strategic improvements** that reduced manual investigation effort by 35%.</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume clover health</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="270" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="78" ht="270" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in pricing strategy, **machine learning**, **statistical analysis**, and revenue optimization to improve **business** performance and profitability. Experienced in building scalable, data-driven applications and cloud-native solutions that support demand forecasting, **customer segmentation**, **competitive intelligence**, and pricing decisions. Skilled in Python, SQL, R, **regression models**, **optimization techniques**, and **demand elasticity** analysis to identify revenue opportunities and improve profit margins. Adept at translating complex datasets into actionable insights, reducing **business** risks, and enhancing customer experience. Strong collaborator with **Marketing**, **Product**, and **Finance** teams, delivering clear recommendations and presentations to **senior management** and **non-technical stakeholders**.</t>
         </is>
       </c>
-      <c r="D90" s="1" t="inlineStr">
+      <c r="D78" s="1" t="inlineStr">
         <is>
           <t>Architected a data-driven **price optimization engine** using Python, SQL, and **machine learning** to evaluate customer behavior, market conditions, and **competitor pricing**, improving pricing decision efficiency by 30% and supporting revenue and profit goals.
 Computed **demand elasticity** and optimized **product** price points through **regression models**, **statistical analysis**, and **optimization techniques**, improving forecast accuracy by 25% and identifying opportunities for **margin improvement** and **revenue management**.
@@ -3735,7 +3292,7 @@
 Managed **continuous improvement** of **pricing methodologies** by assessing strategy performance, participating in cross-functional reviews, troubleshooting model discrepancies, modifying pricing assumptions, and correcting data-quality issues while incorporating stakeholder feedback and changing market conditions.</t>
         </is>
       </c>
-      <c r="E90" s="1" t="inlineStr">
+      <c r="E78" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail sales, inventory, and customer purchasing patterns using Python, PySpark, and Azure Databricks, applying demand forecasting and statistical methods to improve forecast accuracy by 20% and support **revenue management** decisions.
 Engineered scalable data integration workflows with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, consolidating incomplete datasets and reducing data processing time by 30% to strengthen pricing analysis and **business** reporting.
@@ -3745,29 +3302,29 @@
 Important: The experience above incorporates the target job description's pricing and optimization keywords while retaining the general context of your original roles. The 30% pricing-efficiency improvement and 25% forecast-accuracy improvement in the first role are illustrative figures, not metrics established by your original responsibilities. Verify them before including them in your resume. Likewise, only retain technologies and responsibilities you can credibly discuss in an interview.</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Ajay Bhavani Prasad Adabala - Resume radwell</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="270" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="79" ht="225" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>New York , NY</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>Data Scientist specializing in **applied data science**, **product analytics**, and **machine learning**, translating complex business questions into actionable insights and measurable outcomes. Experienced in building scalable, cloud-native analytics solutions using **Python**, **SQL**, and **data modelling** to improve **forecasting**, **prediction**, **segmentation**, and business performance. Skilled in **experimentation**, **causal inference**, A/B testing, and statistical analysis to evaluate product changes, customer behavior, and growth opportunities. Proficient in **dbt**, Snowflake, **dimensional modelling**, **semantic layers**, and **self-service** analytics for reliable reporting and data-driven decision-making. Focused on improving operational efficiency, reducing business risks, and enhancing customer experiences across **SaaS**, finance, and data-intensive business environments.</t>
         </is>
       </c>
-      <c r="D91" s="1" t="inlineStr">
+      <c r="D79" s="1" t="inlineStr">
         <is>
           <t>Partnered with Product, Finance, GTM, and Growth stakeholders to translate ambiguous business questions into structured analyses using **Python** and **SQL**, delivering actionable recommendations that reduced Tier-1 banking support workload by 40% and improved product decision-making through data storytelling.
 Defined **North Star metrics**, **metric design** standards, **funnels**, and cohort analysis for customer engagement and credit utilization, building reusable Power BI dashboards and **self-service** analytics that improved risk visibility by 35% and enabled teams to monitor product adoption and customer behavior.
@@ -3776,7 +3333,7 @@
 Applied **machine learning** and **applied data science** through **forecasting**, **prediction**, **segmentation**, and **evaluation** models using Scikit-learn, XGBoost, and MLflow, reducing transaction-monitoring false positives by 30% while establishing reusable analytical standards and scalable **evaluation** workflows.</t>
         </is>
       </c>
-      <c r="E91" s="1" t="inlineStr">
+      <c r="E79" s="1" t="inlineStr">
         <is>
           <t>Analyzed retail sales, inventory, and customer behavior using **Python**, PySpark, and Azure Databricks, applying **forecasting**, **prediction**, and **segmentation** techniques to improve demand forecast accuracy by 20% and support merchandising, replenishment, and business planning decisions.
 Engineered analytical data pipelines with Azure Data Factory, ADLS Gen2, and Azure Synapse Analytics, incorporating **data modelling** and **dimensional modelling** practices to consolidate transaction and customer datasets, improve data quality by 30%, and deliver trusted datasets for business reporting.
@@ -3786,13 +3343,33 @@
 Important: Hex and Dagster are included in the ATS keyword coverage because they appear in the job description, but they are not attributed to specific work accomplishments. Add them to an experience bullet only if you can accurately support that claim. Likewise, validate the added impact percentages and business outcomes against your actual work before submitting the résumé.</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Ajay Bhavani Prasad Adabala - Resume legora</t>
-        </is>
-      </c>
-    </row>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ajay Bhavani Prasad Adabala - Resume radwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="270" customHeight="1"/>
+    <row r="81" ht="225" customHeight="1"/>
+    <row r="82" ht="225" customHeight="1"/>
+    <row r="83" ht="270" customHeight="1"/>
+    <row r="84" ht="225" customHeight="1"/>
+    <row r="85" ht="225" customHeight="1"/>
+    <row r="86" ht="270" customHeight="1"/>
+    <row r="87" ht="225" customHeight="1"/>
+    <row r="88" ht="270" customHeight="1"/>
+    <row r="89" ht="225" customHeight="1"/>
+    <row r="90" ht="270" customHeight="1"/>
+    <row r="91" ht="270" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Century Gothic"&amp;1 &amp;K5514B4 General#_x000d_</oddHeader>
+    <oddFooter>&amp;R&amp;"Century Gothic"&amp;9 &amp;K5514B4_x000d_# General</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>